--- a/scripts/codemagic-ci/testing/PR-Test-Plan-Template-iOS-QA.xlsx
+++ b/scripts/codemagic-ci/testing/PR-Test-Plan-Template-iOS-QA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cbryant/UCSD/campusmobile/scripts/codemagic-ci/testing/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a6wu/work/campus-mobile/scripts/codemagic-ci/testing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{DD3D6370-9E6F-9546-9E3F-B770E3449134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D80464F-97A5-47A8-AB6C-DFAE23F48E24}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FA89B5-5090-8B4D-83F1-59542CE85486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="500" windowWidth="38400" windowHeight="19960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PR Test Plan" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>PR ${PR_NUMBER} Test Plan - ${APP_VERSION} - ${BUILD_ENV}</t>
   </si>
@@ -59,6 +59,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Time and Date Testing Was Complete (Testing must be done between </t>
     </r>
@@ -69,6 +70,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>6 AM and 5 PM, Mon-Fri</t>
     </r>
@@ -78,6 +80,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">)
 </t>
@@ -87,6 +90,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>(see "services duty cycle" section on the right side of the testing sheet for more info)</t>
     </r>
@@ -149,34 +153,16 @@
     <t>FAIL:</t>
   </si>
   <si>
-    <t>Scanner Testing</t>
-  </si>
-  <si>
     <t>FOLLOW-UP:</t>
-  </si>
-  <si>
-    <t>Native Scanner Code128 submission successful</t>
   </si>
   <si>
     <t>N/A:</t>
   </si>
   <si>
-    <t>Native Scanner 2D submission successful</t>
-  </si>
-  <si>
-    <t>Push Testing</t>
-  </si>
-  <si>
     <t>Tools</t>
   </si>
   <si>
-    <t>DM Push Notification received and appears in Notifications tab</t>
-  </si>
-  <si>
     <t>Notification Tool (QA)</t>
-  </si>
-  <si>
-    <t>TM Push Notification received and appears in Notifications tab</t>
   </si>
   <si>
     <t>Barcode Generator (Code128) - Random</t>
@@ -219,7 +205,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="13">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -288,6 +274,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -295,11 +282,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="14">
@@ -458,7 +441,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -600,6 +583,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1068,17 +1054,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:U947"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="96.5703125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.5703125" style="28" customWidth="1"/>
+    <col min="1" max="1" width="96.5" style="4" customWidth="1"/>
+    <col min="2" max="2" width="28.5" style="28" customWidth="1"/>
     <col min="3" max="3" width="5" style="16" customWidth="1"/>
-    <col min="4" max="4" width="29.7109375" style="12" customWidth="1"/>
+    <col min="4" max="4" width="29.6640625" style="12" customWidth="1"/>
     <col min="5" max="5" width="28" style="12" customWidth="1"/>
-    <col min="6" max="16384" width="14.42578125" style="12"/>
+    <col min="6" max="16384" width="14.5" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="6" customFormat="1" ht="51.75" customHeight="1">
+    <row r="1" spans="1:21" s="6" customFormat="1" ht="51.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1104,7 +1090,7 @@
       <c r="T1" s="7"/>
       <c r="U1" s="7"/>
     </row>
-    <row r="2" spans="1:21" s="6" customFormat="1" ht="15.75" customHeight="1">
+    <row r="2" spans="1:21" s="6" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
@@ -1133,7 +1119,7 @@
       <c r="T2" s="7"/>
       <c r="U2" s="7"/>
     </row>
-    <row r="3" spans="1:21" ht="31.5" customHeight="1">
+    <row r="3" spans="1:21" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="30" t="s">
         <v>5</v>
       </c>
@@ -1164,7 +1150,7 @@
       <c r="T3" s="11"/>
       <c r="U3" s="11"/>
     </row>
-    <row r="4" spans="1:21" ht="18" customHeight="1">
+    <row r="4" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -1193,7 +1179,7 @@
       <c r="T4" s="11"/>
       <c r="U4" s="11"/>
     </row>
-    <row r="5" spans="1:21" ht="18" customHeight="1">
+    <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="36" t="s">
         <v>12</v>
       </c>
@@ -1222,7 +1208,7 @@
       <c r="T5" s="11"/>
       <c r="U5" s="11"/>
     </row>
-    <row r="6" spans="1:21" ht="18" customHeight="1">
+    <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="39" t="s">
         <v>15</v>
       </c>
@@ -1251,7 +1237,7 @@
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
     </row>
-    <row r="7" spans="1:21" ht="18" customHeight="1">
+    <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="36" t="s">
         <v>18</v>
       </c>
@@ -1276,7 +1262,7 @@
       <c r="T7" s="11"/>
       <c r="U7" s="11"/>
     </row>
-    <row r="8" spans="1:21" ht="18" customHeight="1">
+    <row r="8" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="39" t="s">
         <v>19</v>
       </c>
@@ -1303,7 +1289,7 @@
       <c r="T8" s="11"/>
       <c r="U8" s="11"/>
     </row>
-    <row r="9" spans="1:21" ht="18" customHeight="1">
+    <row r="9" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="36" t="s">
         <v>21</v>
       </c>
@@ -1330,7 +1316,7 @@
       <c r="T9" s="11"/>
       <c r="U9" s="11"/>
     </row>
-    <row r="10" spans="1:21" ht="18" customHeight="1">
+    <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="22" t="s">
         <v>23</v>
       </c>
@@ -1357,14 +1343,14 @@
       <c r="T10" s="11"/>
       <c r="U10" s="11"/>
     </row>
-    <row r="11" spans="1:21" ht="18" customHeight="1">
+    <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B11" s="26"/>
       <c r="C11" s="31"/>
       <c r="D11" s="32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="11"/>
@@ -1384,14 +1370,12 @@
       <c r="T11" s="11"/>
       <c r="U11" s="11"/>
     </row>
-    <row r="12" spans="1:21" ht="18" customHeight="1">
-      <c r="A12" s="39" t="s">
-        <v>27</v>
-      </c>
+    <row r="12" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="22"/>
       <c r="B12" s="40"/>
       <c r="C12" s="41"/>
       <c r="D12" s="41" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E12" s="14"/>
       <c r="F12" s="11"/>
@@ -1411,11 +1395,9 @@
       <c r="T12" s="11"/>
       <c r="U12" s="11"/>
     </row>
-    <row r="13" spans="1:21" ht="18" customHeight="1">
-      <c r="A13" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="37"/>
+    <row r="13" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="38"/>
+      <c r="B13" s="45"/>
       <c r="C13" s="32"/>
       <c r="D13" s="33"/>
       <c r="E13" s="33"/>
@@ -1436,14 +1418,12 @@
       <c r="T13" s="11"/>
       <c r="U13" s="11"/>
     </row>
-    <row r="14" spans="1:21" ht="18" customHeight="1">
-      <c r="A14" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="26"/>
+    <row r="14" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="22"/>
+      <c r="B14" s="43"/>
       <c r="C14" s="41"/>
       <c r="D14" s="19" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E14" s="19"/>
       <c r="F14" s="11"/>
@@ -1463,14 +1443,12 @@
       <c r="T14" s="11"/>
       <c r="U14" s="11"/>
     </row>
-    <row r="15" spans="1:21" ht="18" customHeight="1">
-      <c r="A15" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="37"/>
+    <row r="15" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="38"/>
+      <c r="B15" s="45"/>
       <c r="C15" s="32"/>
       <c r="D15" s="20" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E15" s="38"/>
       <c r="F15" s="11"/>
@@ -1490,14 +1468,12 @@
       <c r="T15" s="11"/>
       <c r="U15" s="11"/>
     </row>
-    <row r="16" spans="1:21" ht="18" customHeight="1">
-      <c r="A16" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="40"/>
+    <row r="16" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="22"/>
+      <c r="B16" s="43"/>
       <c r="C16" s="41"/>
       <c r="D16" s="21" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E16" s="22"/>
       <c r="F16" s="11"/>
@@ -1517,14 +1493,14 @@
       <c r="T16" s="11"/>
       <c r="U16" s="11"/>
     </row>
-    <row r="17" spans="1:21" ht="18" customHeight="1">
-      <c r="A17" s="2" t="s">
-        <v>36</v>
+    <row r="17" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="3" t="s">
+        <v>37</v>
       </c>
-      <c r="B17" s="26"/>
+      <c r="B17" s="48"/>
       <c r="C17" s="32"/>
       <c r="D17" s="20" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E17" s="44"/>
       <c r="F17" s="11"/>
@@ -1536,12 +1512,14 @@
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
     </row>
-    <row r="18" spans="1:21" ht="18" customHeight="1">
-      <c r="A18" s="22"/>
+    <row r="18" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="47" t="s">
+        <v>39</v>
+      </c>
       <c r="B18" s="40"/>
       <c r="C18" s="41"/>
       <c r="D18" s="21" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E18" s="42"/>
       <c r="F18" s="11"/>
@@ -1561,12 +1539,14 @@
       <c r="T18" s="11"/>
       <c r="U18" s="11"/>
     </row>
-    <row r="19" spans="1:21" ht="18" customHeight="1">
-      <c r="A19" s="38"/>
-      <c r="B19" s="45"/>
+    <row r="19" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="37"/>
       <c r="C19" s="32"/>
       <c r="D19" s="20" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E19" s="33"/>
       <c r="F19" s="11"/>
@@ -1586,12 +1566,11 @@
       <c r="T19" s="11"/>
       <c r="U19" s="11"/>
     </row>
-    <row r="20" spans="1:21" ht="18" customHeight="1">
-      <c r="A20" s="22"/>
-      <c r="B20" s="43"/>
+    <row r="20" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="27"/>
       <c r="C20" s="41"/>
       <c r="D20" s="21" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E20" s="42"/>
       <c r="F20" s="11"/>
@@ -1611,12 +1590,11 @@
       <c r="T20" s="11"/>
       <c r="U20" s="11"/>
     </row>
-    <row r="21" spans="1:21" ht="18" customHeight="1">
-      <c r="A21" s="38"/>
-      <c r="B21" s="45"/>
+    <row r="21" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="27"/>
       <c r="C21" s="32"/>
       <c r="D21" s="20" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E21" s="33"/>
       <c r="F21" s="11"/>
@@ -1636,12 +1614,11 @@
       <c r="T21" s="11"/>
       <c r="U21" s="11"/>
     </row>
-    <row r="22" spans="1:21" ht="18" customHeight="1">
-      <c r="A22" s="22"/>
-      <c r="B22" s="43"/>
+    <row r="22" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="27"/>
       <c r="C22" s="41"/>
       <c r="D22" s="19" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E22" s="19"/>
       <c r="F22" s="11"/>
@@ -1661,14 +1638,11 @@
       <c r="T22" s="11"/>
       <c r="U22" s="11"/>
     </row>
-    <row r="23" spans="1:21" ht="18" customHeight="1">
-      <c r="A23" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B23" s="26"/>
+    <row r="23" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="27"/>
       <c r="C23" s="32"/>
       <c r="D23" s="20" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E23" s="46"/>
       <c r="F23" s="11"/>
@@ -1688,11 +1662,8 @@
       <c r="T23" s="11"/>
       <c r="U23" s="11"/>
     </row>
-    <row r="24" spans="1:21" ht="18" customHeight="1">
-      <c r="A24" s="47" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="43"/>
+    <row r="24" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B24" s="27"/>
       <c r="C24" s="41"/>
       <c r="D24" s="42"/>
       <c r="E24" s="35"/>
@@ -1713,11 +1684,8 @@
       <c r="T24" s="11"/>
       <c r="U24" s="11"/>
     </row>
-    <row r="25" spans="1:21" ht="31.5" customHeight="1">
-      <c r="A25" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="37"/>
+    <row r="25" spans="1:21" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B25" s="27"/>
       <c r="C25" s="32"/>
       <c r="D25" s="33"/>
       <c r="E25" s="46"/>
@@ -1738,7 +1706,7 @@
       <c r="T25" s="11"/>
       <c r="U25" s="11"/>
     </row>
-    <row r="26" spans="1:21" ht="18" customHeight="1">
+    <row r="26" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="1"/>
       <c r="B26" s="27"/>
       <c r="C26" s="17"/>
@@ -1760,7 +1728,7 @@
       <c r="T26" s="11"/>
       <c r="U26" s="11"/>
     </row>
-    <row r="27" spans="1:21" ht="18" customHeight="1">
+    <row r="27" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="1"/>
       <c r="B27" s="27"/>
       <c r="C27" s="17"/>
@@ -1783,7 +1751,7 @@
       <c r="T27" s="11"/>
       <c r="U27" s="11"/>
     </row>
-    <row r="28" spans="1:21" ht="18" customHeight="1">
+    <row r="28" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1"/>
       <c r="B28" s="27"/>
       <c r="C28" s="17"/>
@@ -1806,7 +1774,7 @@
       <c r="T28" s="11"/>
       <c r="U28" s="11"/>
     </row>
-    <row r="29" spans="1:21" ht="18" customHeight="1">
+    <row r="29" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="1"/>
       <c r="B29" s="27"/>
       <c r="D29" s="11"/>
@@ -1828,7 +1796,7 @@
       <c r="T29" s="11"/>
       <c r="U29" s="11"/>
     </row>
-    <row r="30" spans="1:21" ht="18" customHeight="1">
+    <row r="30" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="1"/>
       <c r="B30" s="27"/>
       <c r="D30" s="11"/>
@@ -1850,7 +1818,7 @@
       <c r="T30" s="11"/>
       <c r="U30" s="11"/>
     </row>
-    <row r="31" spans="1:21" ht="18" customHeight="1">
+    <row r="31" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="1"/>
       <c r="B31" s="27"/>
       <c r="D31" s="11"/>
@@ -1872,7 +1840,7 @@
       <c r="T31" s="11"/>
       <c r="U31" s="11"/>
     </row>
-    <row r="32" spans="1:21" ht="18" customHeight="1">
+    <row r="32" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
       <c r="B32" s="27"/>
       <c r="D32" s="11"/>
@@ -1894,7 +1862,7 @@
       <c r="T32" s="11"/>
       <c r="U32" s="11"/>
     </row>
-    <row r="33" spans="1:21" ht="18" customHeight="1">
+    <row r="33" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="1"/>
       <c r="B33" s="27"/>
       <c r="C33" s="17"/>
@@ -1917,7 +1885,7 @@
       <c r="T33" s="11"/>
       <c r="U33" s="11"/>
     </row>
-    <row r="34" spans="1:21" ht="18" customHeight="1">
+    <row r="34" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="1"/>
       <c r="B34" s="27"/>
       <c r="C34" s="17"/>
@@ -1940,7 +1908,7 @@
       <c r="T34" s="11"/>
       <c r="U34" s="11"/>
     </row>
-    <row r="35" spans="1:21" ht="18" customHeight="1">
+    <row r="35" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="1"/>
       <c r="B35" s="27"/>
       <c r="C35" s="17"/>
@@ -1963,7 +1931,7 @@
       <c r="T35" s="11"/>
       <c r="U35" s="11"/>
     </row>
-    <row r="36" spans="1:21" ht="18" customHeight="1">
+    <row r="36" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="1"/>
       <c r="B36" s="27"/>
       <c r="C36" s="17"/>
@@ -1986,7 +1954,7 @@
       <c r="T36" s="11"/>
       <c r="U36" s="11"/>
     </row>
-    <row r="37" spans="1:21" ht="18" customHeight="1">
+    <row r="37" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="1"/>
       <c r="B37" s="27"/>
       <c r="C37" s="17"/>
@@ -2009,7 +1977,7 @@
       <c r="T37" s="11"/>
       <c r="U37" s="11"/>
     </row>
-    <row r="38" spans="1:21" ht="18" customHeight="1">
+    <row r="38" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="1"/>
       <c r="B38" s="27"/>
       <c r="C38" s="17"/>
@@ -2032,7 +2000,7 @@
       <c r="T38" s="11"/>
       <c r="U38" s="11"/>
     </row>
-    <row r="39" spans="1:21" ht="18" customHeight="1">
+    <row r="39" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="1"/>
       <c r="B39" s="27"/>
       <c r="C39" s="17"/>
@@ -2055,7 +2023,7 @@
       <c r="T39" s="11"/>
       <c r="U39" s="11"/>
     </row>
-    <row r="40" spans="1:21" ht="18" customHeight="1">
+    <row r="40" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="1"/>
       <c r="B40" s="27"/>
       <c r="C40" s="17"/>
@@ -2078,7 +2046,7 @@
       <c r="T40" s="11"/>
       <c r="U40" s="11"/>
     </row>
-    <row r="41" spans="1:21" ht="18" customHeight="1">
+    <row r="41" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="1"/>
       <c r="B41" s="27"/>
       <c r="C41" s="17"/>
@@ -2101,7 +2069,7 @@
       <c r="T41" s="11"/>
       <c r="U41" s="11"/>
     </row>
-    <row r="42" spans="1:21" ht="18" customHeight="1">
+    <row r="42" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="1"/>
       <c r="B42" s="27"/>
       <c r="C42" s="17"/>
@@ -2124,7 +2092,7 @@
       <c r="T42" s="11"/>
       <c r="U42" s="11"/>
     </row>
-    <row r="43" spans="1:21" ht="18" customHeight="1">
+    <row r="43" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="1"/>
       <c r="B43" s="27"/>
       <c r="C43" s="17"/>
@@ -2147,7 +2115,7 @@
       <c r="T43" s="11"/>
       <c r="U43" s="11"/>
     </row>
-    <row r="44" spans="1:21" ht="18" customHeight="1">
+    <row r="44" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="1"/>
       <c r="B44" s="27"/>
       <c r="C44" s="17"/>
@@ -2170,7 +2138,7 @@
       <c r="T44" s="11"/>
       <c r="U44" s="11"/>
     </row>
-    <row r="45" spans="1:21" ht="18" customHeight="1">
+    <row r="45" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="1"/>
       <c r="B45" s="27"/>
       <c r="C45" s="17"/>
@@ -2193,7 +2161,7 @@
       <c r="T45" s="11"/>
       <c r="U45" s="11"/>
     </row>
-    <row r="46" spans="1:21" ht="18" customHeight="1">
+    <row r="46" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="1"/>
       <c r="B46" s="27"/>
       <c r="C46" s="17"/>
@@ -2216,7 +2184,7 @@
       <c r="T46" s="11"/>
       <c r="U46" s="11"/>
     </row>
-    <row r="47" spans="1:21" ht="18" customHeight="1">
+    <row r="47" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="1"/>
       <c r="B47" s="27"/>
       <c r="C47" s="17"/>
@@ -2239,7 +2207,7 @@
       <c r="T47" s="11"/>
       <c r="U47" s="11"/>
     </row>
-    <row r="48" spans="1:21" ht="18" customHeight="1">
+    <row r="48" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="1"/>
       <c r="B48" s="27"/>
       <c r="C48" s="17"/>
@@ -2262,7 +2230,7 @@
       <c r="T48" s="11"/>
       <c r="U48" s="11"/>
     </row>
-    <row r="49" spans="1:21" ht="18" customHeight="1">
+    <row r="49" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="1"/>
       <c r="B49" s="27"/>
       <c r="C49" s="17"/>
@@ -2285,7 +2253,7 @@
       <c r="T49" s="11"/>
       <c r="U49" s="11"/>
     </row>
-    <row r="50" spans="1:21" ht="18" customHeight="1">
+    <row r="50" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="1"/>
       <c r="B50" s="27"/>
       <c r="C50" s="17"/>
@@ -2308,7 +2276,7 @@
       <c r="T50" s="11"/>
       <c r="U50" s="11"/>
     </row>
-    <row r="51" spans="1:21" ht="18" customHeight="1">
+    <row r="51" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="1"/>
       <c r="B51" s="27"/>
       <c r="C51" s="17"/>
@@ -2331,7 +2299,7 @@
       <c r="T51" s="11"/>
       <c r="U51" s="11"/>
     </row>
-    <row r="52" spans="1:21" ht="18" customHeight="1">
+    <row r="52" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="1"/>
       <c r="B52" s="27"/>
       <c r="C52" s="17"/>
@@ -2354,7 +2322,7 @@
       <c r="T52" s="11"/>
       <c r="U52" s="11"/>
     </row>
-    <row r="53" spans="1:21" ht="18" customHeight="1">
+    <row r="53" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="1"/>
       <c r="B53" s="27"/>
       <c r="C53" s="17"/>
@@ -2377,7 +2345,7 @@
       <c r="T53" s="11"/>
       <c r="U53" s="11"/>
     </row>
-    <row r="54" spans="1:21" ht="18" customHeight="1">
+    <row r="54" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="1"/>
       <c r="B54" s="27"/>
       <c r="C54" s="17"/>
@@ -2400,7 +2368,7 @@
       <c r="T54" s="11"/>
       <c r="U54" s="11"/>
     </row>
-    <row r="55" spans="1:21" ht="18" customHeight="1">
+    <row r="55" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="1"/>
       <c r="B55" s="27"/>
       <c r="C55" s="17"/>
@@ -2423,7 +2391,7 @@
       <c r="T55" s="11"/>
       <c r="U55" s="11"/>
     </row>
-    <row r="56" spans="1:21" ht="18" customHeight="1">
+    <row r="56" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="1"/>
       <c r="B56" s="27"/>
       <c r="C56" s="17"/>
@@ -2446,7 +2414,7 @@
       <c r="T56" s="11"/>
       <c r="U56" s="11"/>
     </row>
-    <row r="57" spans="1:21" ht="18" customHeight="1">
+    <row r="57" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="1"/>
       <c r="B57" s="27"/>
       <c r="C57" s="17"/>
@@ -2469,7 +2437,7 @@
       <c r="T57" s="11"/>
       <c r="U57" s="11"/>
     </row>
-    <row r="58" spans="1:21" ht="18" customHeight="1">
+    <row r="58" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="1"/>
       <c r="B58" s="27"/>
       <c r="C58" s="17"/>
@@ -2492,7 +2460,7 @@
       <c r="T58" s="11"/>
       <c r="U58" s="11"/>
     </row>
-    <row r="59" spans="1:21" ht="18" customHeight="1">
+    <row r="59" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="1"/>
       <c r="B59" s="27"/>
       <c r="C59" s="17"/>
@@ -2515,7 +2483,7 @@
       <c r="T59" s="11"/>
       <c r="U59" s="11"/>
     </row>
-    <row r="60" spans="1:21" ht="18" customHeight="1">
+    <row r="60" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="1"/>
       <c r="B60" s="27"/>
       <c r="C60" s="17"/>
@@ -2538,7 +2506,7 @@
       <c r="T60" s="11"/>
       <c r="U60" s="11"/>
     </row>
-    <row r="61" spans="1:21" ht="18" customHeight="1">
+    <row r="61" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="1"/>
       <c r="B61" s="27"/>
       <c r="C61" s="17"/>
@@ -2561,7 +2529,7 @@
       <c r="T61" s="11"/>
       <c r="U61" s="11"/>
     </row>
-    <row r="62" spans="1:21" ht="18" customHeight="1">
+    <row r="62" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="1"/>
       <c r="B62" s="27"/>
       <c r="C62" s="17"/>
@@ -2584,7 +2552,7 @@
       <c r="T62" s="11"/>
       <c r="U62" s="11"/>
     </row>
-    <row r="63" spans="1:21" ht="18" customHeight="1">
+    <row r="63" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="1"/>
       <c r="B63" s="27"/>
       <c r="C63" s="17"/>
@@ -2607,7 +2575,7 @@
       <c r="T63" s="11"/>
       <c r="U63" s="11"/>
     </row>
-    <row r="64" spans="1:21" ht="18" customHeight="1">
+    <row r="64" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="1"/>
       <c r="B64" s="27"/>
       <c r="C64" s="17"/>
@@ -2630,7 +2598,7 @@
       <c r="T64" s="11"/>
       <c r="U64" s="11"/>
     </row>
-    <row r="65" spans="1:21" ht="18" customHeight="1">
+    <row r="65" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="1"/>
       <c r="B65" s="27"/>
       <c r="C65" s="17"/>
@@ -2653,7 +2621,7 @@
       <c r="T65" s="11"/>
       <c r="U65" s="11"/>
     </row>
-    <row r="66" spans="1:21" ht="18" customHeight="1">
+    <row r="66" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="1"/>
       <c r="B66" s="27"/>
       <c r="C66" s="17"/>
@@ -2676,7 +2644,7 @@
       <c r="T66" s="11"/>
       <c r="U66" s="11"/>
     </row>
-    <row r="67" spans="1:21" ht="18" customHeight="1">
+    <row r="67" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="1"/>
       <c r="B67" s="27"/>
       <c r="C67" s="17"/>
@@ -2699,7 +2667,7 @@
       <c r="T67" s="11"/>
       <c r="U67" s="11"/>
     </row>
-    <row r="68" spans="1:21" ht="18" customHeight="1">
+    <row r="68" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="1"/>
       <c r="B68" s="27"/>
       <c r="C68" s="17"/>
@@ -2722,7 +2690,7 @@
       <c r="T68" s="11"/>
       <c r="U68" s="11"/>
     </row>
-    <row r="69" spans="1:21" ht="18" customHeight="1">
+    <row r="69" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="1"/>
       <c r="B69" s="27"/>
       <c r="C69" s="17"/>
@@ -2745,7 +2713,7 @@
       <c r="T69" s="11"/>
       <c r="U69" s="11"/>
     </row>
-    <row r="70" spans="1:21" ht="18" customHeight="1">
+    <row r="70" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="1"/>
       <c r="B70" s="27"/>
       <c r="C70" s="17"/>
@@ -2768,7 +2736,7 @@
       <c r="T70" s="11"/>
       <c r="U70" s="11"/>
     </row>
-    <row r="71" spans="1:21" ht="18" customHeight="1">
+    <row r="71" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="1"/>
       <c r="B71" s="27"/>
       <c r="C71" s="17"/>
@@ -2791,7 +2759,7 @@
       <c r="T71" s="11"/>
       <c r="U71" s="11"/>
     </row>
-    <row r="72" spans="1:21" ht="18" customHeight="1">
+    <row r="72" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="1"/>
       <c r="B72" s="27"/>
       <c r="C72" s="17"/>
@@ -2814,7 +2782,7 @@
       <c r="T72" s="11"/>
       <c r="U72" s="11"/>
     </row>
-    <row r="73" spans="1:21" ht="18" customHeight="1">
+    <row r="73" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="1"/>
       <c r="B73" s="27"/>
       <c r="C73" s="17"/>
@@ -2837,7 +2805,7 @@
       <c r="T73" s="11"/>
       <c r="U73" s="11"/>
     </row>
-    <row r="74" spans="1:21" ht="18" customHeight="1">
+    <row r="74" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="1"/>
       <c r="B74" s="27"/>
       <c r="C74" s="17"/>
@@ -2860,7 +2828,7 @@
       <c r="T74" s="11"/>
       <c r="U74" s="11"/>
     </row>
-    <row r="75" spans="1:21" ht="18" customHeight="1">
+    <row r="75" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="1"/>
       <c r="B75" s="27"/>
       <c r="C75" s="17"/>
@@ -2883,7 +2851,7 @@
       <c r="T75" s="11"/>
       <c r="U75" s="11"/>
     </row>
-    <row r="76" spans="1:21" ht="18" customHeight="1">
+    <row r="76" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="1"/>
       <c r="B76" s="27"/>
       <c r="C76" s="17"/>
@@ -2906,7 +2874,7 @@
       <c r="T76" s="11"/>
       <c r="U76" s="11"/>
     </row>
-    <row r="77" spans="1:21" ht="18" customHeight="1">
+    <row r="77" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="1"/>
       <c r="B77" s="27"/>
       <c r="C77" s="17"/>
@@ -2929,7 +2897,7 @@
       <c r="T77" s="11"/>
       <c r="U77" s="11"/>
     </row>
-    <row r="78" spans="1:21" ht="18" customHeight="1">
+    <row r="78" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="1"/>
       <c r="B78" s="27"/>
       <c r="C78" s="17"/>
@@ -2952,7 +2920,7 @@
       <c r="T78" s="11"/>
       <c r="U78" s="11"/>
     </row>
-    <row r="79" spans="1:21" ht="18" customHeight="1">
+    <row r="79" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="1"/>
       <c r="B79" s="27"/>
       <c r="C79" s="17"/>
@@ -2975,7 +2943,7 @@
       <c r="T79" s="11"/>
       <c r="U79" s="11"/>
     </row>
-    <row r="80" spans="1:21" ht="18" customHeight="1">
+    <row r="80" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="1"/>
       <c r="B80" s="27"/>
       <c r="C80" s="17"/>
@@ -2998,7 +2966,7 @@
       <c r="T80" s="11"/>
       <c r="U80" s="11"/>
     </row>
-    <row r="81" spans="1:21" ht="18" customHeight="1">
+    <row r="81" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="1"/>
       <c r="B81" s="27"/>
       <c r="C81" s="17"/>
@@ -3021,7 +2989,7 @@
       <c r="T81" s="11"/>
       <c r="U81" s="11"/>
     </row>
-    <row r="82" spans="1:21" ht="18" customHeight="1">
+    <row r="82" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="1"/>
       <c r="B82" s="27"/>
       <c r="C82" s="17"/>
@@ -3044,7 +3012,7 @@
       <c r="T82" s="11"/>
       <c r="U82" s="11"/>
     </row>
-    <row r="83" spans="1:21" ht="18" customHeight="1">
+    <row r="83" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="1"/>
       <c r="B83" s="27"/>
       <c r="C83" s="17"/>
@@ -3067,7 +3035,7 @@
       <c r="T83" s="11"/>
       <c r="U83" s="11"/>
     </row>
-    <row r="84" spans="1:21" ht="18" customHeight="1">
+    <row r="84" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="1"/>
       <c r="B84" s="27"/>
       <c r="C84" s="17"/>
@@ -3090,7 +3058,7 @@
       <c r="T84" s="11"/>
       <c r="U84" s="11"/>
     </row>
-    <row r="85" spans="1:21" ht="18" customHeight="1">
+    <row r="85" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="1"/>
       <c r="B85" s="27"/>
       <c r="C85" s="17"/>
@@ -3113,7 +3081,7 @@
       <c r="T85" s="11"/>
       <c r="U85" s="11"/>
     </row>
-    <row r="86" spans="1:21" ht="18" customHeight="1">
+    <row r="86" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="1"/>
       <c r="B86" s="27"/>
       <c r="C86" s="17"/>
@@ -3136,7 +3104,7 @@
       <c r="T86" s="11"/>
       <c r="U86" s="11"/>
     </row>
-    <row r="87" spans="1:21" ht="18" customHeight="1">
+    <row r="87" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="1"/>
       <c r="B87" s="27"/>
       <c r="C87" s="17"/>
@@ -3159,7 +3127,7 @@
       <c r="T87" s="11"/>
       <c r="U87" s="11"/>
     </row>
-    <row r="88" spans="1:21" ht="18" customHeight="1">
+    <row r="88" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="1"/>
       <c r="B88" s="27"/>
       <c r="C88" s="17"/>
@@ -3182,7 +3150,7 @@
       <c r="T88" s="11"/>
       <c r="U88" s="11"/>
     </row>
-    <row r="89" spans="1:21" ht="18" customHeight="1">
+    <row r="89" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="1"/>
       <c r="B89" s="27"/>
       <c r="C89" s="17"/>
@@ -3205,7 +3173,7 @@
       <c r="T89" s="11"/>
       <c r="U89" s="11"/>
     </row>
-    <row r="90" spans="1:21" ht="18" customHeight="1">
+    <row r="90" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="1"/>
       <c r="B90" s="27"/>
       <c r="C90" s="17"/>
@@ -3228,7 +3196,7 @@
       <c r="T90" s="11"/>
       <c r="U90" s="11"/>
     </row>
-    <row r="91" spans="1:21" ht="18" customHeight="1">
+    <row r="91" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="1"/>
       <c r="B91" s="27"/>
       <c r="C91" s="17"/>
@@ -3251,7 +3219,7 @@
       <c r="T91" s="11"/>
       <c r="U91" s="11"/>
     </row>
-    <row r="92" spans="1:21" ht="18" customHeight="1">
+    <row r="92" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="1"/>
       <c r="B92" s="27"/>
       <c r="C92" s="17"/>
@@ -3274,7 +3242,7 @@
       <c r="T92" s="11"/>
       <c r="U92" s="11"/>
     </row>
-    <row r="93" spans="1:21" ht="18" customHeight="1">
+    <row r="93" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="1"/>
       <c r="B93" s="27"/>
       <c r="C93" s="17"/>
@@ -3297,7 +3265,7 @@
       <c r="T93" s="11"/>
       <c r="U93" s="11"/>
     </row>
-    <row r="94" spans="1:21" ht="18" customHeight="1">
+    <row r="94" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="1"/>
       <c r="B94" s="27"/>
       <c r="C94" s="17"/>
@@ -3320,7 +3288,7 @@
       <c r="T94" s="11"/>
       <c r="U94" s="11"/>
     </row>
-    <row r="95" spans="1:21" ht="18" customHeight="1">
+    <row r="95" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="1"/>
       <c r="B95" s="27"/>
       <c r="C95" s="17"/>
@@ -3343,7 +3311,7 @@
       <c r="T95" s="11"/>
       <c r="U95" s="11"/>
     </row>
-    <row r="96" spans="1:21" ht="18" customHeight="1">
+    <row r="96" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="1"/>
       <c r="B96" s="27"/>
       <c r="C96" s="17"/>
@@ -3366,7 +3334,7 @@
       <c r="T96" s="11"/>
       <c r="U96" s="11"/>
     </row>
-    <row r="97" spans="1:21" ht="18" customHeight="1">
+    <row r="97" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="1"/>
       <c r="B97" s="27"/>
       <c r="C97" s="17"/>
@@ -3389,7 +3357,7 @@
       <c r="T97" s="11"/>
       <c r="U97" s="11"/>
     </row>
-    <row r="98" spans="1:21" ht="18" customHeight="1">
+    <row r="98" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="1"/>
       <c r="B98" s="27"/>
       <c r="C98" s="17"/>
@@ -3412,7 +3380,7 @@
       <c r="T98" s="11"/>
       <c r="U98" s="11"/>
     </row>
-    <row r="99" spans="1:21" ht="18" customHeight="1">
+    <row r="99" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="1"/>
       <c r="B99" s="27"/>
       <c r="C99" s="17"/>
@@ -3435,7 +3403,7 @@
       <c r="T99" s="11"/>
       <c r="U99" s="11"/>
     </row>
-    <row r="100" spans="1:21" ht="18" customHeight="1">
+    <row r="100" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="1"/>
       <c r="B100" s="27"/>
       <c r="C100" s="17"/>
@@ -3458,7 +3426,7 @@
       <c r="T100" s="11"/>
       <c r="U100" s="11"/>
     </row>
-    <row r="101" spans="1:21" ht="18" customHeight="1">
+    <row r="101" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="1"/>
       <c r="B101" s="27"/>
       <c r="C101" s="17"/>
@@ -3481,7 +3449,7 @@
       <c r="T101" s="11"/>
       <c r="U101" s="11"/>
     </row>
-    <row r="102" spans="1:21" ht="18" customHeight="1">
+    <row r="102" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="1"/>
       <c r="B102" s="27"/>
       <c r="C102" s="17"/>
@@ -3504,7 +3472,7 @@
       <c r="T102" s="11"/>
       <c r="U102" s="11"/>
     </row>
-    <row r="103" spans="1:21" ht="18" customHeight="1">
+    <row r="103" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="1"/>
       <c r="B103" s="27"/>
       <c r="C103" s="17"/>
@@ -3527,7 +3495,7 @@
       <c r="T103" s="11"/>
       <c r="U103" s="11"/>
     </row>
-    <row r="104" spans="1:21" ht="18" customHeight="1">
+    <row r="104" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="1"/>
       <c r="B104" s="27"/>
       <c r="C104" s="17"/>
@@ -3550,7 +3518,7 @@
       <c r="T104" s="11"/>
       <c r="U104" s="11"/>
     </row>
-    <row r="105" spans="1:21" ht="18" customHeight="1">
+    <row r="105" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="1"/>
       <c r="B105" s="27"/>
       <c r="C105" s="17"/>
@@ -3573,7 +3541,7 @@
       <c r="T105" s="11"/>
       <c r="U105" s="11"/>
     </row>
-    <row r="106" spans="1:21" ht="18" customHeight="1">
+    <row r="106" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="1"/>
       <c r="B106" s="27"/>
       <c r="C106" s="17"/>
@@ -3596,7 +3564,7 @@
       <c r="T106" s="11"/>
       <c r="U106" s="11"/>
     </row>
-    <row r="107" spans="1:21" ht="18" customHeight="1">
+    <row r="107" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="1"/>
       <c r="B107" s="27"/>
       <c r="C107" s="17"/>
@@ -3619,7 +3587,7 @@
       <c r="T107" s="11"/>
       <c r="U107" s="11"/>
     </row>
-    <row r="108" spans="1:21" ht="18" customHeight="1">
+    <row r="108" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="1"/>
       <c r="B108" s="27"/>
       <c r="C108" s="17"/>
@@ -3642,7 +3610,7 @@
       <c r="T108" s="11"/>
       <c r="U108" s="11"/>
     </row>
-    <row r="109" spans="1:21" ht="18" customHeight="1">
+    <row r="109" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="1"/>
       <c r="B109" s="27"/>
       <c r="C109" s="17"/>
@@ -3665,7 +3633,7 @@
       <c r="T109" s="11"/>
       <c r="U109" s="11"/>
     </row>
-    <row r="110" spans="1:21" ht="18" customHeight="1">
+    <row r="110" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="1"/>
       <c r="B110" s="27"/>
       <c r="C110" s="17"/>
@@ -3688,7 +3656,7 @@
       <c r="T110" s="11"/>
       <c r="U110" s="11"/>
     </row>
-    <row r="111" spans="1:21" ht="18" customHeight="1">
+    <row r="111" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="1"/>
       <c r="B111" s="27"/>
       <c r="C111" s="17"/>
@@ -3711,7 +3679,7 @@
       <c r="T111" s="11"/>
       <c r="U111" s="11"/>
     </row>
-    <row r="112" spans="1:21" ht="18" customHeight="1">
+    <row r="112" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="1"/>
       <c r="B112" s="27"/>
       <c r="C112" s="17"/>
@@ -3734,7 +3702,7 @@
       <c r="T112" s="11"/>
       <c r="U112" s="11"/>
     </row>
-    <row r="113" spans="1:21" ht="18" customHeight="1">
+    <row r="113" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="1"/>
       <c r="B113" s="27"/>
       <c r="C113" s="17"/>
@@ -3757,7 +3725,7 @@
       <c r="T113" s="11"/>
       <c r="U113" s="11"/>
     </row>
-    <row r="114" spans="1:21" ht="18" customHeight="1">
+    <row r="114" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="1"/>
       <c r="B114" s="27"/>
       <c r="C114" s="17"/>
@@ -3780,7 +3748,7 @@
       <c r="T114" s="11"/>
       <c r="U114" s="11"/>
     </row>
-    <row r="115" spans="1:21" ht="18" customHeight="1">
+    <row r="115" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="1"/>
       <c r="B115" s="27"/>
       <c r="C115" s="17"/>
@@ -3803,7 +3771,7 @@
       <c r="T115" s="11"/>
       <c r="U115" s="11"/>
     </row>
-    <row r="116" spans="1:21" ht="18" customHeight="1">
+    <row r="116" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="1"/>
       <c r="B116" s="27"/>
       <c r="C116" s="17"/>
@@ -3826,7 +3794,7 @@
       <c r="T116" s="11"/>
       <c r="U116" s="11"/>
     </row>
-    <row r="117" spans="1:21" ht="18" customHeight="1">
+    <row r="117" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="1"/>
       <c r="B117" s="27"/>
       <c r="C117" s="17"/>
@@ -3849,7 +3817,7 @@
       <c r="T117" s="11"/>
       <c r="U117" s="11"/>
     </row>
-    <row r="118" spans="1:21" ht="18" customHeight="1">
+    <row r="118" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="1"/>
       <c r="B118" s="27"/>
       <c r="C118" s="17"/>
@@ -3872,7 +3840,7 @@
       <c r="T118" s="11"/>
       <c r="U118" s="11"/>
     </row>
-    <row r="119" spans="1:21" ht="18" customHeight="1">
+    <row r="119" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="1"/>
       <c r="B119" s="27"/>
       <c r="C119" s="17"/>
@@ -3895,7 +3863,7 @@
       <c r="T119" s="11"/>
       <c r="U119" s="11"/>
     </row>
-    <row r="120" spans="1:21" ht="18" customHeight="1">
+    <row r="120" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="1"/>
       <c r="B120" s="27"/>
       <c r="C120" s="17"/>
@@ -3918,7 +3886,7 @@
       <c r="T120" s="11"/>
       <c r="U120" s="11"/>
     </row>
-    <row r="121" spans="1:21" ht="18" customHeight="1">
+    <row r="121" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="1"/>
       <c r="B121" s="27"/>
       <c r="C121" s="17"/>
@@ -3941,7 +3909,7 @@
       <c r="T121" s="11"/>
       <c r="U121" s="11"/>
     </row>
-    <row r="122" spans="1:21" ht="18" customHeight="1">
+    <row r="122" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="1"/>
       <c r="B122" s="27"/>
       <c r="C122" s="17"/>
@@ -3964,7 +3932,7 @@
       <c r="T122" s="11"/>
       <c r="U122" s="11"/>
     </row>
-    <row r="123" spans="1:21" ht="18" customHeight="1">
+    <row r="123" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="1"/>
       <c r="B123" s="27"/>
       <c r="C123" s="17"/>
@@ -3987,7 +3955,7 @@
       <c r="T123" s="11"/>
       <c r="U123" s="11"/>
     </row>
-    <row r="124" spans="1:21" ht="18" customHeight="1">
+    <row r="124" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="1"/>
       <c r="B124" s="27"/>
       <c r="C124" s="17"/>
@@ -4010,7 +3978,7 @@
       <c r="T124" s="11"/>
       <c r="U124" s="11"/>
     </row>
-    <row r="125" spans="1:21" ht="18" customHeight="1">
+    <row r="125" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="1"/>
       <c r="B125" s="27"/>
       <c r="C125" s="17"/>
@@ -4033,7 +4001,7 @@
       <c r="T125" s="11"/>
       <c r="U125" s="11"/>
     </row>
-    <row r="126" spans="1:21" ht="18" customHeight="1">
+    <row r="126" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="1"/>
       <c r="B126" s="27"/>
       <c r="C126" s="17"/>
@@ -4056,7 +4024,7 @@
       <c r="T126" s="11"/>
       <c r="U126" s="11"/>
     </row>
-    <row r="127" spans="1:21" ht="18" customHeight="1">
+    <row r="127" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="1"/>
       <c r="B127" s="27"/>
       <c r="C127" s="17"/>
@@ -4079,7 +4047,7 @@
       <c r="T127" s="11"/>
       <c r="U127" s="11"/>
     </row>
-    <row r="128" spans="1:21" ht="18" customHeight="1">
+    <row r="128" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="1"/>
       <c r="B128" s="27"/>
       <c r="C128" s="17"/>
@@ -4102,7 +4070,7 @@
       <c r="T128" s="11"/>
       <c r="U128" s="11"/>
     </row>
-    <row r="129" spans="1:21" ht="18" customHeight="1">
+    <row r="129" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="1"/>
       <c r="B129" s="27"/>
       <c r="C129" s="17"/>
@@ -4125,7 +4093,7 @@
       <c r="T129" s="11"/>
       <c r="U129" s="11"/>
     </row>
-    <row r="130" spans="1:21" ht="18" customHeight="1">
+    <row r="130" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="1"/>
       <c r="B130" s="27"/>
       <c r="C130" s="17"/>
@@ -4148,7 +4116,7 @@
       <c r="T130" s="11"/>
       <c r="U130" s="11"/>
     </row>
-    <row r="131" spans="1:21" ht="18" customHeight="1">
+    <row r="131" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="1"/>
       <c r="B131" s="27"/>
       <c r="C131" s="17"/>
@@ -4171,7 +4139,7 @@
       <c r="T131" s="11"/>
       <c r="U131" s="11"/>
     </row>
-    <row r="132" spans="1:21" ht="18" customHeight="1">
+    <row r="132" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="1"/>
       <c r="B132" s="27"/>
       <c r="C132" s="17"/>
@@ -4194,7 +4162,7 @@
       <c r="T132" s="11"/>
       <c r="U132" s="11"/>
     </row>
-    <row r="133" spans="1:21" ht="18" customHeight="1">
+    <row r="133" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="1"/>
       <c r="B133" s="27"/>
       <c r="C133" s="17"/>
@@ -4217,7 +4185,7 @@
       <c r="T133" s="11"/>
       <c r="U133" s="11"/>
     </row>
-    <row r="134" spans="1:21" ht="18" customHeight="1">
+    <row r="134" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="1"/>
       <c r="B134" s="27"/>
       <c r="C134" s="17"/>
@@ -4240,7 +4208,7 @@
       <c r="T134" s="11"/>
       <c r="U134" s="11"/>
     </row>
-    <row r="135" spans="1:21" ht="18" customHeight="1">
+    <row r="135" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="1"/>
       <c r="B135" s="27"/>
       <c r="C135" s="17"/>
@@ -4263,7 +4231,7 @@
       <c r="T135" s="11"/>
       <c r="U135" s="11"/>
     </row>
-    <row r="136" spans="1:21" ht="18" customHeight="1">
+    <row r="136" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="1"/>
       <c r="B136" s="27"/>
       <c r="C136" s="17"/>
@@ -4286,7 +4254,7 @@
       <c r="T136" s="11"/>
       <c r="U136" s="11"/>
     </row>
-    <row r="137" spans="1:21" ht="18" customHeight="1">
+    <row r="137" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="1"/>
       <c r="B137" s="27"/>
       <c r="C137" s="17"/>
@@ -4309,7 +4277,7 @@
       <c r="T137" s="11"/>
       <c r="U137" s="11"/>
     </row>
-    <row r="138" spans="1:21" ht="18" customHeight="1">
+    <row r="138" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="1"/>
       <c r="B138" s="27"/>
       <c r="C138" s="17"/>
@@ -4332,7 +4300,7 @@
       <c r="T138" s="11"/>
       <c r="U138" s="11"/>
     </row>
-    <row r="139" spans="1:21" ht="18" customHeight="1">
+    <row r="139" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="1"/>
       <c r="B139" s="27"/>
       <c r="C139" s="17"/>
@@ -4355,7 +4323,7 @@
       <c r="T139" s="11"/>
       <c r="U139" s="11"/>
     </row>
-    <row r="140" spans="1:21" ht="18" customHeight="1">
+    <row r="140" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="1"/>
       <c r="B140" s="27"/>
       <c r="C140" s="17"/>
@@ -4378,7 +4346,7 @@
       <c r="T140" s="11"/>
       <c r="U140" s="11"/>
     </row>
-    <row r="141" spans="1:21" ht="18" customHeight="1">
+    <row r="141" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="1"/>
       <c r="B141" s="27"/>
       <c r="C141" s="17"/>
@@ -4401,7 +4369,7 @@
       <c r="T141" s="11"/>
       <c r="U141" s="11"/>
     </row>
-    <row r="142" spans="1:21" ht="18" customHeight="1">
+    <row r="142" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="1"/>
       <c r="B142" s="27"/>
       <c r="C142" s="17"/>
@@ -4424,7 +4392,7 @@
       <c r="T142" s="11"/>
       <c r="U142" s="11"/>
     </row>
-    <row r="143" spans="1:21" ht="18" customHeight="1">
+    <row r="143" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="1"/>
       <c r="B143" s="27"/>
       <c r="C143" s="17"/>
@@ -4447,7 +4415,7 @@
       <c r="T143" s="11"/>
       <c r="U143" s="11"/>
     </row>
-    <row r="144" spans="1:21" ht="18" customHeight="1">
+    <row r="144" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="1"/>
       <c r="B144" s="27"/>
       <c r="C144" s="17"/>
@@ -4470,7 +4438,7 @@
       <c r="T144" s="11"/>
       <c r="U144" s="11"/>
     </row>
-    <row r="145" spans="1:21" ht="18" customHeight="1">
+    <row r="145" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="1"/>
       <c r="B145" s="27"/>
       <c r="C145" s="17"/>
@@ -4493,7 +4461,7 @@
       <c r="T145" s="11"/>
       <c r="U145" s="11"/>
     </row>
-    <row r="146" spans="1:21" ht="18" customHeight="1">
+    <row r="146" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="1"/>
       <c r="B146" s="27"/>
       <c r="C146" s="17"/>
@@ -4516,7 +4484,7 @@
       <c r="T146" s="11"/>
       <c r="U146" s="11"/>
     </row>
-    <row r="147" spans="1:21" ht="18" customHeight="1">
+    <row r="147" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="1"/>
       <c r="B147" s="27"/>
       <c r="C147" s="17"/>
@@ -4539,7 +4507,7 @@
       <c r="T147" s="11"/>
       <c r="U147" s="11"/>
     </row>
-    <row r="148" spans="1:21" ht="18" customHeight="1">
+    <row r="148" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="1"/>
       <c r="B148" s="27"/>
       <c r="C148" s="17"/>
@@ -4562,7 +4530,7 @@
       <c r="T148" s="11"/>
       <c r="U148" s="11"/>
     </row>
-    <row r="149" spans="1:21" ht="18" customHeight="1">
+    <row r="149" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="1"/>
       <c r="B149" s="27"/>
       <c r="C149" s="17"/>
@@ -4585,7 +4553,7 @@
       <c r="T149" s="11"/>
       <c r="U149" s="11"/>
     </row>
-    <row r="150" spans="1:21" ht="18" customHeight="1">
+    <row r="150" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="1"/>
       <c r="B150" s="27"/>
       <c r="C150" s="17"/>
@@ -4608,7 +4576,7 @@
       <c r="T150" s="11"/>
       <c r="U150" s="11"/>
     </row>
-    <row r="151" spans="1:21" ht="18" customHeight="1">
+    <row r="151" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="1"/>
       <c r="B151" s="27"/>
       <c r="C151" s="17"/>
@@ -4631,7 +4599,7 @@
       <c r="T151" s="11"/>
       <c r="U151" s="11"/>
     </row>
-    <row r="152" spans="1:21" ht="18" customHeight="1">
+    <row r="152" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152" s="1"/>
       <c r="B152" s="27"/>
       <c r="C152" s="17"/>
@@ -4654,7 +4622,7 @@
       <c r="T152" s="11"/>
       <c r="U152" s="11"/>
     </row>
-    <row r="153" spans="1:21" ht="18" customHeight="1">
+    <row r="153" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A153" s="1"/>
       <c r="B153" s="27"/>
       <c r="C153" s="17"/>
@@ -4677,7 +4645,7 @@
       <c r="T153" s="11"/>
       <c r="U153" s="11"/>
     </row>
-    <row r="154" spans="1:21" ht="18" customHeight="1">
+    <row r="154" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A154" s="1"/>
       <c r="B154" s="27"/>
       <c r="C154" s="17"/>
@@ -4700,7 +4668,7 @@
       <c r="T154" s="11"/>
       <c r="U154" s="11"/>
     </row>
-    <row r="155" spans="1:21" ht="18" customHeight="1">
+    <row r="155" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A155" s="1"/>
       <c r="B155" s="27"/>
       <c r="C155" s="17"/>
@@ -4723,7 +4691,7 @@
       <c r="T155" s="11"/>
       <c r="U155" s="11"/>
     </row>
-    <row r="156" spans="1:21" ht="18" customHeight="1">
+    <row r="156" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156" s="1"/>
       <c r="B156" s="27"/>
       <c r="C156" s="17"/>
@@ -4746,7 +4714,7 @@
       <c r="T156" s="11"/>
       <c r="U156" s="11"/>
     </row>
-    <row r="157" spans="1:21" ht="18" customHeight="1">
+    <row r="157" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157" s="1"/>
       <c r="B157" s="27"/>
       <c r="C157" s="17"/>
@@ -4769,7 +4737,7 @@
       <c r="T157" s="11"/>
       <c r="U157" s="11"/>
     </row>
-    <row r="158" spans="1:21" ht="18" customHeight="1">
+    <row r="158" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="1"/>
       <c r="B158" s="27"/>
       <c r="C158" s="17"/>
@@ -4792,7 +4760,7 @@
       <c r="T158" s="11"/>
       <c r="U158" s="11"/>
     </row>
-    <row r="159" spans="1:21" ht="18" customHeight="1">
+    <row r="159" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159" s="1"/>
       <c r="B159" s="27"/>
       <c r="C159" s="17"/>
@@ -4815,7 +4783,7 @@
       <c r="T159" s="11"/>
       <c r="U159" s="11"/>
     </row>
-    <row r="160" spans="1:21" ht="18" customHeight="1">
+    <row r="160" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160" s="1"/>
       <c r="B160" s="27"/>
       <c r="C160" s="17"/>
@@ -4838,7 +4806,7 @@
       <c r="T160" s="11"/>
       <c r="U160" s="11"/>
     </row>
-    <row r="161" spans="1:21" ht="18" customHeight="1">
+    <row r="161" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161" s="1"/>
       <c r="B161" s="27"/>
       <c r="C161" s="17"/>
@@ -4861,7 +4829,7 @@
       <c r="T161" s="11"/>
       <c r="U161" s="11"/>
     </row>
-    <row r="162" spans="1:21" ht="18" customHeight="1">
+    <row r="162" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="1"/>
       <c r="B162" s="27"/>
       <c r="C162" s="17"/>
@@ -4884,7 +4852,7 @@
       <c r="T162" s="11"/>
       <c r="U162" s="11"/>
     </row>
-    <row r="163" spans="1:21" ht="18" customHeight="1">
+    <row r="163" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163" s="1"/>
       <c r="B163" s="27"/>
       <c r="C163" s="17"/>
@@ -4907,7 +4875,7 @@
       <c r="T163" s="11"/>
       <c r="U163" s="11"/>
     </row>
-    <row r="164" spans="1:21" ht="18" customHeight="1">
+    <row r="164" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164" s="1"/>
       <c r="B164" s="27"/>
       <c r="C164" s="17"/>
@@ -4930,7 +4898,7 @@
       <c r="T164" s="11"/>
       <c r="U164" s="11"/>
     </row>
-    <row r="165" spans="1:21" ht="18" customHeight="1">
+    <row r="165" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165" s="1"/>
       <c r="B165" s="27"/>
       <c r="C165" s="17"/>
@@ -4953,7 +4921,7 @@
       <c r="T165" s="11"/>
       <c r="U165" s="11"/>
     </row>
-    <row r="166" spans="1:21" ht="18" customHeight="1">
+    <row r="166" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A166" s="1"/>
       <c r="B166" s="27"/>
       <c r="C166" s="17"/>
@@ -4976,7 +4944,7 @@
       <c r="T166" s="11"/>
       <c r="U166" s="11"/>
     </row>
-    <row r="167" spans="1:21" ht="18" customHeight="1">
+    <row r="167" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167" s="1"/>
       <c r="B167" s="27"/>
       <c r="C167" s="17"/>
@@ -4999,7 +4967,7 @@
       <c r="T167" s="11"/>
       <c r="U167" s="11"/>
     </row>
-    <row r="168" spans="1:21" ht="18" customHeight="1">
+    <row r="168" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168" s="1"/>
       <c r="B168" s="27"/>
       <c r="C168" s="17"/>
@@ -5022,7 +4990,7 @@
       <c r="T168" s="11"/>
       <c r="U168" s="11"/>
     </row>
-    <row r="169" spans="1:21" ht="18" customHeight="1">
+    <row r="169" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169" s="1"/>
       <c r="B169" s="27"/>
       <c r="C169" s="17"/>
@@ -5045,7 +5013,7 @@
       <c r="T169" s="11"/>
       <c r="U169" s="11"/>
     </row>
-    <row r="170" spans="1:21" ht="18" customHeight="1">
+    <row r="170" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="1"/>
       <c r="B170" s="27"/>
       <c r="C170" s="17"/>
@@ -5068,7 +5036,7 @@
       <c r="T170" s="11"/>
       <c r="U170" s="11"/>
     </row>
-    <row r="171" spans="1:21" ht="18" customHeight="1">
+    <row r="171" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A171" s="1"/>
       <c r="B171" s="27"/>
       <c r="C171" s="17"/>
@@ -5091,7 +5059,7 @@
       <c r="T171" s="11"/>
       <c r="U171" s="11"/>
     </row>
-    <row r="172" spans="1:21" ht="18" customHeight="1">
+    <row r="172" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172" s="1"/>
       <c r="B172" s="27"/>
       <c r="C172" s="17"/>
@@ -5114,7 +5082,7 @@
       <c r="T172" s="11"/>
       <c r="U172" s="11"/>
     </row>
-    <row r="173" spans="1:21" ht="18" customHeight="1">
+    <row r="173" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A173" s="1"/>
       <c r="B173" s="27"/>
       <c r="C173" s="17"/>
@@ -5137,7 +5105,7 @@
       <c r="T173" s="11"/>
       <c r="U173" s="11"/>
     </row>
-    <row r="174" spans="1:21" ht="18" customHeight="1">
+    <row r="174" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A174" s="1"/>
       <c r="B174" s="27"/>
       <c r="C174" s="17"/>
@@ -5160,7 +5128,7 @@
       <c r="T174" s="11"/>
       <c r="U174" s="11"/>
     </row>
-    <row r="175" spans="1:21" ht="18" customHeight="1">
+    <row r="175" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A175" s="1"/>
       <c r="B175" s="27"/>
       <c r="C175" s="17"/>
@@ -5183,7 +5151,7 @@
       <c r="T175" s="11"/>
       <c r="U175" s="11"/>
     </row>
-    <row r="176" spans="1:21" ht="18" customHeight="1">
+    <row r="176" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A176" s="1"/>
       <c r="B176" s="27"/>
       <c r="C176" s="17"/>
@@ -5206,7 +5174,7 @@
       <c r="T176" s="11"/>
       <c r="U176" s="11"/>
     </row>
-    <row r="177" spans="1:21" ht="18" customHeight="1">
+    <row r="177" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A177" s="1"/>
       <c r="B177" s="27"/>
       <c r="C177" s="17"/>
@@ -5229,7 +5197,7 @@
       <c r="T177" s="11"/>
       <c r="U177" s="11"/>
     </row>
-    <row r="178" spans="1:21" ht="18" customHeight="1">
+    <row r="178" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A178" s="1"/>
       <c r="B178" s="27"/>
       <c r="C178" s="17"/>
@@ -5252,7 +5220,7 @@
       <c r="T178" s="11"/>
       <c r="U178" s="11"/>
     </row>
-    <row r="179" spans="1:21" ht="18" customHeight="1">
+    <row r="179" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A179" s="1"/>
       <c r="B179" s="27"/>
       <c r="C179" s="17"/>
@@ -5275,7 +5243,7 @@
       <c r="T179" s="11"/>
       <c r="U179" s="11"/>
     </row>
-    <row r="180" spans="1:21" ht="18" customHeight="1">
+    <row r="180" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A180" s="1"/>
       <c r="B180" s="27"/>
       <c r="C180" s="17"/>
@@ -5298,7 +5266,7 @@
       <c r="T180" s="11"/>
       <c r="U180" s="11"/>
     </row>
-    <row r="181" spans="1:21" ht="18" customHeight="1">
+    <row r="181" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A181" s="1"/>
       <c r="B181" s="27"/>
       <c r="C181" s="17"/>
@@ -5321,7 +5289,7 @@
       <c r="T181" s="11"/>
       <c r="U181" s="11"/>
     </row>
-    <row r="182" spans="1:21" ht="18" customHeight="1">
+    <row r="182" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A182" s="1"/>
       <c r="B182" s="27"/>
       <c r="C182" s="17"/>
@@ -5344,7 +5312,7 @@
       <c r="T182" s="11"/>
       <c r="U182" s="11"/>
     </row>
-    <row r="183" spans="1:21" ht="18" customHeight="1">
+    <row r="183" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A183" s="1"/>
       <c r="B183" s="27"/>
       <c r="C183" s="17"/>
@@ -5367,7 +5335,7 @@
       <c r="T183" s="11"/>
       <c r="U183" s="11"/>
     </row>
-    <row r="184" spans="1:21" ht="18" customHeight="1">
+    <row r="184" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A184" s="1"/>
       <c r="B184" s="27"/>
       <c r="C184" s="17"/>
@@ -5390,7 +5358,7 @@
       <c r="T184" s="11"/>
       <c r="U184" s="11"/>
     </row>
-    <row r="185" spans="1:21" ht="18" customHeight="1">
+    <row r="185" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A185" s="1"/>
       <c r="B185" s="27"/>
       <c r="C185" s="17"/>
@@ -5413,7 +5381,7 @@
       <c r="T185" s="11"/>
       <c r="U185" s="11"/>
     </row>
-    <row r="186" spans="1:21" ht="18" customHeight="1">
+    <row r="186" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A186" s="1"/>
       <c r="B186" s="27"/>
       <c r="C186" s="17"/>
@@ -5436,7 +5404,7 @@
       <c r="T186" s="11"/>
       <c r="U186" s="11"/>
     </row>
-    <row r="187" spans="1:21" ht="18" customHeight="1">
+    <row r="187" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A187" s="1"/>
       <c r="B187" s="27"/>
       <c r="C187" s="17"/>
@@ -5459,7 +5427,7 @@
       <c r="T187" s="11"/>
       <c r="U187" s="11"/>
     </row>
-    <row r="188" spans="1:21" ht="18" customHeight="1">
+    <row r="188" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A188" s="1"/>
       <c r="B188" s="27"/>
       <c r="C188" s="17"/>
@@ -5482,7 +5450,7 @@
       <c r="T188" s="11"/>
       <c r="U188" s="11"/>
     </row>
-    <row r="189" spans="1:21" ht="18" customHeight="1">
+    <row r="189" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A189" s="1"/>
       <c r="B189" s="27"/>
       <c r="C189" s="17"/>
@@ -5505,7 +5473,7 @@
       <c r="T189" s="11"/>
       <c r="U189" s="11"/>
     </row>
-    <row r="190" spans="1:21" ht="18" customHeight="1">
+    <row r="190" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A190" s="1"/>
       <c r="B190" s="27"/>
       <c r="C190" s="17"/>
@@ -5528,7 +5496,7 @@
       <c r="T190" s="11"/>
       <c r="U190" s="11"/>
     </row>
-    <row r="191" spans="1:21" ht="18" customHeight="1">
+    <row r="191" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A191" s="1"/>
       <c r="B191" s="27"/>
       <c r="C191" s="17"/>
@@ -5551,7 +5519,7 @@
       <c r="T191" s="11"/>
       <c r="U191" s="11"/>
     </row>
-    <row r="192" spans="1:21" ht="18" customHeight="1">
+    <row r="192" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A192" s="1"/>
       <c r="B192" s="27"/>
       <c r="C192" s="17"/>
@@ -5574,7 +5542,7 @@
       <c r="T192" s="11"/>
       <c r="U192" s="11"/>
     </row>
-    <row r="193" spans="1:21" ht="18" customHeight="1">
+    <row r="193" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A193" s="1"/>
       <c r="B193" s="27"/>
       <c r="C193" s="17"/>
@@ -5597,7 +5565,7 @@
       <c r="T193" s="11"/>
       <c r="U193" s="11"/>
     </row>
-    <row r="194" spans="1:21" ht="18" customHeight="1">
+    <row r="194" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A194" s="1"/>
       <c r="B194" s="27"/>
       <c r="C194" s="17"/>
@@ -5620,7 +5588,7 @@
       <c r="T194" s="11"/>
       <c r="U194" s="11"/>
     </row>
-    <row r="195" spans="1:21" ht="18" customHeight="1">
+    <row r="195" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A195" s="1"/>
       <c r="B195" s="27"/>
       <c r="C195" s="17"/>
@@ -5643,7 +5611,7 @@
       <c r="T195" s="11"/>
       <c r="U195" s="11"/>
     </row>
-    <row r="196" spans="1:21" ht="18" customHeight="1">
+    <row r="196" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A196" s="1"/>
       <c r="B196" s="27"/>
       <c r="C196" s="17"/>
@@ -5666,7 +5634,7 @@
       <c r="T196" s="11"/>
       <c r="U196" s="11"/>
     </row>
-    <row r="197" spans="1:21" ht="18" customHeight="1">
+    <row r="197" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A197" s="1"/>
       <c r="B197" s="27"/>
       <c r="C197" s="17"/>
@@ -5689,7 +5657,7 @@
       <c r="T197" s="11"/>
       <c r="U197" s="11"/>
     </row>
-    <row r="198" spans="1:21" ht="18" customHeight="1">
+    <row r="198" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A198" s="1"/>
       <c r="B198" s="27"/>
       <c r="C198" s="17"/>
@@ -5712,7 +5680,7 @@
       <c r="T198" s="11"/>
       <c r="U198" s="11"/>
     </row>
-    <row r="199" spans="1:21" ht="18" customHeight="1">
+    <row r="199" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A199" s="1"/>
       <c r="B199" s="27"/>
       <c r="C199" s="17"/>
@@ -5735,7 +5703,7 @@
       <c r="T199" s="11"/>
       <c r="U199" s="11"/>
     </row>
-    <row r="200" spans="1:21" ht="18" customHeight="1">
+    <row r="200" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A200" s="1"/>
       <c r="B200" s="27"/>
       <c r="C200" s="17"/>
@@ -5758,7 +5726,7 @@
       <c r="T200" s="11"/>
       <c r="U200" s="11"/>
     </row>
-    <row r="201" spans="1:21" ht="18" customHeight="1">
+    <row r="201" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A201" s="1"/>
       <c r="B201" s="27"/>
       <c r="C201" s="17"/>
@@ -5781,7 +5749,7 @@
       <c r="T201" s="11"/>
       <c r="U201" s="11"/>
     </row>
-    <row r="202" spans="1:21" ht="18" customHeight="1">
+    <row r="202" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A202" s="1"/>
       <c r="B202" s="27"/>
       <c r="C202" s="17"/>
@@ -5804,7 +5772,7 @@
       <c r="T202" s="11"/>
       <c r="U202" s="11"/>
     </row>
-    <row r="203" spans="1:21" ht="18" customHeight="1">
+    <row r="203" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A203" s="1"/>
       <c r="B203" s="27"/>
       <c r="C203" s="17"/>
@@ -5827,7 +5795,7 @@
       <c r="T203" s="11"/>
       <c r="U203" s="11"/>
     </row>
-    <row r="204" spans="1:21" ht="18" customHeight="1">
+    <row r="204" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A204" s="1"/>
       <c r="B204" s="27"/>
       <c r="C204" s="17"/>
@@ -5850,7 +5818,7 @@
       <c r="T204" s="11"/>
       <c r="U204" s="11"/>
     </row>
-    <row r="205" spans="1:21" ht="18" customHeight="1">
+    <row r="205" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A205" s="1"/>
       <c r="B205" s="27"/>
       <c r="C205" s="17"/>
@@ -5873,7 +5841,7 @@
       <c r="T205" s="11"/>
       <c r="U205" s="11"/>
     </row>
-    <row r="206" spans="1:21" ht="18" customHeight="1">
+    <row r="206" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A206" s="1"/>
       <c r="B206" s="27"/>
       <c r="C206" s="17"/>
@@ -5896,7 +5864,7 @@
       <c r="T206" s="11"/>
       <c r="U206" s="11"/>
     </row>
-    <row r="207" spans="1:21" ht="18" customHeight="1">
+    <row r="207" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A207" s="1"/>
       <c r="B207" s="27"/>
       <c r="C207" s="17"/>
@@ -5919,7 +5887,7 @@
       <c r="T207" s="11"/>
       <c r="U207" s="11"/>
     </row>
-    <row r="208" spans="1:21" ht="18" customHeight="1">
+    <row r="208" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A208" s="1"/>
       <c r="B208" s="27"/>
       <c r="C208" s="17"/>
@@ -5942,7 +5910,7 @@
       <c r="T208" s="11"/>
       <c r="U208" s="11"/>
     </row>
-    <row r="209" spans="1:21" ht="18" customHeight="1">
+    <row r="209" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A209" s="1"/>
       <c r="B209" s="27"/>
       <c r="C209" s="17"/>
@@ -5965,7 +5933,7 @@
       <c r="T209" s="11"/>
       <c r="U209" s="11"/>
     </row>
-    <row r="210" spans="1:21" ht="18" customHeight="1">
+    <row r="210" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A210" s="1"/>
       <c r="B210" s="27"/>
       <c r="C210" s="17"/>
@@ -5988,7 +5956,7 @@
       <c r="T210" s="11"/>
       <c r="U210" s="11"/>
     </row>
-    <row r="211" spans="1:21" ht="18" customHeight="1">
+    <row r="211" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A211" s="1"/>
       <c r="B211" s="27"/>
       <c r="C211" s="17"/>
@@ -6011,7 +5979,7 @@
       <c r="T211" s="11"/>
       <c r="U211" s="11"/>
     </row>
-    <row r="212" spans="1:21" ht="18" customHeight="1">
+    <row r="212" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A212" s="1"/>
       <c r="B212" s="27"/>
       <c r="C212" s="17"/>
@@ -6034,7 +6002,7 @@
       <c r="T212" s="11"/>
       <c r="U212" s="11"/>
     </row>
-    <row r="213" spans="1:21" ht="18" customHeight="1">
+    <row r="213" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A213" s="1"/>
       <c r="B213" s="27"/>
       <c r="C213" s="17"/>
@@ -6057,7 +6025,7 @@
       <c r="T213" s="11"/>
       <c r="U213" s="11"/>
     </row>
-    <row r="214" spans="1:21" ht="18" customHeight="1">
+    <row r="214" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A214" s="1"/>
       <c r="B214" s="27"/>
       <c r="C214" s="17"/>
@@ -6080,7 +6048,7 @@
       <c r="T214" s="11"/>
       <c r="U214" s="11"/>
     </row>
-    <row r="215" spans="1:21" ht="18" customHeight="1">
+    <row r="215" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A215" s="1"/>
       <c r="B215" s="27"/>
       <c r="C215" s="17"/>
@@ -6103,7 +6071,7 @@
       <c r="T215" s="11"/>
       <c r="U215" s="11"/>
     </row>
-    <row r="216" spans="1:21" ht="18" customHeight="1">
+    <row r="216" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A216" s="1"/>
       <c r="B216" s="27"/>
       <c r="C216" s="17"/>
@@ -6126,7 +6094,7 @@
       <c r="T216" s="11"/>
       <c r="U216" s="11"/>
     </row>
-    <row r="217" spans="1:21" ht="18" customHeight="1">
+    <row r="217" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A217" s="1"/>
       <c r="B217" s="27"/>
       <c r="C217" s="17"/>
@@ -6149,7 +6117,7 @@
       <c r="T217" s="11"/>
       <c r="U217" s="11"/>
     </row>
-    <row r="218" spans="1:21" ht="18" customHeight="1">
+    <row r="218" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A218" s="1"/>
       <c r="B218" s="27"/>
       <c r="C218" s="17"/>
@@ -6172,7 +6140,7 @@
       <c r="T218" s="11"/>
       <c r="U218" s="11"/>
     </row>
-    <row r="219" spans="1:21" ht="18" customHeight="1">
+    <row r="219" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A219" s="1"/>
       <c r="B219" s="27"/>
       <c r="C219" s="17"/>
@@ -6195,7 +6163,7 @@
       <c r="T219" s="11"/>
       <c r="U219" s="11"/>
     </row>
-    <row r="220" spans="1:21" ht="18" customHeight="1">
+    <row r="220" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A220" s="1"/>
       <c r="B220" s="27"/>
       <c r="C220" s="17"/>
@@ -6218,7 +6186,7 @@
       <c r="T220" s="11"/>
       <c r="U220" s="11"/>
     </row>
-    <row r="221" spans="1:21" ht="18" customHeight="1">
+    <row r="221" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A221" s="1"/>
       <c r="B221" s="27"/>
       <c r="C221" s="17"/>
@@ -6241,7 +6209,7 @@
       <c r="T221" s="11"/>
       <c r="U221" s="11"/>
     </row>
-    <row r="222" spans="1:21" ht="18" customHeight="1">
+    <row r="222" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A222" s="1"/>
       <c r="B222" s="27"/>
       <c r="C222" s="17"/>
@@ -6264,7 +6232,7 @@
       <c r="T222" s="11"/>
       <c r="U222" s="11"/>
     </row>
-    <row r="223" spans="1:21" ht="18" customHeight="1">
+    <row r="223" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A223" s="1"/>
       <c r="B223" s="27"/>
       <c r="C223" s="17"/>
@@ -6287,7 +6255,7 @@
       <c r="T223" s="11"/>
       <c r="U223" s="11"/>
     </row>
-    <row r="224" spans="1:21" ht="18" customHeight="1">
+    <row r="224" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A224" s="1"/>
       <c r="B224" s="27"/>
       <c r="C224" s="17"/>
@@ -6310,7 +6278,7 @@
       <c r="T224" s="11"/>
       <c r="U224" s="11"/>
     </row>
-    <row r="225" spans="1:21" ht="18" customHeight="1">
+    <row r="225" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A225" s="1"/>
       <c r="B225" s="27"/>
       <c r="C225" s="17"/>
@@ -6333,7 +6301,7 @@
       <c r="T225" s="11"/>
       <c r="U225" s="11"/>
     </row>
-    <row r="226" spans="1:21" ht="18" customHeight="1">
+    <row r="226" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A226" s="1"/>
       <c r="B226" s="27"/>
       <c r="C226" s="17"/>
@@ -6356,7 +6324,7 @@
       <c r="T226" s="11"/>
       <c r="U226" s="11"/>
     </row>
-    <row r="227" spans="1:21" ht="18" customHeight="1">
+    <row r="227" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A227" s="1"/>
       <c r="B227" s="27"/>
       <c r="C227" s="17"/>
@@ -6379,7 +6347,7 @@
       <c r="T227" s="11"/>
       <c r="U227" s="11"/>
     </row>
-    <row r="228" spans="1:21" ht="18" customHeight="1">
+    <row r="228" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A228" s="1"/>
       <c r="B228" s="27"/>
       <c r="C228" s="17"/>
@@ -6402,7 +6370,7 @@
       <c r="T228" s="11"/>
       <c r="U228" s="11"/>
     </row>
-    <row r="229" spans="1:21" ht="18" customHeight="1">
+    <row r="229" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A229" s="1"/>
       <c r="B229" s="27"/>
       <c r="C229" s="17"/>
@@ -6425,7 +6393,7 @@
       <c r="T229" s="11"/>
       <c r="U229" s="11"/>
     </row>
-    <row r="230" spans="1:21" ht="18" customHeight="1">
+    <row r="230" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A230" s="1"/>
       <c r="B230" s="27"/>
       <c r="C230" s="17"/>
@@ -6448,7 +6416,7 @@
       <c r="T230" s="11"/>
       <c r="U230" s="11"/>
     </row>
-    <row r="231" spans="1:21" ht="18" customHeight="1">
+    <row r="231" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A231" s="1"/>
       <c r="B231" s="27"/>
       <c r="C231" s="17"/>
@@ -6471,7 +6439,7 @@
       <c r="T231" s="11"/>
       <c r="U231" s="11"/>
     </row>
-    <row r="232" spans="1:21" ht="18" customHeight="1">
+    <row r="232" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A232" s="1"/>
       <c r="B232" s="27"/>
       <c r="C232" s="17"/>
@@ -6494,7 +6462,7 @@
       <c r="T232" s="11"/>
       <c r="U232" s="11"/>
     </row>
-    <row r="233" spans="1:21" ht="18" customHeight="1">
+    <row r="233" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A233" s="1"/>
       <c r="B233" s="27"/>
       <c r="C233" s="17"/>
@@ -6517,7 +6485,7 @@
       <c r="T233" s="11"/>
       <c r="U233" s="11"/>
     </row>
-    <row r="234" spans="1:21" ht="18" customHeight="1">
+    <row r="234" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A234" s="1"/>
       <c r="B234" s="27"/>
       <c r="C234" s="17"/>
@@ -6540,7 +6508,7 @@
       <c r="T234" s="11"/>
       <c r="U234" s="11"/>
     </row>
-    <row r="235" spans="1:21" ht="18" customHeight="1">
+    <row r="235" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A235" s="1"/>
       <c r="B235" s="27"/>
       <c r="C235" s="17"/>
@@ -6563,7 +6531,7 @@
       <c r="T235" s="11"/>
       <c r="U235" s="11"/>
     </row>
-    <row r="236" spans="1:21" ht="18" customHeight="1">
+    <row r="236" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A236" s="1"/>
       <c r="B236" s="27"/>
       <c r="C236" s="17"/>
@@ -6586,7 +6554,7 @@
       <c r="T236" s="11"/>
       <c r="U236" s="11"/>
     </row>
-    <row r="237" spans="1:21" ht="18" customHeight="1">
+    <row r="237" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A237" s="1"/>
       <c r="B237" s="27"/>
       <c r="C237" s="17"/>
@@ -6609,7 +6577,7 @@
       <c r="T237" s="11"/>
       <c r="U237" s="11"/>
     </row>
-    <row r="238" spans="1:21" ht="18" customHeight="1">
+    <row r="238" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A238" s="1"/>
       <c r="B238" s="27"/>
       <c r="C238" s="17"/>
@@ -6632,7 +6600,7 @@
       <c r="T238" s="11"/>
       <c r="U238" s="11"/>
     </row>
-    <row r="239" spans="1:21" ht="18" customHeight="1">
+    <row r="239" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A239" s="1"/>
       <c r="B239" s="27"/>
       <c r="C239" s="17"/>
@@ -6655,7 +6623,7 @@
       <c r="T239" s="11"/>
       <c r="U239" s="11"/>
     </row>
-    <row r="240" spans="1:21" ht="18" customHeight="1">
+    <row r="240" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A240" s="1"/>
       <c r="B240" s="27"/>
       <c r="C240" s="17"/>
@@ -6678,7 +6646,7 @@
       <c r="T240" s="11"/>
       <c r="U240" s="11"/>
     </row>
-    <row r="241" spans="1:21" ht="18" customHeight="1">
+    <row r="241" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A241" s="1"/>
       <c r="B241" s="27"/>
       <c r="C241" s="17"/>
@@ -6701,7 +6669,7 @@
       <c r="T241" s="11"/>
       <c r="U241" s="11"/>
     </row>
-    <row r="242" spans="1:21" ht="18" customHeight="1">
+    <row r="242" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A242" s="1"/>
       <c r="B242" s="27"/>
       <c r="C242" s="17"/>
@@ -6724,7 +6692,7 @@
       <c r="T242" s="11"/>
       <c r="U242" s="11"/>
     </row>
-    <row r="243" spans="1:21" ht="18" customHeight="1">
+    <row r="243" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A243" s="1"/>
       <c r="B243" s="27"/>
       <c r="C243" s="17"/>
@@ -6747,7 +6715,7 @@
       <c r="T243" s="11"/>
       <c r="U243" s="11"/>
     </row>
-    <row r="244" spans="1:21" ht="18" customHeight="1">
+    <row r="244" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A244" s="1"/>
       <c r="B244" s="27"/>
       <c r="C244" s="17"/>
@@ -6770,7 +6738,7 @@
       <c r="T244" s="11"/>
       <c r="U244" s="11"/>
     </row>
-    <row r="245" spans="1:21" ht="18" customHeight="1">
+    <row r="245" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A245" s="1"/>
       <c r="B245" s="27"/>
       <c r="C245" s="17"/>
@@ -6793,7 +6761,7 @@
       <c r="T245" s="11"/>
       <c r="U245" s="11"/>
     </row>
-    <row r="246" spans="1:21" ht="18" customHeight="1">
+    <row r="246" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A246" s="1"/>
       <c r="B246" s="27"/>
       <c r="C246" s="17"/>
@@ -6816,7 +6784,7 @@
       <c r="T246" s="11"/>
       <c r="U246" s="11"/>
     </row>
-    <row r="247" spans="1:21" ht="18" customHeight="1">
+    <row r="247" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A247" s="1"/>
       <c r="B247" s="27"/>
       <c r="C247" s="17"/>
@@ -6839,7 +6807,7 @@
       <c r="T247" s="11"/>
       <c r="U247" s="11"/>
     </row>
-    <row r="248" spans="1:21" ht="18" customHeight="1">
+    <row r="248" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A248" s="1"/>
       <c r="B248" s="27"/>
       <c r="C248" s="17"/>
@@ -6862,7 +6830,7 @@
       <c r="T248" s="11"/>
       <c r="U248" s="11"/>
     </row>
-    <row r="249" spans="1:21" ht="18" customHeight="1">
+    <row r="249" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A249" s="1"/>
       <c r="B249" s="27"/>
       <c r="C249" s="17"/>
@@ -6885,7 +6853,7 @@
       <c r="T249" s="11"/>
       <c r="U249" s="11"/>
     </row>
-    <row r="250" spans="1:21" ht="18" customHeight="1">
+    <row r="250" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A250" s="1"/>
       <c r="B250" s="27"/>
       <c r="C250" s="17"/>
@@ -6908,7 +6876,7 @@
       <c r="T250" s="11"/>
       <c r="U250" s="11"/>
     </row>
-    <row r="251" spans="1:21" ht="18" customHeight="1">
+    <row r="251" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A251" s="1"/>
       <c r="B251" s="27"/>
       <c r="C251" s="17"/>
@@ -6931,7 +6899,7 @@
       <c r="T251" s="11"/>
       <c r="U251" s="11"/>
     </row>
-    <row r="252" spans="1:21" ht="18" customHeight="1">
+    <row r="252" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A252" s="1"/>
       <c r="B252" s="27"/>
       <c r="C252" s="17"/>
@@ -6954,7 +6922,7 @@
       <c r="T252" s="11"/>
       <c r="U252" s="11"/>
     </row>
-    <row r="253" spans="1:21" ht="18" customHeight="1">
+    <row r="253" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A253" s="1"/>
       <c r="B253" s="27"/>
       <c r="C253" s="17"/>
@@ -6977,7 +6945,7 @@
       <c r="T253" s="11"/>
       <c r="U253" s="11"/>
     </row>
-    <row r="254" spans="1:21" ht="18" customHeight="1">
+    <row r="254" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A254" s="1"/>
       <c r="B254" s="27"/>
       <c r="C254" s="17"/>
@@ -7000,7 +6968,7 @@
       <c r="T254" s="11"/>
       <c r="U254" s="11"/>
     </row>
-    <row r="255" spans="1:21" ht="18" customHeight="1">
+    <row r="255" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A255" s="1"/>
       <c r="B255" s="27"/>
       <c r="C255" s="17"/>
@@ -7023,7 +6991,7 @@
       <c r="T255" s="11"/>
       <c r="U255" s="11"/>
     </row>
-    <row r="256" spans="1:21" ht="18" customHeight="1">
+    <row r="256" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A256" s="1"/>
       <c r="B256" s="27"/>
       <c r="C256" s="17"/>
@@ -7046,7 +7014,7 @@
       <c r="T256" s="11"/>
       <c r="U256" s="11"/>
     </row>
-    <row r="257" spans="1:21" ht="18" customHeight="1">
+    <row r="257" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A257" s="1"/>
       <c r="B257" s="27"/>
       <c r="C257" s="17"/>
@@ -7069,7 +7037,7 @@
       <c r="T257" s="11"/>
       <c r="U257" s="11"/>
     </row>
-    <row r="258" spans="1:21" ht="18" customHeight="1">
+    <row r="258" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A258" s="1"/>
       <c r="B258" s="27"/>
       <c r="C258" s="17"/>
@@ -7092,7 +7060,7 @@
       <c r="T258" s="11"/>
       <c r="U258" s="11"/>
     </row>
-    <row r="259" spans="1:21" ht="18" customHeight="1">
+    <row r="259" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A259" s="1"/>
       <c r="B259" s="27"/>
       <c r="C259" s="17"/>
@@ -7115,7 +7083,7 @@
       <c r="T259" s="11"/>
       <c r="U259" s="11"/>
     </row>
-    <row r="260" spans="1:21" ht="18" customHeight="1">
+    <row r="260" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A260" s="1"/>
       <c r="B260" s="27"/>
       <c r="C260" s="17"/>
@@ -7138,7 +7106,7 @@
       <c r="T260" s="11"/>
       <c r="U260" s="11"/>
     </row>
-    <row r="261" spans="1:21" ht="18" customHeight="1">
+    <row r="261" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A261" s="1"/>
       <c r="B261" s="27"/>
       <c r="C261" s="17"/>
@@ -7161,7 +7129,7 @@
       <c r="T261" s="11"/>
       <c r="U261" s="11"/>
     </row>
-    <row r="262" spans="1:21" ht="18" customHeight="1">
+    <row r="262" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A262" s="1"/>
       <c r="B262" s="27"/>
       <c r="C262" s="17"/>
@@ -7184,7 +7152,7 @@
       <c r="T262" s="11"/>
       <c r="U262" s="11"/>
     </row>
-    <row r="263" spans="1:21" ht="18" customHeight="1">
+    <row r="263" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A263" s="1"/>
       <c r="B263" s="27"/>
       <c r="C263" s="17"/>
@@ -7207,7 +7175,7 @@
       <c r="T263" s="11"/>
       <c r="U263" s="11"/>
     </row>
-    <row r="264" spans="1:21" ht="18" customHeight="1">
+    <row r="264" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A264" s="1"/>
       <c r="B264" s="27"/>
       <c r="C264" s="17"/>
@@ -7230,7 +7198,7 @@
       <c r="T264" s="11"/>
       <c r="U264" s="11"/>
     </row>
-    <row r="265" spans="1:21" ht="18" customHeight="1">
+    <row r="265" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A265" s="1"/>
       <c r="B265" s="27"/>
       <c r="C265" s="17"/>
@@ -7253,7 +7221,7 @@
       <c r="T265" s="11"/>
       <c r="U265" s="11"/>
     </row>
-    <row r="266" spans="1:21" ht="18" customHeight="1">
+    <row r="266" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A266" s="1"/>
       <c r="B266" s="27"/>
       <c r="C266" s="17"/>
@@ -7276,7 +7244,7 @@
       <c r="T266" s="11"/>
       <c r="U266" s="11"/>
     </row>
-    <row r="267" spans="1:21" ht="18" customHeight="1">
+    <row r="267" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A267" s="1"/>
       <c r="B267" s="27"/>
       <c r="C267" s="17"/>
@@ -7299,7 +7267,7 @@
       <c r="T267" s="11"/>
       <c r="U267" s="11"/>
     </row>
-    <row r="268" spans="1:21" ht="18" customHeight="1">
+    <row r="268" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A268" s="1"/>
       <c r="B268" s="27"/>
       <c r="C268" s="17"/>
@@ -7322,7 +7290,7 @@
       <c r="T268" s="11"/>
       <c r="U268" s="11"/>
     </row>
-    <row r="269" spans="1:21" ht="18" customHeight="1">
+    <row r="269" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A269" s="1"/>
       <c r="B269" s="27"/>
       <c r="C269" s="17"/>
@@ -7345,7 +7313,7 @@
       <c r="T269" s="11"/>
       <c r="U269" s="11"/>
     </row>
-    <row r="270" spans="1:21" ht="18" customHeight="1">
+    <row r="270" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A270" s="1"/>
       <c r="B270" s="27"/>
       <c r="C270" s="17"/>
@@ -7368,7 +7336,7 @@
       <c r="T270" s="11"/>
       <c r="U270" s="11"/>
     </row>
-    <row r="271" spans="1:21" ht="18" customHeight="1">
+    <row r="271" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A271" s="1"/>
       <c r="B271" s="27"/>
       <c r="C271" s="17"/>
@@ -7391,7 +7359,7 @@
       <c r="T271" s="11"/>
       <c r="U271" s="11"/>
     </row>
-    <row r="272" spans="1:21" ht="18" customHeight="1">
+    <row r="272" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A272" s="1"/>
       <c r="B272" s="27"/>
       <c r="C272" s="17"/>
@@ -7414,7 +7382,7 @@
       <c r="T272" s="11"/>
       <c r="U272" s="11"/>
     </row>
-    <row r="273" spans="1:21" ht="18" customHeight="1">
+    <row r="273" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A273" s="1"/>
       <c r="B273" s="27"/>
       <c r="C273" s="17"/>
@@ -7437,7 +7405,7 @@
       <c r="T273" s="11"/>
       <c r="U273" s="11"/>
     </row>
-    <row r="274" spans="1:21" ht="18" customHeight="1">
+    <row r="274" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A274" s="1"/>
       <c r="B274" s="27"/>
       <c r="C274" s="17"/>
@@ -7460,7 +7428,7 @@
       <c r="T274" s="11"/>
       <c r="U274" s="11"/>
     </row>
-    <row r="275" spans="1:21" ht="18" customHeight="1">
+    <row r="275" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A275" s="1"/>
       <c r="B275" s="27"/>
       <c r="C275" s="17"/>
@@ -7483,7 +7451,7 @@
       <c r="T275" s="11"/>
       <c r="U275" s="11"/>
     </row>
-    <row r="276" spans="1:21" ht="18" customHeight="1">
+    <row r="276" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A276" s="1"/>
       <c r="B276" s="27"/>
       <c r="C276" s="17"/>
@@ -7506,7 +7474,7 @@
       <c r="T276" s="11"/>
       <c r="U276" s="11"/>
     </row>
-    <row r="277" spans="1:21" ht="18" customHeight="1">
+    <row r="277" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A277" s="1"/>
       <c r="B277" s="27"/>
       <c r="C277" s="17"/>
@@ -7529,7 +7497,7 @@
       <c r="T277" s="11"/>
       <c r="U277" s="11"/>
     </row>
-    <row r="278" spans="1:21" ht="18" customHeight="1">
+    <row r="278" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A278" s="1"/>
       <c r="B278" s="27"/>
       <c r="C278" s="17"/>
@@ -7552,7 +7520,7 @@
       <c r="T278" s="11"/>
       <c r="U278" s="11"/>
     </row>
-    <row r="279" spans="1:21" ht="18" customHeight="1">
+    <row r="279" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A279" s="1"/>
       <c r="B279" s="27"/>
       <c r="C279" s="17"/>
@@ -7575,7 +7543,7 @@
       <c r="T279" s="11"/>
       <c r="U279" s="11"/>
     </row>
-    <row r="280" spans="1:21" ht="18" customHeight="1">
+    <row r="280" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A280" s="1"/>
       <c r="B280" s="27"/>
       <c r="C280" s="17"/>
@@ -7598,7 +7566,7 @@
       <c r="T280" s="11"/>
       <c r="U280" s="11"/>
     </row>
-    <row r="281" spans="1:21" ht="18" customHeight="1">
+    <row r="281" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A281" s="1"/>
       <c r="B281" s="27"/>
       <c r="C281" s="17"/>
@@ -7621,7 +7589,7 @@
       <c r="T281" s="11"/>
       <c r="U281" s="11"/>
     </row>
-    <row r="282" spans="1:21" ht="18" customHeight="1">
+    <row r="282" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A282" s="1"/>
       <c r="B282" s="27"/>
       <c r="C282" s="17"/>
@@ -7644,7 +7612,7 @@
       <c r="T282" s="11"/>
       <c r="U282" s="11"/>
     </row>
-    <row r="283" spans="1:21" ht="18" customHeight="1">
+    <row r="283" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A283" s="1"/>
       <c r="B283" s="27"/>
       <c r="C283" s="17"/>
@@ -7667,7 +7635,7 @@
       <c r="T283" s="11"/>
       <c r="U283" s="11"/>
     </row>
-    <row r="284" spans="1:21" ht="18" customHeight="1">
+    <row r="284" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A284" s="1"/>
       <c r="B284" s="27"/>
       <c r="C284" s="17"/>
@@ -7690,7 +7658,7 @@
       <c r="T284" s="11"/>
       <c r="U284" s="11"/>
     </row>
-    <row r="285" spans="1:21" ht="18" customHeight="1">
+    <row r="285" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A285" s="1"/>
       <c r="B285" s="27"/>
       <c r="C285" s="17"/>
@@ -7713,7 +7681,7 @@
       <c r="T285" s="11"/>
       <c r="U285" s="11"/>
     </row>
-    <row r="286" spans="1:21" ht="18" customHeight="1">
+    <row r="286" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A286" s="1"/>
       <c r="B286" s="27"/>
       <c r="C286" s="17"/>
@@ -7736,7 +7704,7 @@
       <c r="T286" s="11"/>
       <c r="U286" s="11"/>
     </row>
-    <row r="287" spans="1:21" ht="18" customHeight="1">
+    <row r="287" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A287" s="1"/>
       <c r="B287" s="27"/>
       <c r="C287" s="17"/>
@@ -7759,7 +7727,7 @@
       <c r="T287" s="11"/>
       <c r="U287" s="11"/>
     </row>
-    <row r="288" spans="1:21" ht="18" customHeight="1">
+    <row r="288" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A288" s="1"/>
       <c r="B288" s="27"/>
       <c r="C288" s="17"/>
@@ -7782,7 +7750,7 @@
       <c r="T288" s="11"/>
       <c r="U288" s="11"/>
     </row>
-    <row r="289" spans="1:21" ht="18" customHeight="1">
+    <row r="289" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A289" s="1"/>
       <c r="B289" s="27"/>
       <c r="C289" s="17"/>
@@ -7805,7 +7773,7 @@
       <c r="T289" s="11"/>
       <c r="U289" s="11"/>
     </row>
-    <row r="290" spans="1:21" ht="18" customHeight="1">
+    <row r="290" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A290" s="1"/>
       <c r="B290" s="27"/>
       <c r="C290" s="17"/>
@@ -7828,7 +7796,7 @@
       <c r="T290" s="11"/>
       <c r="U290" s="11"/>
     </row>
-    <row r="291" spans="1:21" ht="18" customHeight="1">
+    <row r="291" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A291" s="1"/>
       <c r="B291" s="27"/>
       <c r="C291" s="17"/>
@@ -7851,7 +7819,7 @@
       <c r="T291" s="11"/>
       <c r="U291" s="11"/>
     </row>
-    <row r="292" spans="1:21" ht="18" customHeight="1">
+    <row r="292" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A292" s="1"/>
       <c r="B292" s="27"/>
       <c r="C292" s="17"/>
@@ -7874,7 +7842,7 @@
       <c r="T292" s="11"/>
       <c r="U292" s="11"/>
     </row>
-    <row r="293" spans="1:21" ht="18" customHeight="1">
+    <row r="293" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A293" s="1"/>
       <c r="B293" s="27"/>
       <c r="C293" s="17"/>
@@ -7897,7 +7865,7 @@
       <c r="T293" s="11"/>
       <c r="U293" s="11"/>
     </row>
-    <row r="294" spans="1:21" ht="18" customHeight="1">
+    <row r="294" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A294" s="1"/>
       <c r="B294" s="27"/>
       <c r="C294" s="17"/>
@@ -7920,7 +7888,7 @@
       <c r="T294" s="11"/>
       <c r="U294" s="11"/>
     </row>
-    <row r="295" spans="1:21" ht="18" customHeight="1">
+    <row r="295" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A295" s="1"/>
       <c r="B295" s="27"/>
       <c r="C295" s="17"/>
@@ -7943,7 +7911,7 @@
       <c r="T295" s="11"/>
       <c r="U295" s="11"/>
     </row>
-    <row r="296" spans="1:21" ht="18" customHeight="1">
+    <row r="296" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A296" s="1"/>
       <c r="B296" s="27"/>
       <c r="C296" s="17"/>
@@ -7966,7 +7934,7 @@
       <c r="T296" s="11"/>
       <c r="U296" s="11"/>
     </row>
-    <row r="297" spans="1:21" ht="18" customHeight="1">
+    <row r="297" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A297" s="1"/>
       <c r="B297" s="27"/>
       <c r="C297" s="17"/>
@@ -7989,7 +7957,7 @@
       <c r="T297" s="11"/>
       <c r="U297" s="11"/>
     </row>
-    <row r="298" spans="1:21" ht="18" customHeight="1">
+    <row r="298" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A298" s="1"/>
       <c r="B298" s="27"/>
       <c r="C298" s="17"/>
@@ -8012,7 +7980,7 @@
       <c r="T298" s="11"/>
       <c r="U298" s="11"/>
     </row>
-    <row r="299" spans="1:21" ht="18" customHeight="1">
+    <row r="299" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A299" s="1"/>
       <c r="B299" s="27"/>
       <c r="C299" s="17"/>
@@ -8035,7 +8003,7 @@
       <c r="T299" s="11"/>
       <c r="U299" s="11"/>
     </row>
-    <row r="300" spans="1:21" ht="18" customHeight="1">
+    <row r="300" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A300" s="1"/>
       <c r="B300" s="27"/>
       <c r="C300" s="17"/>
@@ -8058,7 +8026,7 @@
       <c r="T300" s="11"/>
       <c r="U300" s="11"/>
     </row>
-    <row r="301" spans="1:21" ht="18" customHeight="1">
+    <row r="301" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A301" s="1"/>
       <c r="B301" s="27"/>
       <c r="C301" s="17"/>
@@ -8081,7 +8049,7 @@
       <c r="T301" s="11"/>
       <c r="U301" s="11"/>
     </row>
-    <row r="302" spans="1:21" ht="18" customHeight="1">
+    <row r="302" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A302" s="1"/>
       <c r="B302" s="27"/>
       <c r="C302" s="17"/>
@@ -8104,7 +8072,7 @@
       <c r="T302" s="11"/>
       <c r="U302" s="11"/>
     </row>
-    <row r="303" spans="1:21" ht="18" customHeight="1">
+    <row r="303" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A303" s="1"/>
       <c r="B303" s="27"/>
       <c r="C303" s="17"/>
@@ -8127,7 +8095,7 @@
       <c r="T303" s="11"/>
       <c r="U303" s="11"/>
     </row>
-    <row r="304" spans="1:21" ht="18" customHeight="1">
+    <row r="304" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A304" s="1"/>
       <c r="B304" s="27"/>
       <c r="C304" s="17"/>
@@ -8150,7 +8118,7 @@
       <c r="T304" s="11"/>
       <c r="U304" s="11"/>
     </row>
-    <row r="305" spans="1:21" ht="18" customHeight="1">
+    <row r="305" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A305" s="1"/>
       <c r="B305" s="27"/>
       <c r="C305" s="17"/>
@@ -8173,7 +8141,7 @@
       <c r="T305" s="11"/>
       <c r="U305" s="11"/>
     </row>
-    <row r="306" spans="1:21" ht="18" customHeight="1">
+    <row r="306" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A306" s="1"/>
       <c r="B306" s="27"/>
       <c r="C306" s="17"/>
@@ -8196,7 +8164,7 @@
       <c r="T306" s="11"/>
       <c r="U306" s="11"/>
     </row>
-    <row r="307" spans="1:21" ht="18" customHeight="1">
+    <row r="307" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A307" s="1"/>
       <c r="B307" s="27"/>
       <c r="C307" s="17"/>
@@ -8219,7 +8187,7 @@
       <c r="T307" s="11"/>
       <c r="U307" s="11"/>
     </row>
-    <row r="308" spans="1:21" ht="18" customHeight="1">
+    <row r="308" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A308" s="1"/>
       <c r="B308" s="27"/>
       <c r="C308" s="17"/>
@@ -8242,7 +8210,7 @@
       <c r="T308" s="11"/>
       <c r="U308" s="11"/>
     </row>
-    <row r="309" spans="1:21" ht="18" customHeight="1">
+    <row r="309" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A309" s="1"/>
       <c r="B309" s="27"/>
       <c r="C309" s="17"/>
@@ -8265,7 +8233,7 @@
       <c r="T309" s="11"/>
       <c r="U309" s="11"/>
     </row>
-    <row r="310" spans="1:21" ht="18" customHeight="1">
+    <row r="310" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A310" s="1"/>
       <c r="B310" s="27"/>
       <c r="C310" s="17"/>
@@ -8288,7 +8256,7 @@
       <c r="T310" s="11"/>
       <c r="U310" s="11"/>
     </row>
-    <row r="311" spans="1:21" ht="18" customHeight="1">
+    <row r="311" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A311" s="1"/>
       <c r="B311" s="27"/>
       <c r="C311" s="17"/>
@@ -8311,7 +8279,7 @@
       <c r="T311" s="11"/>
       <c r="U311" s="11"/>
     </row>
-    <row r="312" spans="1:21" ht="18" customHeight="1">
+    <row r="312" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A312" s="1"/>
       <c r="B312" s="27"/>
       <c r="C312" s="17"/>
@@ -8334,7 +8302,7 @@
       <c r="T312" s="11"/>
       <c r="U312" s="11"/>
     </row>
-    <row r="313" spans="1:21" ht="18" customHeight="1">
+    <row r="313" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A313" s="1"/>
       <c r="B313" s="27"/>
       <c r="C313" s="17"/>
@@ -8357,7 +8325,7 @@
       <c r="T313" s="11"/>
       <c r="U313" s="11"/>
     </row>
-    <row r="314" spans="1:21" ht="18" customHeight="1">
+    <row r="314" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A314" s="1"/>
       <c r="B314" s="27"/>
       <c r="C314" s="17"/>
@@ -8380,7 +8348,7 @@
       <c r="T314" s="11"/>
       <c r="U314" s="11"/>
     </row>
-    <row r="315" spans="1:21" ht="18" customHeight="1">
+    <row r="315" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A315" s="1"/>
       <c r="B315" s="27"/>
       <c r="C315" s="17"/>
@@ -8403,7 +8371,7 @@
       <c r="T315" s="11"/>
       <c r="U315" s="11"/>
     </row>
-    <row r="316" spans="1:21" ht="18" customHeight="1">
+    <row r="316" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A316" s="1"/>
       <c r="B316" s="27"/>
       <c r="C316" s="17"/>
@@ -8426,7 +8394,7 @@
       <c r="T316" s="11"/>
       <c r="U316" s="11"/>
     </row>
-    <row r="317" spans="1:21" ht="18" customHeight="1">
+    <row r="317" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A317" s="1"/>
       <c r="B317" s="27"/>
       <c r="C317" s="17"/>
@@ -8449,7 +8417,7 @@
       <c r="T317" s="11"/>
       <c r="U317" s="11"/>
     </row>
-    <row r="318" spans="1:21" ht="18" customHeight="1">
+    <row r="318" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A318" s="1"/>
       <c r="B318" s="27"/>
       <c r="C318" s="17"/>
@@ -8472,7 +8440,7 @@
       <c r="T318" s="11"/>
       <c r="U318" s="11"/>
     </row>
-    <row r="319" spans="1:21" ht="18" customHeight="1">
+    <row r="319" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A319" s="1"/>
       <c r="B319" s="27"/>
       <c r="C319" s="17"/>
@@ -8495,7 +8463,7 @@
       <c r="T319" s="11"/>
       <c r="U319" s="11"/>
     </row>
-    <row r="320" spans="1:21" ht="18" customHeight="1">
+    <row r="320" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A320" s="1"/>
       <c r="B320" s="27"/>
       <c r="C320" s="17"/>
@@ -8518,7 +8486,7 @@
       <c r="T320" s="11"/>
       <c r="U320" s="11"/>
     </row>
-    <row r="321" spans="1:21" ht="18" customHeight="1">
+    <row r="321" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A321" s="1"/>
       <c r="B321" s="27"/>
       <c r="C321" s="17"/>
@@ -8541,7 +8509,7 @@
       <c r="T321" s="11"/>
       <c r="U321" s="11"/>
     </row>
-    <row r="322" spans="1:21" ht="18" customHeight="1">
+    <row r="322" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A322" s="1"/>
       <c r="B322" s="27"/>
       <c r="C322" s="17"/>
@@ -8564,7 +8532,7 @@
       <c r="T322" s="11"/>
       <c r="U322" s="11"/>
     </row>
-    <row r="323" spans="1:21" ht="18" customHeight="1">
+    <row r="323" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A323" s="1"/>
       <c r="B323" s="27"/>
       <c r="C323" s="17"/>
@@ -8587,7 +8555,7 @@
       <c r="T323" s="11"/>
       <c r="U323" s="11"/>
     </row>
-    <row r="324" spans="1:21" ht="18" customHeight="1">
+    <row r="324" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A324" s="1"/>
       <c r="B324" s="27"/>
       <c r="C324" s="17"/>
@@ -8610,7 +8578,7 @@
       <c r="T324" s="11"/>
       <c r="U324" s="11"/>
     </row>
-    <row r="325" spans="1:21" ht="18" customHeight="1">
+    <row r="325" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A325" s="1"/>
       <c r="B325" s="27"/>
       <c r="C325" s="17"/>
@@ -8633,7 +8601,7 @@
       <c r="T325" s="11"/>
       <c r="U325" s="11"/>
     </row>
-    <row r="326" spans="1:21" ht="18" customHeight="1">
+    <row r="326" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A326" s="1"/>
       <c r="B326" s="27"/>
       <c r="C326" s="17"/>
@@ -8656,7 +8624,7 @@
       <c r="T326" s="11"/>
       <c r="U326" s="11"/>
     </row>
-    <row r="327" spans="1:21" ht="18" customHeight="1">
+    <row r="327" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A327" s="1"/>
       <c r="B327" s="27"/>
       <c r="C327" s="17"/>
@@ -8679,7 +8647,7 @@
       <c r="T327" s="11"/>
       <c r="U327" s="11"/>
     </row>
-    <row r="328" spans="1:21" ht="18" customHeight="1">
+    <row r="328" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A328" s="1"/>
       <c r="B328" s="27"/>
       <c r="C328" s="17"/>
@@ -8702,7 +8670,7 @@
       <c r="T328" s="11"/>
       <c r="U328" s="11"/>
     </row>
-    <row r="329" spans="1:21" ht="18" customHeight="1">
+    <row r="329" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A329" s="1"/>
       <c r="B329" s="27"/>
       <c r="C329" s="17"/>
@@ -8725,7 +8693,7 @@
       <c r="T329" s="11"/>
       <c r="U329" s="11"/>
     </row>
-    <row r="330" spans="1:21" ht="18" customHeight="1">
+    <row r="330" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A330" s="1"/>
       <c r="B330" s="27"/>
       <c r="C330" s="17"/>
@@ -8748,7 +8716,7 @@
       <c r="T330" s="11"/>
       <c r="U330" s="11"/>
     </row>
-    <row r="331" spans="1:21" ht="18" customHeight="1">
+    <row r="331" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A331" s="1"/>
       <c r="B331" s="27"/>
       <c r="C331" s="17"/>
@@ -8771,7 +8739,7 @@
       <c r="T331" s="11"/>
       <c r="U331" s="11"/>
     </row>
-    <row r="332" spans="1:21" ht="18" customHeight="1">
+    <row r="332" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A332" s="1"/>
       <c r="B332" s="27"/>
       <c r="C332" s="17"/>
@@ -8794,7 +8762,7 @@
       <c r="T332" s="11"/>
       <c r="U332" s="11"/>
     </row>
-    <row r="333" spans="1:21" ht="18" customHeight="1">
+    <row r="333" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A333" s="1"/>
       <c r="B333" s="27"/>
       <c r="C333" s="17"/>
@@ -8817,7 +8785,7 @@
       <c r="T333" s="11"/>
       <c r="U333" s="11"/>
     </row>
-    <row r="334" spans="1:21" ht="18" customHeight="1">
+    <row r="334" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A334" s="1"/>
       <c r="B334" s="27"/>
       <c r="C334" s="17"/>
@@ -8840,7 +8808,7 @@
       <c r="T334" s="11"/>
       <c r="U334" s="11"/>
     </row>
-    <row r="335" spans="1:21" ht="18" customHeight="1">
+    <row r="335" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A335" s="1"/>
       <c r="B335" s="27"/>
       <c r="C335" s="17"/>
@@ -8863,7 +8831,7 @@
       <c r="T335" s="11"/>
       <c r="U335" s="11"/>
     </row>
-    <row r="336" spans="1:21" ht="18" customHeight="1">
+    <row r="336" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A336" s="1"/>
       <c r="B336" s="27"/>
       <c r="C336" s="17"/>
@@ -8886,7 +8854,7 @@
       <c r="T336" s="11"/>
       <c r="U336" s="11"/>
     </row>
-    <row r="337" spans="1:21" ht="18" customHeight="1">
+    <row r="337" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A337" s="1"/>
       <c r="B337" s="27"/>
       <c r="C337" s="17"/>
@@ -8909,7 +8877,7 @@
       <c r="T337" s="11"/>
       <c r="U337" s="11"/>
     </row>
-    <row r="338" spans="1:21" ht="18" customHeight="1">
+    <row r="338" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A338" s="1"/>
       <c r="B338" s="27"/>
       <c r="C338" s="17"/>
@@ -8932,7 +8900,7 @@
       <c r="T338" s="11"/>
       <c r="U338" s="11"/>
     </row>
-    <row r="339" spans="1:21" ht="18" customHeight="1">
+    <row r="339" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A339" s="1"/>
       <c r="B339" s="27"/>
       <c r="C339" s="17"/>
@@ -8955,7 +8923,7 @@
       <c r="T339" s="11"/>
       <c r="U339" s="11"/>
     </row>
-    <row r="340" spans="1:21" ht="18" customHeight="1">
+    <row r="340" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A340" s="1"/>
       <c r="B340" s="27"/>
       <c r="C340" s="17"/>
@@ -8978,7 +8946,7 @@
       <c r="T340" s="11"/>
       <c r="U340" s="11"/>
     </row>
-    <row r="341" spans="1:21" ht="18" customHeight="1">
+    <row r="341" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A341" s="1"/>
       <c r="B341" s="27"/>
       <c r="C341" s="17"/>
@@ -9001,7 +8969,7 @@
       <c r="T341" s="11"/>
       <c r="U341" s="11"/>
     </row>
-    <row r="342" spans="1:21" ht="18" customHeight="1">
+    <row r="342" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A342" s="1"/>
       <c r="B342" s="27"/>
       <c r="C342" s="17"/>
@@ -9024,7 +8992,7 @@
       <c r="T342" s="11"/>
       <c r="U342" s="11"/>
     </row>
-    <row r="343" spans="1:21" ht="18" customHeight="1">
+    <row r="343" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A343" s="1"/>
       <c r="B343" s="27"/>
       <c r="C343" s="17"/>
@@ -9047,7 +9015,7 @@
       <c r="T343" s="11"/>
       <c r="U343" s="11"/>
     </row>
-    <row r="344" spans="1:21" ht="18" customHeight="1">
+    <row r="344" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A344" s="1"/>
       <c r="B344" s="27"/>
       <c r="C344" s="17"/>
@@ -9070,7 +9038,7 @@
       <c r="T344" s="11"/>
       <c r="U344" s="11"/>
     </row>
-    <row r="345" spans="1:21" ht="18" customHeight="1">
+    <row r="345" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A345" s="1"/>
       <c r="B345" s="27"/>
       <c r="C345" s="17"/>
@@ -9093,7 +9061,7 @@
       <c r="T345" s="11"/>
       <c r="U345" s="11"/>
     </row>
-    <row r="346" spans="1:21" ht="18" customHeight="1">
+    <row r="346" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A346" s="1"/>
       <c r="B346" s="27"/>
       <c r="C346" s="17"/>
@@ -9116,7 +9084,7 @@
       <c r="T346" s="11"/>
       <c r="U346" s="11"/>
     </row>
-    <row r="347" spans="1:21" ht="18" customHeight="1">
+    <row r="347" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A347" s="1"/>
       <c r="B347" s="27"/>
       <c r="C347" s="17"/>
@@ -9139,7 +9107,7 @@
       <c r="T347" s="11"/>
       <c r="U347" s="11"/>
     </row>
-    <row r="348" spans="1:21" ht="18" customHeight="1">
+    <row r="348" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A348" s="1"/>
       <c r="B348" s="27"/>
       <c r="C348" s="17"/>
@@ -9162,7 +9130,7 @@
       <c r="T348" s="11"/>
       <c r="U348" s="11"/>
     </row>
-    <row r="349" spans="1:21" ht="18" customHeight="1">
+    <row r="349" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A349" s="1"/>
       <c r="B349" s="27"/>
       <c r="C349" s="17"/>
@@ -9185,7 +9153,7 @@
       <c r="T349" s="11"/>
       <c r="U349" s="11"/>
     </row>
-    <row r="350" spans="1:21" ht="18" customHeight="1">
+    <row r="350" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A350" s="1"/>
       <c r="B350" s="27"/>
       <c r="C350" s="17"/>
@@ -9208,7 +9176,7 @@
       <c r="T350" s="11"/>
       <c r="U350" s="11"/>
     </row>
-    <row r="351" spans="1:21" ht="18" customHeight="1">
+    <row r="351" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A351" s="1"/>
       <c r="B351" s="27"/>
       <c r="C351" s="17"/>
@@ -9231,7 +9199,7 @@
       <c r="T351" s="11"/>
       <c r="U351" s="11"/>
     </row>
-    <row r="352" spans="1:21" ht="18" customHeight="1">
+    <row r="352" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A352" s="1"/>
       <c r="B352" s="27"/>
       <c r="C352" s="17"/>
@@ -9254,7 +9222,7 @@
       <c r="T352" s="11"/>
       <c r="U352" s="11"/>
     </row>
-    <row r="353" spans="1:21" ht="18" customHeight="1">
+    <row r="353" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A353" s="1"/>
       <c r="B353" s="27"/>
       <c r="C353" s="17"/>
@@ -9277,7 +9245,7 @@
       <c r="T353" s="11"/>
       <c r="U353" s="11"/>
     </row>
-    <row r="354" spans="1:21" ht="18" customHeight="1">
+    <row r="354" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A354" s="1"/>
       <c r="B354" s="27"/>
       <c r="C354" s="17"/>
@@ -9300,7 +9268,7 @@
       <c r="T354" s="11"/>
       <c r="U354" s="11"/>
     </row>
-    <row r="355" spans="1:21" ht="18" customHeight="1">
+    <row r="355" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A355" s="1"/>
       <c r="B355" s="27"/>
       <c r="C355" s="17"/>
@@ -9323,7 +9291,7 @@
       <c r="T355" s="11"/>
       <c r="U355" s="11"/>
     </row>
-    <row r="356" spans="1:21" ht="18" customHeight="1">
+    <row r="356" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A356" s="1"/>
       <c r="B356" s="27"/>
       <c r="C356" s="17"/>
@@ -9346,7 +9314,7 @@
       <c r="T356" s="11"/>
       <c r="U356" s="11"/>
     </row>
-    <row r="357" spans="1:21" ht="18" customHeight="1">
+    <row r="357" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A357" s="1"/>
       <c r="B357" s="27"/>
       <c r="C357" s="17"/>
@@ -9369,7 +9337,7 @@
       <c r="T357" s="11"/>
       <c r="U357" s="11"/>
     </row>
-    <row r="358" spans="1:21" ht="18" customHeight="1">
+    <row r="358" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A358" s="1"/>
       <c r="B358" s="27"/>
       <c r="C358" s="17"/>
@@ -9392,7 +9360,7 @@
       <c r="T358" s="11"/>
       <c r="U358" s="11"/>
     </row>
-    <row r="359" spans="1:21" ht="18" customHeight="1">
+    <row r="359" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A359" s="1"/>
       <c r="B359" s="27"/>
       <c r="C359" s="17"/>
@@ -9415,7 +9383,7 @@
       <c r="T359" s="11"/>
       <c r="U359" s="11"/>
     </row>
-    <row r="360" spans="1:21" ht="18" customHeight="1">
+    <row r="360" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A360" s="1"/>
       <c r="B360" s="27"/>
       <c r="C360" s="17"/>
@@ -9438,7 +9406,7 @@
       <c r="T360" s="11"/>
       <c r="U360" s="11"/>
     </row>
-    <row r="361" spans="1:21" ht="18" customHeight="1">
+    <row r="361" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A361" s="1"/>
       <c r="B361" s="27"/>
       <c r="C361" s="17"/>
@@ -9461,7 +9429,7 @@
       <c r="T361" s="11"/>
       <c r="U361" s="11"/>
     </row>
-    <row r="362" spans="1:21" ht="18" customHeight="1">
+    <row r="362" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A362" s="1"/>
       <c r="B362" s="27"/>
       <c r="C362" s="17"/>
@@ -9484,7 +9452,7 @@
       <c r="T362" s="11"/>
       <c r="U362" s="11"/>
     </row>
-    <row r="363" spans="1:21" ht="18" customHeight="1">
+    <row r="363" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A363" s="1"/>
       <c r="B363" s="27"/>
       <c r="C363" s="17"/>
@@ -9507,7 +9475,7 @@
       <c r="T363" s="11"/>
       <c r="U363" s="11"/>
     </row>
-    <row r="364" spans="1:21" ht="18" customHeight="1">
+    <row r="364" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A364" s="1"/>
       <c r="B364" s="27"/>
       <c r="C364" s="17"/>
@@ -9530,7 +9498,7 @@
       <c r="T364" s="11"/>
       <c r="U364" s="11"/>
     </row>
-    <row r="365" spans="1:21" ht="18" customHeight="1">
+    <row r="365" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A365" s="1"/>
       <c r="B365" s="27"/>
       <c r="C365" s="17"/>
@@ -9553,7 +9521,7 @@
       <c r="T365" s="11"/>
       <c r="U365" s="11"/>
     </row>
-    <row r="366" spans="1:21" ht="18" customHeight="1">
+    <row r="366" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A366" s="1"/>
       <c r="B366" s="27"/>
       <c r="C366" s="17"/>
@@ -9576,7 +9544,7 @@
       <c r="T366" s="11"/>
       <c r="U366" s="11"/>
     </row>
-    <row r="367" spans="1:21" ht="18" customHeight="1">
+    <row r="367" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A367" s="1"/>
       <c r="B367" s="27"/>
       <c r="C367" s="17"/>
@@ -9599,7 +9567,7 @@
       <c r="T367" s="11"/>
       <c r="U367" s="11"/>
     </row>
-    <row r="368" spans="1:21" ht="18" customHeight="1">
+    <row r="368" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A368" s="1"/>
       <c r="B368" s="27"/>
       <c r="C368" s="17"/>
@@ -9622,7 +9590,7 @@
       <c r="T368" s="11"/>
       <c r="U368" s="11"/>
     </row>
-    <row r="369" spans="1:21" ht="18" customHeight="1">
+    <row r="369" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A369" s="1"/>
       <c r="B369" s="27"/>
       <c r="C369" s="17"/>
@@ -9645,7 +9613,7 @@
       <c r="T369" s="11"/>
       <c r="U369" s="11"/>
     </row>
-    <row r="370" spans="1:21" ht="18" customHeight="1">
+    <row r="370" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A370" s="1"/>
       <c r="B370" s="27"/>
       <c r="C370" s="17"/>
@@ -9668,7 +9636,7 @@
       <c r="T370" s="11"/>
       <c r="U370" s="11"/>
     </row>
-    <row r="371" spans="1:21" ht="18" customHeight="1">
+    <row r="371" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A371" s="1"/>
       <c r="B371" s="27"/>
       <c r="C371" s="17"/>
@@ -9691,7 +9659,7 @@
       <c r="T371" s="11"/>
       <c r="U371" s="11"/>
     </row>
-    <row r="372" spans="1:21" ht="18" customHeight="1">
+    <row r="372" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A372" s="1"/>
       <c r="B372" s="27"/>
       <c r="C372" s="17"/>
@@ -9714,7 +9682,7 @@
       <c r="T372" s="11"/>
       <c r="U372" s="11"/>
     </row>
-    <row r="373" spans="1:21" ht="18" customHeight="1">
+    <row r="373" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A373" s="1"/>
       <c r="B373" s="27"/>
       <c r="C373" s="17"/>
@@ -9737,7 +9705,7 @@
       <c r="T373" s="11"/>
       <c r="U373" s="11"/>
     </row>
-    <row r="374" spans="1:21" ht="18" customHeight="1">
+    <row r="374" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A374" s="1"/>
       <c r="B374" s="27"/>
       <c r="C374" s="17"/>
@@ -9760,7 +9728,7 @@
       <c r="T374" s="11"/>
       <c r="U374" s="11"/>
     </row>
-    <row r="375" spans="1:21" ht="18" customHeight="1">
+    <row r="375" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A375" s="1"/>
       <c r="B375" s="27"/>
       <c r="C375" s="17"/>
@@ -9783,7 +9751,7 @@
       <c r="T375" s="11"/>
       <c r="U375" s="11"/>
     </row>
-    <row r="376" spans="1:21" ht="18" customHeight="1">
+    <row r="376" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A376" s="1"/>
       <c r="B376" s="27"/>
       <c r="C376" s="17"/>
@@ -9806,7 +9774,7 @@
       <c r="T376" s="11"/>
       <c r="U376" s="11"/>
     </row>
-    <row r="377" spans="1:21" ht="18" customHeight="1">
+    <row r="377" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A377" s="1"/>
       <c r="B377" s="27"/>
       <c r="C377" s="17"/>
@@ -9829,7 +9797,7 @@
       <c r="T377" s="11"/>
       <c r="U377" s="11"/>
     </row>
-    <row r="378" spans="1:21" ht="18" customHeight="1">
+    <row r="378" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A378" s="1"/>
       <c r="B378" s="27"/>
       <c r="C378" s="17"/>
@@ -9852,7 +9820,7 @@
       <c r="T378" s="11"/>
       <c r="U378" s="11"/>
     </row>
-    <row r="379" spans="1:21" ht="18" customHeight="1">
+    <row r="379" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A379" s="1"/>
       <c r="B379" s="27"/>
       <c r="C379" s="17"/>
@@ -9875,7 +9843,7 @@
       <c r="T379" s="11"/>
       <c r="U379" s="11"/>
     </row>
-    <row r="380" spans="1:21" ht="18" customHeight="1">
+    <row r="380" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A380" s="1"/>
       <c r="B380" s="27"/>
       <c r="C380" s="17"/>
@@ -9898,7 +9866,7 @@
       <c r="T380" s="11"/>
       <c r="U380" s="11"/>
     </row>
-    <row r="381" spans="1:21" ht="18" customHeight="1">
+    <row r="381" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A381" s="1"/>
       <c r="B381" s="27"/>
       <c r="C381" s="17"/>
@@ -9921,7 +9889,7 @@
       <c r="T381" s="11"/>
       <c r="U381" s="11"/>
     </row>
-    <row r="382" spans="1:21" ht="18" customHeight="1">
+    <row r="382" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A382" s="1"/>
       <c r="B382" s="27"/>
       <c r="C382" s="17"/>
@@ -9944,7 +9912,7 @@
       <c r="T382" s="11"/>
       <c r="U382" s="11"/>
     </row>
-    <row r="383" spans="1:21" ht="18" customHeight="1">
+    <row r="383" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A383" s="1"/>
       <c r="B383" s="27"/>
       <c r="C383" s="17"/>
@@ -9967,7 +9935,7 @@
       <c r="T383" s="11"/>
       <c r="U383" s="11"/>
     </row>
-    <row r="384" spans="1:21" ht="18" customHeight="1">
+    <row r="384" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A384" s="1"/>
       <c r="B384" s="27"/>
       <c r="C384" s="17"/>
@@ -9990,7 +9958,7 @@
       <c r="T384" s="11"/>
       <c r="U384" s="11"/>
     </row>
-    <row r="385" spans="1:21" ht="18" customHeight="1">
+    <row r="385" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A385" s="1"/>
       <c r="B385" s="27"/>
       <c r="C385" s="17"/>
@@ -10013,7 +9981,7 @@
       <c r="T385" s="11"/>
       <c r="U385" s="11"/>
     </row>
-    <row r="386" spans="1:21" ht="18" customHeight="1">
+    <row r="386" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A386" s="1"/>
       <c r="B386" s="27"/>
       <c r="C386" s="17"/>
@@ -10036,7 +10004,7 @@
       <c r="T386" s="11"/>
       <c r="U386" s="11"/>
     </row>
-    <row r="387" spans="1:21" ht="18" customHeight="1">
+    <row r="387" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A387" s="1"/>
       <c r="B387" s="27"/>
       <c r="C387" s="17"/>
@@ -10059,7 +10027,7 @@
       <c r="T387" s="11"/>
       <c r="U387" s="11"/>
     </row>
-    <row r="388" spans="1:21" ht="18" customHeight="1">
+    <row r="388" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A388" s="1"/>
       <c r="B388" s="27"/>
       <c r="C388" s="17"/>
@@ -10082,7 +10050,7 @@
       <c r="T388" s="11"/>
       <c r="U388" s="11"/>
     </row>
-    <row r="389" spans="1:21" ht="18" customHeight="1">
+    <row r="389" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A389" s="1"/>
       <c r="B389" s="27"/>
       <c r="C389" s="17"/>
@@ -10105,7 +10073,7 @@
       <c r="T389" s="11"/>
       <c r="U389" s="11"/>
     </row>
-    <row r="390" spans="1:21" ht="18" customHeight="1">
+    <row r="390" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A390" s="1"/>
       <c r="B390" s="27"/>
       <c r="C390" s="17"/>
@@ -10128,7 +10096,7 @@
       <c r="T390" s="11"/>
       <c r="U390" s="11"/>
     </row>
-    <row r="391" spans="1:21" ht="18" customHeight="1">
+    <row r="391" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A391" s="1"/>
       <c r="B391" s="27"/>
       <c r="C391" s="17"/>
@@ -10151,7 +10119,7 @@
       <c r="T391" s="11"/>
       <c r="U391" s="11"/>
     </row>
-    <row r="392" spans="1:21" ht="18" customHeight="1">
+    <row r="392" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A392" s="1"/>
       <c r="B392" s="27"/>
       <c r="C392" s="17"/>
@@ -10174,7 +10142,7 @@
       <c r="T392" s="11"/>
       <c r="U392" s="11"/>
     </row>
-    <row r="393" spans="1:21" ht="18" customHeight="1">
+    <row r="393" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A393" s="1"/>
       <c r="B393" s="27"/>
       <c r="C393" s="17"/>
@@ -10197,7 +10165,7 @@
       <c r="T393" s="11"/>
       <c r="U393" s="11"/>
     </row>
-    <row r="394" spans="1:21" ht="18" customHeight="1">
+    <row r="394" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A394" s="1"/>
       <c r="B394" s="27"/>
       <c r="C394" s="17"/>
@@ -10220,7 +10188,7 @@
       <c r="T394" s="11"/>
       <c r="U394" s="11"/>
     </row>
-    <row r="395" spans="1:21" ht="18" customHeight="1">
+    <row r="395" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A395" s="1"/>
       <c r="B395" s="27"/>
       <c r="C395" s="17"/>
@@ -10243,7 +10211,7 @@
       <c r="T395" s="11"/>
       <c r="U395" s="11"/>
     </row>
-    <row r="396" spans="1:21" ht="18" customHeight="1">
+    <row r="396" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A396" s="1"/>
       <c r="B396" s="27"/>
       <c r="C396" s="17"/>
@@ -10266,7 +10234,7 @@
       <c r="T396" s="11"/>
       <c r="U396" s="11"/>
     </row>
-    <row r="397" spans="1:21" ht="18" customHeight="1">
+    <row r="397" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A397" s="1"/>
       <c r="B397" s="27"/>
       <c r="C397" s="17"/>
@@ -10289,7 +10257,7 @@
       <c r="T397" s="11"/>
       <c r="U397" s="11"/>
     </row>
-    <row r="398" spans="1:21" ht="18" customHeight="1">
+    <row r="398" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A398" s="1"/>
       <c r="B398" s="27"/>
       <c r="C398" s="17"/>
@@ -10312,7 +10280,7 @@
       <c r="T398" s="11"/>
       <c r="U398" s="11"/>
     </row>
-    <row r="399" spans="1:21" ht="18" customHeight="1">
+    <row r="399" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A399" s="1"/>
       <c r="B399" s="27"/>
       <c r="C399" s="17"/>
@@ -10335,7 +10303,7 @@
       <c r="T399" s="11"/>
       <c r="U399" s="11"/>
     </row>
-    <row r="400" spans="1:21" ht="18" customHeight="1">
+    <row r="400" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A400" s="1"/>
       <c r="B400" s="27"/>
       <c r="C400" s="17"/>
@@ -10358,7 +10326,7 @@
       <c r="T400" s="11"/>
       <c r="U400" s="11"/>
     </row>
-    <row r="401" spans="1:21" ht="18" customHeight="1">
+    <row r="401" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A401" s="1"/>
       <c r="B401" s="27"/>
       <c r="C401" s="17"/>
@@ -10381,7 +10349,7 @@
       <c r="T401" s="11"/>
       <c r="U401" s="11"/>
     </row>
-    <row r="402" spans="1:21" ht="18" customHeight="1">
+    <row r="402" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A402" s="1"/>
       <c r="B402" s="27"/>
       <c r="C402" s="17"/>
@@ -10404,7 +10372,7 @@
       <c r="T402" s="11"/>
       <c r="U402" s="11"/>
     </row>
-    <row r="403" spans="1:21" ht="18" customHeight="1">
+    <row r="403" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A403" s="1"/>
       <c r="B403" s="27"/>
       <c r="C403" s="17"/>
@@ -10427,7 +10395,7 @@
       <c r="T403" s="11"/>
       <c r="U403" s="11"/>
     </row>
-    <row r="404" spans="1:21" ht="18" customHeight="1">
+    <row r="404" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A404" s="1"/>
       <c r="B404" s="27"/>
       <c r="C404" s="17"/>
@@ -10450,7 +10418,7 @@
       <c r="T404" s="11"/>
       <c r="U404" s="11"/>
     </row>
-    <row r="405" spans="1:21" ht="18" customHeight="1">
+    <row r="405" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A405" s="1"/>
       <c r="B405" s="27"/>
       <c r="C405" s="17"/>
@@ -10473,7 +10441,7 @@
       <c r="T405" s="11"/>
       <c r="U405" s="11"/>
     </row>
-    <row r="406" spans="1:21" ht="18" customHeight="1">
+    <row r="406" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A406" s="1"/>
       <c r="B406" s="27"/>
       <c r="C406" s="17"/>
@@ -10496,7 +10464,7 @@
       <c r="T406" s="11"/>
       <c r="U406" s="11"/>
     </row>
-    <row r="407" spans="1:21" ht="18" customHeight="1">
+    <row r="407" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A407" s="1"/>
       <c r="B407" s="27"/>
       <c r="C407" s="17"/>
@@ -10519,7 +10487,7 @@
       <c r="T407" s="11"/>
       <c r="U407" s="11"/>
     </row>
-    <row r="408" spans="1:21" ht="18" customHeight="1">
+    <row r="408" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A408" s="1"/>
       <c r="B408" s="27"/>
       <c r="C408" s="17"/>
@@ -10542,7 +10510,7 @@
       <c r="T408" s="11"/>
       <c r="U408" s="11"/>
     </row>
-    <row r="409" spans="1:21" ht="18" customHeight="1">
+    <row r="409" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A409" s="1"/>
       <c r="B409" s="27"/>
       <c r="C409" s="17"/>
@@ -10565,7 +10533,7 @@
       <c r="T409" s="11"/>
       <c r="U409" s="11"/>
     </row>
-    <row r="410" spans="1:21" ht="18" customHeight="1">
+    <row r="410" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A410" s="1"/>
       <c r="B410" s="27"/>
       <c r="C410" s="17"/>
@@ -10588,7 +10556,7 @@
       <c r="T410" s="11"/>
       <c r="U410" s="11"/>
     </row>
-    <row r="411" spans="1:21" ht="18" customHeight="1">
+    <row r="411" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A411" s="1"/>
       <c r="B411" s="27"/>
       <c r="C411" s="17"/>
@@ -10611,7 +10579,7 @@
       <c r="T411" s="11"/>
       <c r="U411" s="11"/>
     </row>
-    <row r="412" spans="1:21" ht="18" customHeight="1">
+    <row r="412" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A412" s="1"/>
       <c r="B412" s="27"/>
       <c r="C412" s="17"/>
@@ -10634,7 +10602,7 @@
       <c r="T412" s="11"/>
       <c r="U412" s="11"/>
     </row>
-    <row r="413" spans="1:21" ht="18" customHeight="1">
+    <row r="413" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A413" s="1"/>
       <c r="B413" s="27"/>
       <c r="C413" s="17"/>
@@ -10657,7 +10625,7 @@
       <c r="T413" s="11"/>
       <c r="U413" s="11"/>
     </row>
-    <row r="414" spans="1:21" ht="18" customHeight="1">
+    <row r="414" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A414" s="1"/>
       <c r="B414" s="27"/>
       <c r="C414" s="17"/>
@@ -10680,7 +10648,7 @@
       <c r="T414" s="11"/>
       <c r="U414" s="11"/>
     </row>
-    <row r="415" spans="1:21" ht="18" customHeight="1">
+    <row r="415" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A415" s="1"/>
       <c r="B415" s="27"/>
       <c r="C415" s="17"/>
@@ -10703,7 +10671,7 @@
       <c r="T415" s="11"/>
       <c r="U415" s="11"/>
     </row>
-    <row r="416" spans="1:21" ht="18" customHeight="1">
+    <row r="416" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A416" s="1"/>
       <c r="B416" s="27"/>
       <c r="C416" s="17"/>
@@ -10726,7 +10694,7 @@
       <c r="T416" s="11"/>
       <c r="U416" s="11"/>
     </row>
-    <row r="417" spans="1:21" ht="18" customHeight="1">
+    <row r="417" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A417" s="1"/>
       <c r="B417" s="27"/>
       <c r="C417" s="17"/>
@@ -10749,7 +10717,7 @@
       <c r="T417" s="11"/>
       <c r="U417" s="11"/>
     </row>
-    <row r="418" spans="1:21" ht="18" customHeight="1">
+    <row r="418" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A418" s="1"/>
       <c r="B418" s="27"/>
       <c r="C418" s="17"/>
@@ -10772,7 +10740,7 @@
       <c r="T418" s="11"/>
       <c r="U418" s="11"/>
     </row>
-    <row r="419" spans="1:21" ht="18" customHeight="1">
+    <row r="419" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A419" s="1"/>
       <c r="B419" s="27"/>
       <c r="C419" s="17"/>
@@ -10795,7 +10763,7 @@
       <c r="T419" s="11"/>
       <c r="U419" s="11"/>
     </row>
-    <row r="420" spans="1:21" ht="18" customHeight="1">
+    <row r="420" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A420" s="1"/>
       <c r="B420" s="27"/>
       <c r="C420" s="17"/>
@@ -10818,7 +10786,7 @@
       <c r="T420" s="11"/>
       <c r="U420" s="11"/>
     </row>
-    <row r="421" spans="1:21" ht="18" customHeight="1">
+    <row r="421" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A421" s="1"/>
       <c r="B421" s="27"/>
       <c r="C421" s="17"/>
@@ -10841,7 +10809,7 @@
       <c r="T421" s="11"/>
       <c r="U421" s="11"/>
     </row>
-    <row r="422" spans="1:21" ht="18" customHeight="1">
+    <row r="422" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A422" s="1"/>
       <c r="B422" s="27"/>
       <c r="C422" s="17"/>
@@ -10864,7 +10832,7 @@
       <c r="T422" s="11"/>
       <c r="U422" s="11"/>
     </row>
-    <row r="423" spans="1:21" ht="18" customHeight="1">
+    <row r="423" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A423" s="1"/>
       <c r="B423" s="27"/>
       <c r="C423" s="17"/>
@@ -10887,7 +10855,7 @@
       <c r="T423" s="11"/>
       <c r="U423" s="11"/>
     </row>
-    <row r="424" spans="1:21" ht="18" customHeight="1">
+    <row r="424" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A424" s="1"/>
       <c r="B424" s="27"/>
       <c r="C424" s="17"/>
@@ -10910,7 +10878,7 @@
       <c r="T424" s="11"/>
       <c r="U424" s="11"/>
     </row>
-    <row r="425" spans="1:21" ht="18" customHeight="1">
+    <row r="425" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A425" s="1"/>
       <c r="B425" s="27"/>
       <c r="C425" s="17"/>
@@ -10933,7 +10901,7 @@
       <c r="T425" s="11"/>
       <c r="U425" s="11"/>
     </row>
-    <row r="426" spans="1:21" ht="18" customHeight="1">
+    <row r="426" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A426" s="1"/>
       <c r="B426" s="27"/>
       <c r="C426" s="17"/>
@@ -10956,7 +10924,7 @@
       <c r="T426" s="11"/>
       <c r="U426" s="11"/>
     </row>
-    <row r="427" spans="1:21" ht="18" customHeight="1">
+    <row r="427" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A427" s="1"/>
       <c r="B427" s="27"/>
       <c r="C427" s="17"/>
@@ -10979,7 +10947,7 @@
       <c r="T427" s="11"/>
       <c r="U427" s="11"/>
     </row>
-    <row r="428" spans="1:21" ht="18" customHeight="1">
+    <row r="428" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A428" s="1"/>
       <c r="B428" s="27"/>
       <c r="C428" s="17"/>
@@ -11002,7 +10970,7 @@
       <c r="T428" s="11"/>
       <c r="U428" s="11"/>
     </row>
-    <row r="429" spans="1:21" ht="18" customHeight="1">
+    <row r="429" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A429" s="1"/>
       <c r="B429" s="27"/>
       <c r="C429" s="17"/>
@@ -11025,7 +10993,7 @@
       <c r="T429" s="11"/>
       <c r="U429" s="11"/>
     </row>
-    <row r="430" spans="1:21" ht="18" customHeight="1">
+    <row r="430" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A430" s="1"/>
       <c r="B430" s="27"/>
       <c r="C430" s="17"/>
@@ -11048,7 +11016,7 @@
       <c r="T430" s="11"/>
       <c r="U430" s="11"/>
     </row>
-    <row r="431" spans="1:21" ht="18" customHeight="1">
+    <row r="431" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A431" s="1"/>
       <c r="B431" s="27"/>
       <c r="C431" s="17"/>
@@ -11071,7 +11039,7 @@
       <c r="T431" s="11"/>
       <c r="U431" s="11"/>
     </row>
-    <row r="432" spans="1:21" ht="18" customHeight="1">
+    <row r="432" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A432" s="1"/>
       <c r="B432" s="27"/>
       <c r="C432" s="17"/>
@@ -11094,7 +11062,7 @@
       <c r="T432" s="11"/>
       <c r="U432" s="11"/>
     </row>
-    <row r="433" spans="1:21" ht="18" customHeight="1">
+    <row r="433" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A433" s="1"/>
       <c r="B433" s="27"/>
       <c r="C433" s="17"/>
@@ -11117,7 +11085,7 @@
       <c r="T433" s="11"/>
       <c r="U433" s="11"/>
     </row>
-    <row r="434" spans="1:21" ht="18" customHeight="1">
+    <row r="434" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A434" s="1"/>
       <c r="B434" s="27"/>
       <c r="C434" s="17"/>
@@ -11140,7 +11108,7 @@
       <c r="T434" s="11"/>
       <c r="U434" s="11"/>
     </row>
-    <row r="435" spans="1:21" ht="18" customHeight="1">
+    <row r="435" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A435" s="1"/>
       <c r="B435" s="27"/>
       <c r="C435" s="17"/>
@@ -11163,7 +11131,7 @@
       <c r="T435" s="11"/>
       <c r="U435" s="11"/>
     </row>
-    <row r="436" spans="1:21" ht="18" customHeight="1">
+    <row r="436" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A436" s="1"/>
       <c r="B436" s="27"/>
       <c r="C436" s="17"/>
@@ -11186,7 +11154,7 @@
       <c r="T436" s="11"/>
       <c r="U436" s="11"/>
     </row>
-    <row r="437" spans="1:21" ht="18" customHeight="1">
+    <row r="437" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A437" s="1"/>
       <c r="B437" s="27"/>
       <c r="C437" s="17"/>
@@ -11209,7 +11177,7 @@
       <c r="T437" s="11"/>
       <c r="U437" s="11"/>
     </row>
-    <row r="438" spans="1:21" ht="18" customHeight="1">
+    <row r="438" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A438" s="1"/>
       <c r="B438" s="27"/>
       <c r="C438" s="17"/>
@@ -11232,7 +11200,7 @@
       <c r="T438" s="11"/>
       <c r="U438" s="11"/>
     </row>
-    <row r="439" spans="1:21" ht="18" customHeight="1">
+    <row r="439" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A439" s="1"/>
       <c r="B439" s="27"/>
       <c r="C439" s="17"/>
@@ -11255,7 +11223,7 @@
       <c r="T439" s="11"/>
       <c r="U439" s="11"/>
     </row>
-    <row r="440" spans="1:21" ht="18" customHeight="1">
+    <row r="440" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A440" s="1"/>
       <c r="B440" s="27"/>
       <c r="C440" s="17"/>
@@ -11278,7 +11246,7 @@
       <c r="T440" s="11"/>
       <c r="U440" s="11"/>
     </row>
-    <row r="441" spans="1:21" ht="18" customHeight="1">
+    <row r="441" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A441" s="1"/>
       <c r="B441" s="27"/>
       <c r="C441" s="17"/>
@@ -11301,7 +11269,7 @@
       <c r="T441" s="11"/>
       <c r="U441" s="11"/>
     </row>
-    <row r="442" spans="1:21" ht="18" customHeight="1">
+    <row r="442" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A442" s="1"/>
       <c r="B442" s="27"/>
       <c r="C442" s="17"/>
@@ -11324,7 +11292,7 @@
       <c r="T442" s="11"/>
       <c r="U442" s="11"/>
     </row>
-    <row r="443" spans="1:21" ht="18" customHeight="1">
+    <row r="443" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A443" s="1"/>
       <c r="B443" s="27"/>
       <c r="C443" s="17"/>
@@ -11347,7 +11315,7 @@
       <c r="T443" s="11"/>
       <c r="U443" s="11"/>
     </row>
-    <row r="444" spans="1:21" ht="18" customHeight="1">
+    <row r="444" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A444" s="1"/>
       <c r="B444" s="27"/>
       <c r="C444" s="17"/>
@@ -11370,7 +11338,7 @@
       <c r="T444" s="11"/>
       <c r="U444" s="11"/>
     </row>
-    <row r="445" spans="1:21" ht="18" customHeight="1">
+    <row r="445" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A445" s="1"/>
       <c r="B445" s="27"/>
       <c r="C445" s="17"/>
@@ -11393,7 +11361,7 @@
       <c r="T445" s="11"/>
       <c r="U445" s="11"/>
     </row>
-    <row r="446" spans="1:21" ht="18" customHeight="1">
+    <row r="446" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A446" s="1"/>
       <c r="B446" s="27"/>
       <c r="C446" s="17"/>
@@ -11416,7 +11384,7 @@
       <c r="T446" s="11"/>
       <c r="U446" s="11"/>
     </row>
-    <row r="447" spans="1:21" ht="18" customHeight="1">
+    <row r="447" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A447" s="1"/>
       <c r="B447" s="27"/>
       <c r="C447" s="17"/>
@@ -11439,7 +11407,7 @@
       <c r="T447" s="11"/>
       <c r="U447" s="11"/>
     </row>
-    <row r="448" spans="1:21" ht="18" customHeight="1">
+    <row r="448" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A448" s="1"/>
       <c r="B448" s="27"/>
       <c r="C448" s="17"/>
@@ -11462,7 +11430,7 @@
       <c r="T448" s="11"/>
       <c r="U448" s="11"/>
     </row>
-    <row r="449" spans="1:21" ht="18" customHeight="1">
+    <row r="449" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A449" s="1"/>
       <c r="B449" s="27"/>
       <c r="C449" s="17"/>
@@ -11485,7 +11453,7 @@
       <c r="T449" s="11"/>
       <c r="U449" s="11"/>
     </row>
-    <row r="450" spans="1:21" ht="18" customHeight="1">
+    <row r="450" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A450" s="1"/>
       <c r="B450" s="27"/>
       <c r="C450" s="17"/>
@@ -11508,7 +11476,7 @@
       <c r="T450" s="11"/>
       <c r="U450" s="11"/>
     </row>
-    <row r="451" spans="1:21" ht="18" customHeight="1">
+    <row r="451" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A451" s="1"/>
       <c r="B451" s="27"/>
       <c r="C451" s="17"/>
@@ -11531,7 +11499,7 @@
       <c r="T451" s="11"/>
       <c r="U451" s="11"/>
     </row>
-    <row r="452" spans="1:21" ht="18" customHeight="1">
+    <row r="452" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A452" s="1"/>
       <c r="B452" s="27"/>
       <c r="C452" s="17"/>
@@ -11554,7 +11522,7 @@
       <c r="T452" s="11"/>
       <c r="U452" s="11"/>
     </row>
-    <row r="453" spans="1:21" ht="18" customHeight="1">
+    <row r="453" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A453" s="1"/>
       <c r="B453" s="27"/>
       <c r="C453" s="17"/>
@@ -11577,7 +11545,7 @@
       <c r="T453" s="11"/>
       <c r="U453" s="11"/>
     </row>
-    <row r="454" spans="1:21" ht="18" customHeight="1">
+    <row r="454" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A454" s="1"/>
       <c r="B454" s="27"/>
       <c r="C454" s="17"/>
@@ -11600,7 +11568,7 @@
       <c r="T454" s="11"/>
       <c r="U454" s="11"/>
     </row>
-    <row r="455" spans="1:21" ht="18" customHeight="1">
+    <row r="455" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A455" s="1"/>
       <c r="B455" s="27"/>
       <c r="C455" s="17"/>
@@ -11623,7 +11591,7 @@
       <c r="T455" s="11"/>
       <c r="U455" s="11"/>
     </row>
-    <row r="456" spans="1:21" ht="18" customHeight="1">
+    <row r="456" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A456" s="1"/>
       <c r="B456" s="27"/>
       <c r="C456" s="17"/>
@@ -11646,7 +11614,7 @@
       <c r="T456" s="11"/>
       <c r="U456" s="11"/>
     </row>
-    <row r="457" spans="1:21" ht="18" customHeight="1">
+    <row r="457" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A457" s="1"/>
       <c r="B457" s="27"/>
       <c r="C457" s="17"/>
@@ -11669,7 +11637,7 @@
       <c r="T457" s="11"/>
       <c r="U457" s="11"/>
     </row>
-    <row r="458" spans="1:21" ht="18" customHeight="1">
+    <row r="458" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A458" s="1"/>
       <c r="B458" s="27"/>
       <c r="C458" s="17"/>
@@ -11692,7 +11660,7 @@
       <c r="T458" s="11"/>
       <c r="U458" s="11"/>
     </row>
-    <row r="459" spans="1:21" ht="18" customHeight="1">
+    <row r="459" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A459" s="1"/>
       <c r="B459" s="27"/>
       <c r="C459" s="17"/>
@@ -11715,7 +11683,7 @@
       <c r="T459" s="11"/>
       <c r="U459" s="11"/>
     </row>
-    <row r="460" spans="1:21" ht="18" customHeight="1">
+    <row r="460" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A460" s="1"/>
       <c r="B460" s="27"/>
       <c r="C460" s="17"/>
@@ -11738,7 +11706,7 @@
       <c r="T460" s="11"/>
       <c r="U460" s="11"/>
     </row>
-    <row r="461" spans="1:21" ht="18" customHeight="1">
+    <row r="461" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A461" s="1"/>
       <c r="B461" s="27"/>
       <c r="C461" s="17"/>
@@ -11761,7 +11729,7 @@
       <c r="T461" s="11"/>
       <c r="U461" s="11"/>
     </row>
-    <row r="462" spans="1:21" ht="18" customHeight="1">
+    <row r="462" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A462" s="1"/>
       <c r="B462" s="27"/>
       <c r="C462" s="17"/>
@@ -11784,7 +11752,7 @@
       <c r="T462" s="11"/>
       <c r="U462" s="11"/>
     </row>
-    <row r="463" spans="1:21" ht="18" customHeight="1">
+    <row r="463" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A463" s="1"/>
       <c r="B463" s="27"/>
       <c r="C463" s="17"/>
@@ -11807,7 +11775,7 @@
       <c r="T463" s="11"/>
       <c r="U463" s="11"/>
     </row>
-    <row r="464" spans="1:21" ht="18" customHeight="1">
+    <row r="464" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A464" s="1"/>
       <c r="B464" s="27"/>
       <c r="C464" s="17"/>
@@ -11830,7 +11798,7 @@
       <c r="T464" s="11"/>
       <c r="U464" s="11"/>
     </row>
-    <row r="465" spans="1:21" ht="18" customHeight="1">
+    <row r="465" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A465" s="1"/>
       <c r="B465" s="27"/>
       <c r="C465" s="17"/>
@@ -11853,7 +11821,7 @@
       <c r="T465" s="11"/>
       <c r="U465" s="11"/>
     </row>
-    <row r="466" spans="1:21" ht="18" customHeight="1">
+    <row r="466" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A466" s="1"/>
       <c r="B466" s="27"/>
       <c r="C466" s="17"/>
@@ -11876,7 +11844,7 @@
       <c r="T466" s="11"/>
       <c r="U466" s="11"/>
     </row>
-    <row r="467" spans="1:21" ht="18" customHeight="1">
+    <row r="467" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A467" s="1"/>
       <c r="B467" s="27"/>
       <c r="C467" s="17"/>
@@ -11899,7 +11867,7 @@
       <c r="T467" s="11"/>
       <c r="U467" s="11"/>
     </row>
-    <row r="468" spans="1:21" ht="18" customHeight="1">
+    <row r="468" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A468" s="1"/>
       <c r="B468" s="27"/>
       <c r="C468" s="17"/>
@@ -11922,7 +11890,7 @@
       <c r="T468" s="11"/>
       <c r="U468" s="11"/>
     </row>
-    <row r="469" spans="1:21" ht="18" customHeight="1">
+    <row r="469" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A469" s="1"/>
       <c r="B469" s="27"/>
       <c r="C469" s="17"/>
@@ -11945,7 +11913,7 @@
       <c r="T469" s="11"/>
       <c r="U469" s="11"/>
     </row>
-    <row r="470" spans="1:21" ht="18" customHeight="1">
+    <row r="470" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A470" s="1"/>
       <c r="B470" s="27"/>
       <c r="C470" s="17"/>
@@ -11968,7 +11936,7 @@
       <c r="T470" s="11"/>
       <c r="U470" s="11"/>
     </row>
-    <row r="471" spans="1:21" ht="18" customHeight="1">
+    <row r="471" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A471" s="1"/>
       <c r="B471" s="27"/>
       <c r="C471" s="17"/>
@@ -11991,7 +11959,7 @@
       <c r="T471" s="11"/>
       <c r="U471" s="11"/>
     </row>
-    <row r="472" spans="1:21" ht="18" customHeight="1">
+    <row r="472" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A472" s="1"/>
       <c r="B472" s="27"/>
       <c r="C472" s="17"/>
@@ -12014,7 +11982,7 @@
       <c r="T472" s="11"/>
       <c r="U472" s="11"/>
     </row>
-    <row r="473" spans="1:21" ht="18" customHeight="1">
+    <row r="473" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A473" s="1"/>
       <c r="B473" s="27"/>
       <c r="C473" s="17"/>
@@ -12037,7 +12005,7 @@
       <c r="T473" s="11"/>
       <c r="U473" s="11"/>
     </row>
-    <row r="474" spans="1:21" ht="18" customHeight="1">
+    <row r="474" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A474" s="1"/>
       <c r="B474" s="27"/>
       <c r="C474" s="17"/>
@@ -12060,7 +12028,7 @@
       <c r="T474" s="11"/>
       <c r="U474" s="11"/>
     </row>
-    <row r="475" spans="1:21" ht="18" customHeight="1">
+    <row r="475" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A475" s="1"/>
       <c r="B475" s="27"/>
       <c r="C475" s="17"/>
@@ -12083,7 +12051,7 @@
       <c r="T475" s="11"/>
       <c r="U475" s="11"/>
     </row>
-    <row r="476" spans="1:21" ht="18" customHeight="1">
+    <row r="476" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A476" s="1"/>
       <c r="B476" s="27"/>
       <c r="C476" s="17"/>
@@ -12106,7 +12074,7 @@
       <c r="T476" s="11"/>
       <c r="U476" s="11"/>
     </row>
-    <row r="477" spans="1:21" ht="18" customHeight="1">
+    <row r="477" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A477" s="1"/>
       <c r="B477" s="27"/>
       <c r="C477" s="17"/>
@@ -12129,7 +12097,7 @@
       <c r="T477" s="11"/>
       <c r="U477" s="11"/>
     </row>
-    <row r="478" spans="1:21" ht="18" customHeight="1">
+    <row r="478" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A478" s="1"/>
       <c r="B478" s="27"/>
       <c r="C478" s="17"/>
@@ -12152,7 +12120,7 @@
       <c r="T478" s="11"/>
       <c r="U478" s="11"/>
     </row>
-    <row r="479" spans="1:21" ht="18" customHeight="1">
+    <row r="479" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A479" s="1"/>
       <c r="B479" s="27"/>
       <c r="C479" s="17"/>
@@ -12175,7 +12143,7 @@
       <c r="T479" s="11"/>
       <c r="U479" s="11"/>
     </row>
-    <row r="480" spans="1:21" ht="18" customHeight="1">
+    <row r="480" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A480" s="1"/>
       <c r="B480" s="27"/>
       <c r="C480" s="17"/>
@@ -12198,7 +12166,7 @@
       <c r="T480" s="11"/>
       <c r="U480" s="11"/>
     </row>
-    <row r="481" spans="1:21" ht="18" customHeight="1">
+    <row r="481" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A481" s="1"/>
       <c r="B481" s="27"/>
       <c r="C481" s="17"/>
@@ -12221,7 +12189,7 @@
       <c r="T481" s="11"/>
       <c r="U481" s="11"/>
     </row>
-    <row r="482" spans="1:21" ht="18" customHeight="1">
+    <row r="482" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A482" s="1"/>
       <c r="B482" s="27"/>
       <c r="C482" s="17"/>
@@ -12244,7 +12212,7 @@
       <c r="T482" s="11"/>
       <c r="U482" s="11"/>
     </row>
-    <row r="483" spans="1:21" ht="18" customHeight="1">
+    <row r="483" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A483" s="1"/>
       <c r="B483" s="27"/>
       <c r="C483" s="17"/>
@@ -12267,7 +12235,7 @@
       <c r="T483" s="11"/>
       <c r="U483" s="11"/>
     </row>
-    <row r="484" spans="1:21" ht="18" customHeight="1">
+    <row r="484" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A484" s="1"/>
       <c r="B484" s="27"/>
       <c r="C484" s="17"/>
@@ -12290,7 +12258,7 @@
       <c r="T484" s="11"/>
       <c r="U484" s="11"/>
     </row>
-    <row r="485" spans="1:21" ht="18" customHeight="1">
+    <row r="485" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A485" s="1"/>
       <c r="B485" s="27"/>
       <c r="C485" s="17"/>
@@ -12313,7 +12281,7 @@
       <c r="T485" s="11"/>
       <c r="U485" s="11"/>
     </row>
-    <row r="486" spans="1:21" ht="18" customHeight="1">
+    <row r="486" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A486" s="1"/>
       <c r="B486" s="27"/>
       <c r="C486" s="17"/>
@@ -12336,7 +12304,7 @@
       <c r="T486" s="11"/>
       <c r="U486" s="11"/>
     </row>
-    <row r="487" spans="1:21" ht="18" customHeight="1">
+    <row r="487" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A487" s="1"/>
       <c r="B487" s="27"/>
       <c r="C487" s="17"/>
@@ -12359,7 +12327,7 @@
       <c r="T487" s="11"/>
       <c r="U487" s="11"/>
     </row>
-    <row r="488" spans="1:21" ht="18" customHeight="1">
+    <row r="488" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A488" s="1"/>
       <c r="B488" s="27"/>
       <c r="C488" s="17"/>
@@ -12382,7 +12350,7 @@
       <c r="T488" s="11"/>
       <c r="U488" s="11"/>
     </row>
-    <row r="489" spans="1:21" ht="18" customHeight="1">
+    <row r="489" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A489" s="1"/>
       <c r="B489" s="27"/>
       <c r="C489" s="17"/>
@@ -12405,7 +12373,7 @@
       <c r="T489" s="11"/>
       <c r="U489" s="11"/>
     </row>
-    <row r="490" spans="1:21" ht="18" customHeight="1">
+    <row r="490" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A490" s="1"/>
       <c r="B490" s="27"/>
       <c r="C490" s="17"/>
@@ -12428,7 +12396,7 @@
       <c r="T490" s="11"/>
       <c r="U490" s="11"/>
     </row>
-    <row r="491" spans="1:21" ht="18" customHeight="1">
+    <row r="491" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A491" s="1"/>
       <c r="B491" s="27"/>
       <c r="C491" s="17"/>
@@ -12451,7 +12419,7 @@
       <c r="T491" s="11"/>
       <c r="U491" s="11"/>
     </row>
-    <row r="492" spans="1:21" ht="18" customHeight="1">
+    <row r="492" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A492" s="1"/>
       <c r="B492" s="27"/>
       <c r="C492" s="17"/>
@@ -12474,7 +12442,7 @@
       <c r="T492" s="11"/>
       <c r="U492" s="11"/>
     </row>
-    <row r="493" spans="1:21" ht="18" customHeight="1">
+    <row r="493" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A493" s="1"/>
       <c r="B493" s="27"/>
       <c r="C493" s="17"/>
@@ -12497,7 +12465,7 @@
       <c r="T493" s="11"/>
       <c r="U493" s="11"/>
     </row>
-    <row r="494" spans="1:21" ht="18" customHeight="1">
+    <row r="494" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A494" s="1"/>
       <c r="B494" s="27"/>
       <c r="C494" s="17"/>
@@ -12520,7 +12488,7 @@
       <c r="T494" s="11"/>
       <c r="U494" s="11"/>
     </row>
-    <row r="495" spans="1:21" ht="18" customHeight="1">
+    <row r="495" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A495" s="1"/>
       <c r="B495" s="27"/>
       <c r="C495" s="17"/>
@@ -12543,7 +12511,7 @@
       <c r="T495" s="11"/>
       <c r="U495" s="11"/>
     </row>
-    <row r="496" spans="1:21" ht="18" customHeight="1">
+    <row r="496" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A496" s="1"/>
       <c r="B496" s="27"/>
       <c r="C496" s="17"/>
@@ -12566,7 +12534,7 @@
       <c r="T496" s="11"/>
       <c r="U496" s="11"/>
     </row>
-    <row r="497" spans="1:21" ht="18" customHeight="1">
+    <row r="497" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A497" s="1"/>
       <c r="B497" s="27"/>
       <c r="C497" s="17"/>
@@ -12589,7 +12557,7 @@
       <c r="T497" s="11"/>
       <c r="U497" s="11"/>
     </row>
-    <row r="498" spans="1:21" ht="18" customHeight="1">
+    <row r="498" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A498" s="1"/>
       <c r="B498" s="27"/>
       <c r="C498" s="17"/>
@@ -12612,7 +12580,7 @@
       <c r="T498" s="11"/>
       <c r="U498" s="11"/>
     </row>
-    <row r="499" spans="1:21" ht="18" customHeight="1">
+    <row r="499" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A499" s="1"/>
       <c r="B499" s="27"/>
       <c r="C499" s="17"/>
@@ -12635,7 +12603,7 @@
       <c r="T499" s="11"/>
       <c r="U499" s="11"/>
     </row>
-    <row r="500" spans="1:21" ht="18" customHeight="1">
+    <row r="500" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A500" s="1"/>
       <c r="B500" s="27"/>
       <c r="C500" s="17"/>
@@ -12658,7 +12626,7 @@
       <c r="T500" s="11"/>
       <c r="U500" s="11"/>
     </row>
-    <row r="501" spans="1:21" ht="18" customHeight="1">
+    <row r="501" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A501" s="1"/>
       <c r="B501" s="27"/>
       <c r="C501" s="17"/>
@@ -12681,7 +12649,7 @@
       <c r="T501" s="11"/>
       <c r="U501" s="11"/>
     </row>
-    <row r="502" spans="1:21" ht="18" customHeight="1">
+    <row r="502" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A502" s="1"/>
       <c r="B502" s="27"/>
       <c r="C502" s="17"/>
@@ -12704,7 +12672,7 @@
       <c r="T502" s="11"/>
       <c r="U502" s="11"/>
     </row>
-    <row r="503" spans="1:21" ht="18" customHeight="1">
+    <row r="503" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A503" s="1"/>
       <c r="B503" s="27"/>
       <c r="C503" s="17"/>
@@ -12727,7 +12695,7 @@
       <c r="T503" s="11"/>
       <c r="U503" s="11"/>
     </row>
-    <row r="504" spans="1:21" ht="18" customHeight="1">
+    <row r="504" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A504" s="1"/>
       <c r="B504" s="27"/>
       <c r="C504" s="17"/>
@@ -12750,7 +12718,7 @@
       <c r="T504" s="11"/>
       <c r="U504" s="11"/>
     </row>
-    <row r="505" spans="1:21" ht="18" customHeight="1">
+    <row r="505" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A505" s="1"/>
       <c r="B505" s="27"/>
       <c r="C505" s="17"/>
@@ -12773,7 +12741,7 @@
       <c r="T505" s="11"/>
       <c r="U505" s="11"/>
     </row>
-    <row r="506" spans="1:21" ht="18" customHeight="1">
+    <row r="506" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A506" s="1"/>
       <c r="B506" s="27"/>
       <c r="C506" s="17"/>
@@ -12796,7 +12764,7 @@
       <c r="T506" s="11"/>
       <c r="U506" s="11"/>
     </row>
-    <row r="507" spans="1:21" ht="18" customHeight="1">
+    <row r="507" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A507" s="1"/>
       <c r="B507" s="27"/>
       <c r="C507" s="17"/>
@@ -12819,7 +12787,7 @@
       <c r="T507" s="11"/>
       <c r="U507" s="11"/>
     </row>
-    <row r="508" spans="1:21" ht="18" customHeight="1">
+    <row r="508" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A508" s="1"/>
       <c r="B508" s="27"/>
       <c r="C508" s="17"/>
@@ -12842,7 +12810,7 @@
       <c r="T508" s="11"/>
       <c r="U508" s="11"/>
     </row>
-    <row r="509" spans="1:21" ht="18" customHeight="1">
+    <row r="509" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A509" s="1"/>
       <c r="B509" s="27"/>
       <c r="C509" s="17"/>
@@ -12865,7 +12833,7 @@
       <c r="T509" s="11"/>
       <c r="U509" s="11"/>
     </row>
-    <row r="510" spans="1:21" ht="18" customHeight="1">
+    <row r="510" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A510" s="1"/>
       <c r="B510" s="27"/>
       <c r="C510" s="17"/>
@@ -12888,7 +12856,7 @@
       <c r="T510" s="11"/>
       <c r="U510" s="11"/>
     </row>
-    <row r="511" spans="1:21" ht="18" customHeight="1">
+    <row r="511" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A511" s="1"/>
       <c r="B511" s="27"/>
       <c r="C511" s="17"/>
@@ -12911,7 +12879,7 @@
       <c r="T511" s="11"/>
       <c r="U511" s="11"/>
     </row>
-    <row r="512" spans="1:21" ht="18" customHeight="1">
+    <row r="512" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A512" s="1"/>
       <c r="B512" s="27"/>
       <c r="C512" s="17"/>
@@ -12934,7 +12902,7 @@
       <c r="T512" s="11"/>
       <c r="U512" s="11"/>
     </row>
-    <row r="513" spans="1:21" ht="18" customHeight="1">
+    <row r="513" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A513" s="1"/>
       <c r="B513" s="27"/>
       <c r="C513" s="17"/>
@@ -12957,7 +12925,7 @@
       <c r="T513" s="11"/>
       <c r="U513" s="11"/>
     </row>
-    <row r="514" spans="1:21" ht="18" customHeight="1">
+    <row r="514" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A514" s="1"/>
       <c r="B514" s="27"/>
       <c r="C514" s="17"/>
@@ -12980,7 +12948,7 @@
       <c r="T514" s="11"/>
       <c r="U514" s="11"/>
     </row>
-    <row r="515" spans="1:21" ht="18" customHeight="1">
+    <row r="515" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A515" s="1"/>
       <c r="B515" s="27"/>
       <c r="C515" s="17"/>
@@ -13003,7 +12971,7 @@
       <c r="T515" s="11"/>
       <c r="U515" s="11"/>
     </row>
-    <row r="516" spans="1:21" ht="18" customHeight="1">
+    <row r="516" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A516" s="1"/>
       <c r="B516" s="27"/>
       <c r="C516" s="17"/>
@@ -13026,7 +12994,7 @@
       <c r="T516" s="11"/>
       <c r="U516" s="11"/>
     </row>
-    <row r="517" spans="1:21" ht="18" customHeight="1">
+    <row r="517" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A517" s="1"/>
       <c r="B517" s="27"/>
       <c r="C517" s="17"/>
@@ -13049,7 +13017,7 @@
       <c r="T517" s="11"/>
       <c r="U517" s="11"/>
     </row>
-    <row r="518" spans="1:21" ht="18" customHeight="1">
+    <row r="518" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A518" s="1"/>
       <c r="B518" s="27"/>
       <c r="C518" s="17"/>
@@ -13072,7 +13040,7 @@
       <c r="T518" s="11"/>
       <c r="U518" s="11"/>
     </row>
-    <row r="519" spans="1:21" ht="18" customHeight="1">
+    <row r="519" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A519" s="1"/>
       <c r="B519" s="27"/>
       <c r="C519" s="17"/>
@@ -13095,7 +13063,7 @@
       <c r="T519" s="11"/>
       <c r="U519" s="11"/>
     </row>
-    <row r="520" spans="1:21" ht="18" customHeight="1">
+    <row r="520" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A520" s="1"/>
       <c r="B520" s="27"/>
       <c r="C520" s="17"/>
@@ -13118,7 +13086,7 @@
       <c r="T520" s="11"/>
       <c r="U520" s="11"/>
     </row>
-    <row r="521" spans="1:21" ht="18" customHeight="1">
+    <row r="521" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A521" s="1"/>
       <c r="B521" s="27"/>
       <c r="C521" s="17"/>
@@ -13141,7 +13109,7 @@
       <c r="T521" s="11"/>
       <c r="U521" s="11"/>
     </row>
-    <row r="522" spans="1:21" ht="18" customHeight="1">
+    <row r="522" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A522" s="1"/>
       <c r="B522" s="27"/>
       <c r="C522" s="17"/>
@@ -13164,7 +13132,7 @@
       <c r="T522" s="11"/>
       <c r="U522" s="11"/>
     </row>
-    <row r="523" spans="1:21" ht="18" customHeight="1">
+    <row r="523" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A523" s="1"/>
       <c r="B523" s="27"/>
       <c r="C523" s="17"/>
@@ -13187,7 +13155,7 @@
       <c r="T523" s="11"/>
       <c r="U523" s="11"/>
     </row>
-    <row r="524" spans="1:21" ht="18" customHeight="1">
+    <row r="524" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A524" s="1"/>
       <c r="B524" s="27"/>
       <c r="C524" s="17"/>
@@ -13210,7 +13178,7 @@
       <c r="T524" s="11"/>
       <c r="U524" s="11"/>
     </row>
-    <row r="525" spans="1:21" ht="18" customHeight="1">
+    <row r="525" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A525" s="1"/>
       <c r="B525" s="27"/>
       <c r="C525" s="17"/>
@@ -13233,7 +13201,7 @@
       <c r="T525" s="11"/>
       <c r="U525" s="11"/>
     </row>
-    <row r="526" spans="1:21" ht="18" customHeight="1">
+    <row r="526" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A526" s="1"/>
       <c r="B526" s="27"/>
       <c r="C526" s="17"/>
@@ -13256,7 +13224,7 @@
       <c r="T526" s="11"/>
       <c r="U526" s="11"/>
     </row>
-    <row r="527" spans="1:21" ht="18" customHeight="1">
+    <row r="527" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A527" s="1"/>
       <c r="B527" s="27"/>
       <c r="C527" s="17"/>
@@ -13279,7 +13247,7 @@
       <c r="T527" s="11"/>
       <c r="U527" s="11"/>
     </row>
-    <row r="528" spans="1:21" ht="18" customHeight="1">
+    <row r="528" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A528" s="1"/>
       <c r="B528" s="27"/>
       <c r="C528" s="17"/>
@@ -13302,7 +13270,7 @@
       <c r="T528" s="11"/>
       <c r="U528" s="11"/>
     </row>
-    <row r="529" spans="1:21" ht="18" customHeight="1">
+    <row r="529" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A529" s="1"/>
       <c r="B529" s="27"/>
       <c r="C529" s="17"/>
@@ -13325,7 +13293,7 @@
       <c r="T529" s="11"/>
       <c r="U529" s="11"/>
     </row>
-    <row r="530" spans="1:21" ht="18" customHeight="1">
+    <row r="530" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A530" s="1"/>
       <c r="B530" s="27"/>
       <c r="C530" s="17"/>
@@ -13348,7 +13316,7 @@
       <c r="T530" s="11"/>
       <c r="U530" s="11"/>
     </row>
-    <row r="531" spans="1:21" ht="18" customHeight="1">
+    <row r="531" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A531" s="1"/>
       <c r="B531" s="27"/>
       <c r="C531" s="17"/>
@@ -13371,7 +13339,7 @@
       <c r="T531" s="11"/>
       <c r="U531" s="11"/>
     </row>
-    <row r="532" spans="1:21" ht="18" customHeight="1">
+    <row r="532" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A532" s="1"/>
       <c r="B532" s="27"/>
       <c r="C532" s="17"/>
@@ -13394,7 +13362,7 @@
       <c r="T532" s="11"/>
       <c r="U532" s="11"/>
     </row>
-    <row r="533" spans="1:21" ht="18" customHeight="1">
+    <row r="533" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A533" s="1"/>
       <c r="B533" s="27"/>
       <c r="C533" s="17"/>
@@ -13417,7 +13385,7 @@
       <c r="T533" s="11"/>
       <c r="U533" s="11"/>
     </row>
-    <row r="534" spans="1:21" ht="18" customHeight="1">
+    <row r="534" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A534" s="1"/>
       <c r="B534" s="27"/>
       <c r="C534" s="17"/>
@@ -13440,7 +13408,7 @@
       <c r="T534" s="11"/>
       <c r="U534" s="11"/>
     </row>
-    <row r="535" spans="1:21" ht="18" customHeight="1">
+    <row r="535" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A535" s="1"/>
       <c r="B535" s="27"/>
       <c r="C535" s="17"/>
@@ -13463,7 +13431,7 @@
       <c r="T535" s="11"/>
       <c r="U535" s="11"/>
     </row>
-    <row r="536" spans="1:21" ht="18" customHeight="1">
+    <row r="536" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A536" s="1"/>
       <c r="B536" s="27"/>
       <c r="C536" s="17"/>
@@ -13486,7 +13454,7 @@
       <c r="T536" s="11"/>
       <c r="U536" s="11"/>
     </row>
-    <row r="537" spans="1:21" ht="18" customHeight="1">
+    <row r="537" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A537" s="1"/>
       <c r="B537" s="27"/>
       <c r="C537" s="17"/>
@@ -13509,7 +13477,7 @@
       <c r="T537" s="11"/>
       <c r="U537" s="11"/>
     </row>
-    <row r="538" spans="1:21" ht="18" customHeight="1">
+    <row r="538" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A538" s="1"/>
       <c r="B538" s="27"/>
       <c r="C538" s="17"/>
@@ -13532,7 +13500,7 @@
       <c r="T538" s="11"/>
       <c r="U538" s="11"/>
     </row>
-    <row r="539" spans="1:21" ht="18" customHeight="1">
+    <row r="539" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A539" s="1"/>
       <c r="B539" s="27"/>
       <c r="C539" s="17"/>
@@ -13555,7 +13523,7 @@
       <c r="T539" s="11"/>
       <c r="U539" s="11"/>
     </row>
-    <row r="540" spans="1:21" ht="18" customHeight="1">
+    <row r="540" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A540" s="1"/>
       <c r="B540" s="27"/>
       <c r="C540" s="17"/>
@@ -13578,7 +13546,7 @@
       <c r="T540" s="11"/>
       <c r="U540" s="11"/>
     </row>
-    <row r="541" spans="1:21" ht="18" customHeight="1">
+    <row r="541" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A541" s="1"/>
       <c r="B541" s="27"/>
       <c r="C541" s="17"/>
@@ -13601,7 +13569,7 @@
       <c r="T541" s="11"/>
       <c r="U541" s="11"/>
     </row>
-    <row r="542" spans="1:21" ht="18" customHeight="1">
+    <row r="542" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A542" s="1"/>
       <c r="B542" s="27"/>
       <c r="C542" s="17"/>
@@ -13624,7 +13592,7 @@
       <c r="T542" s="11"/>
       <c r="U542" s="11"/>
     </row>
-    <row r="543" spans="1:21" ht="18" customHeight="1">
+    <row r="543" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A543" s="1"/>
       <c r="B543" s="27"/>
       <c r="C543" s="17"/>
@@ -13647,7 +13615,7 @@
       <c r="T543" s="11"/>
       <c r="U543" s="11"/>
     </row>
-    <row r="544" spans="1:21" ht="18" customHeight="1">
+    <row r="544" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A544" s="1"/>
       <c r="B544" s="27"/>
       <c r="C544" s="17"/>
@@ -13670,7 +13638,7 @@
       <c r="T544" s="11"/>
       <c r="U544" s="11"/>
     </row>
-    <row r="545" spans="1:21" ht="18" customHeight="1">
+    <row r="545" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A545" s="1"/>
       <c r="B545" s="27"/>
       <c r="C545" s="17"/>
@@ -13693,7 +13661,7 @@
       <c r="T545" s="11"/>
       <c r="U545" s="11"/>
     </row>
-    <row r="546" spans="1:21" ht="18" customHeight="1">
+    <row r="546" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A546" s="1"/>
       <c r="B546" s="27"/>
       <c r="C546" s="17"/>
@@ -13716,7 +13684,7 @@
       <c r="T546" s="11"/>
       <c r="U546" s="11"/>
     </row>
-    <row r="547" spans="1:21" ht="18" customHeight="1">
+    <row r="547" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A547" s="1"/>
       <c r="B547" s="27"/>
       <c r="C547" s="17"/>
@@ -13739,7 +13707,7 @@
       <c r="T547" s="11"/>
       <c r="U547" s="11"/>
     </row>
-    <row r="548" spans="1:21" ht="18" customHeight="1">
+    <row r="548" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A548" s="1"/>
       <c r="B548" s="27"/>
       <c r="C548" s="17"/>
@@ -13762,7 +13730,7 @@
       <c r="T548" s="11"/>
       <c r="U548" s="11"/>
     </row>
-    <row r="549" spans="1:21" ht="18" customHeight="1">
+    <row r="549" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A549" s="1"/>
       <c r="B549" s="27"/>
       <c r="C549" s="17"/>
@@ -13785,7 +13753,7 @@
       <c r="T549" s="11"/>
       <c r="U549" s="11"/>
     </row>
-    <row r="550" spans="1:21" ht="18" customHeight="1">
+    <row r="550" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A550" s="1"/>
       <c r="B550" s="27"/>
       <c r="C550" s="17"/>
@@ -13808,7 +13776,7 @@
       <c r="T550" s="11"/>
       <c r="U550" s="11"/>
     </row>
-    <row r="551" spans="1:21" ht="18" customHeight="1">
+    <row r="551" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A551" s="1"/>
       <c r="B551" s="27"/>
       <c r="C551" s="17"/>
@@ -13831,7 +13799,7 @@
       <c r="T551" s="11"/>
       <c r="U551" s="11"/>
     </row>
-    <row r="552" spans="1:21" ht="18" customHeight="1">
+    <row r="552" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A552" s="1"/>
       <c r="B552" s="27"/>
       <c r="C552" s="17"/>
@@ -13854,7 +13822,7 @@
       <c r="T552" s="11"/>
       <c r="U552" s="11"/>
     </row>
-    <row r="553" spans="1:21" ht="18" customHeight="1">
+    <row r="553" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A553" s="1"/>
       <c r="B553" s="27"/>
       <c r="C553" s="17"/>
@@ -13877,7 +13845,7 @@
       <c r="T553" s="11"/>
       <c r="U553" s="11"/>
     </row>
-    <row r="554" spans="1:21" ht="18" customHeight="1">
+    <row r="554" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A554" s="1"/>
       <c r="B554" s="27"/>
       <c r="C554" s="17"/>
@@ -13900,7 +13868,7 @@
       <c r="T554" s="11"/>
       <c r="U554" s="11"/>
     </row>
-    <row r="555" spans="1:21" ht="18" customHeight="1">
+    <row r="555" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A555" s="1"/>
       <c r="B555" s="27"/>
       <c r="C555" s="17"/>
@@ -13923,7 +13891,7 @@
       <c r="T555" s="11"/>
       <c r="U555" s="11"/>
     </row>
-    <row r="556" spans="1:21" ht="18" customHeight="1">
+    <row r="556" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A556" s="1"/>
       <c r="B556" s="27"/>
       <c r="C556" s="17"/>
@@ -13946,7 +13914,7 @@
       <c r="T556" s="11"/>
       <c r="U556" s="11"/>
     </row>
-    <row r="557" spans="1:21" ht="18" customHeight="1">
+    <row r="557" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A557" s="1"/>
       <c r="B557" s="27"/>
       <c r="C557" s="17"/>
@@ -13969,7 +13937,7 @@
       <c r="T557" s="11"/>
       <c r="U557" s="11"/>
     </row>
-    <row r="558" spans="1:21" ht="18" customHeight="1">
+    <row r="558" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A558" s="1"/>
       <c r="B558" s="27"/>
       <c r="C558" s="17"/>
@@ -13992,7 +13960,7 @@
       <c r="T558" s="11"/>
       <c r="U558" s="11"/>
     </row>
-    <row r="559" spans="1:21" ht="18" customHeight="1">
+    <row r="559" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A559" s="1"/>
       <c r="B559" s="27"/>
       <c r="C559" s="17"/>
@@ -14015,7 +13983,7 @@
       <c r="T559" s="11"/>
       <c r="U559" s="11"/>
     </row>
-    <row r="560" spans="1:21" ht="18" customHeight="1">
+    <row r="560" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A560" s="1"/>
       <c r="B560" s="27"/>
       <c r="C560" s="17"/>
@@ -14038,7 +14006,7 @@
       <c r="T560" s="11"/>
       <c r="U560" s="11"/>
     </row>
-    <row r="561" spans="1:21" ht="18" customHeight="1">
+    <row r="561" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A561" s="1"/>
       <c r="B561" s="27"/>
       <c r="C561" s="17"/>
@@ -14061,7 +14029,7 @@
       <c r="T561" s="11"/>
       <c r="U561" s="11"/>
     </row>
-    <row r="562" spans="1:21" ht="18" customHeight="1">
+    <row r="562" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A562" s="1"/>
       <c r="B562" s="27"/>
       <c r="C562" s="17"/>
@@ -14084,7 +14052,7 @@
       <c r="T562" s="11"/>
       <c r="U562" s="11"/>
     </row>
-    <row r="563" spans="1:21" ht="18" customHeight="1">
+    <row r="563" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A563" s="1"/>
       <c r="B563" s="27"/>
       <c r="C563" s="17"/>
@@ -14107,7 +14075,7 @@
       <c r="T563" s="11"/>
       <c r="U563" s="11"/>
     </row>
-    <row r="564" spans="1:21" ht="18" customHeight="1">
+    <row r="564" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A564" s="1"/>
       <c r="B564" s="27"/>
       <c r="C564" s="17"/>
@@ -14130,7 +14098,7 @@
       <c r="T564" s="11"/>
       <c r="U564" s="11"/>
     </row>
-    <row r="565" spans="1:21" ht="18" customHeight="1">
+    <row r="565" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A565" s="1"/>
       <c r="B565" s="27"/>
       <c r="C565" s="17"/>
@@ -14153,7 +14121,7 @@
       <c r="T565" s="11"/>
       <c r="U565" s="11"/>
     </row>
-    <row r="566" spans="1:21" ht="18" customHeight="1">
+    <row r="566" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A566" s="1"/>
       <c r="B566" s="27"/>
       <c r="C566" s="17"/>
@@ -14176,7 +14144,7 @@
       <c r="T566" s="11"/>
       <c r="U566" s="11"/>
     </row>
-    <row r="567" spans="1:21" ht="18" customHeight="1">
+    <row r="567" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A567" s="1"/>
       <c r="B567" s="27"/>
       <c r="C567" s="17"/>
@@ -14199,7 +14167,7 @@
       <c r="T567" s="11"/>
       <c r="U567" s="11"/>
     </row>
-    <row r="568" spans="1:21" ht="18" customHeight="1">
+    <row r="568" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A568" s="1"/>
       <c r="B568" s="27"/>
       <c r="C568" s="17"/>
@@ -14222,7 +14190,7 @@
       <c r="T568" s="11"/>
       <c r="U568" s="11"/>
     </row>
-    <row r="569" spans="1:21" ht="18" customHeight="1">
+    <row r="569" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A569" s="1"/>
       <c r="B569" s="27"/>
       <c r="C569" s="17"/>
@@ -14245,7 +14213,7 @@
       <c r="T569" s="11"/>
       <c r="U569" s="11"/>
     </row>
-    <row r="570" spans="1:21" ht="18" customHeight="1">
+    <row r="570" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A570" s="1"/>
       <c r="B570" s="27"/>
       <c r="C570" s="17"/>
@@ -14268,7 +14236,7 @@
       <c r="T570" s="11"/>
       <c r="U570" s="11"/>
     </row>
-    <row r="571" spans="1:21" ht="18" customHeight="1">
+    <row r="571" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A571" s="1"/>
       <c r="B571" s="27"/>
       <c r="C571" s="17"/>
@@ -14291,7 +14259,7 @@
       <c r="T571" s="11"/>
       <c r="U571" s="11"/>
     </row>
-    <row r="572" spans="1:21" ht="18" customHeight="1">
+    <row r="572" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A572" s="1"/>
       <c r="B572" s="27"/>
       <c r="C572" s="17"/>
@@ -14314,7 +14282,7 @@
       <c r="T572" s="11"/>
       <c r="U572" s="11"/>
     </row>
-    <row r="573" spans="1:21" ht="18" customHeight="1">
+    <row r="573" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A573" s="1"/>
       <c r="B573" s="27"/>
       <c r="C573" s="17"/>
@@ -14337,7 +14305,7 @@
       <c r="T573" s="11"/>
       <c r="U573" s="11"/>
     </row>
-    <row r="574" spans="1:21" ht="18" customHeight="1">
+    <row r="574" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A574" s="1"/>
       <c r="B574" s="27"/>
       <c r="C574" s="17"/>
@@ -14360,7 +14328,7 @@
       <c r="T574" s="11"/>
       <c r="U574" s="11"/>
     </row>
-    <row r="575" spans="1:21" ht="18" customHeight="1">
+    <row r="575" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A575" s="1"/>
       <c r="B575" s="27"/>
       <c r="C575" s="17"/>
@@ -14383,7 +14351,7 @@
       <c r="T575" s="11"/>
       <c r="U575" s="11"/>
     </row>
-    <row r="576" spans="1:21" ht="18" customHeight="1">
+    <row r="576" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A576" s="1"/>
       <c r="B576" s="27"/>
       <c r="C576" s="17"/>
@@ -14406,7 +14374,7 @@
       <c r="T576" s="11"/>
       <c r="U576" s="11"/>
     </row>
-    <row r="577" spans="1:21" ht="18" customHeight="1">
+    <row r="577" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A577" s="1"/>
       <c r="B577" s="27"/>
       <c r="C577" s="17"/>
@@ -14429,7 +14397,7 @@
       <c r="T577" s="11"/>
       <c r="U577" s="11"/>
     </row>
-    <row r="578" spans="1:21" ht="18" customHeight="1">
+    <row r="578" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A578" s="1"/>
       <c r="B578" s="27"/>
       <c r="C578" s="17"/>
@@ -14452,7 +14420,7 @@
       <c r="T578" s="11"/>
       <c r="U578" s="11"/>
     </row>
-    <row r="579" spans="1:21" ht="18" customHeight="1">
+    <row r="579" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A579" s="1"/>
       <c r="B579" s="27"/>
       <c r="C579" s="17"/>
@@ -14475,7 +14443,7 @@
       <c r="T579" s="11"/>
       <c r="U579" s="11"/>
     </row>
-    <row r="580" spans="1:21" ht="18" customHeight="1">
+    <row r="580" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A580" s="1"/>
       <c r="B580" s="27"/>
       <c r="C580" s="17"/>
@@ -14498,7 +14466,7 @@
       <c r="T580" s="11"/>
       <c r="U580" s="11"/>
     </row>
-    <row r="581" spans="1:21" ht="18" customHeight="1">
+    <row r="581" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A581" s="1"/>
       <c r="B581" s="27"/>
       <c r="C581" s="17"/>
@@ -14521,7 +14489,7 @@
       <c r="T581" s="11"/>
       <c r="U581" s="11"/>
     </row>
-    <row r="582" spans="1:21" ht="18" customHeight="1">
+    <row r="582" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A582" s="1"/>
       <c r="B582" s="27"/>
       <c r="C582" s="17"/>
@@ -14544,7 +14512,7 @@
       <c r="T582" s="11"/>
       <c r="U582" s="11"/>
     </row>
-    <row r="583" spans="1:21" ht="18" customHeight="1">
+    <row r="583" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A583" s="1"/>
       <c r="B583" s="27"/>
       <c r="C583" s="17"/>
@@ -14567,7 +14535,7 @@
       <c r="T583" s="11"/>
       <c r="U583" s="11"/>
     </row>
-    <row r="584" spans="1:21" ht="18" customHeight="1">
+    <row r="584" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A584" s="1"/>
       <c r="B584" s="27"/>
       <c r="C584" s="17"/>
@@ -14590,7 +14558,7 @@
       <c r="T584" s="11"/>
       <c r="U584" s="11"/>
     </row>
-    <row r="585" spans="1:21" ht="18" customHeight="1">
+    <row r="585" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A585" s="1"/>
       <c r="B585" s="27"/>
       <c r="C585" s="17"/>
@@ -14613,7 +14581,7 @@
       <c r="T585" s="11"/>
       <c r="U585" s="11"/>
     </row>
-    <row r="586" spans="1:21" ht="18" customHeight="1">
+    <row r="586" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A586" s="1"/>
       <c r="B586" s="27"/>
       <c r="C586" s="17"/>
@@ -14636,7 +14604,7 @@
       <c r="T586" s="11"/>
       <c r="U586" s="11"/>
     </row>
-    <row r="587" spans="1:21" ht="18" customHeight="1">
+    <row r="587" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A587" s="1"/>
       <c r="B587" s="27"/>
       <c r="C587" s="17"/>
@@ -14659,7 +14627,7 @@
       <c r="T587" s="11"/>
       <c r="U587" s="11"/>
     </row>
-    <row r="588" spans="1:21" ht="18" customHeight="1">
+    <row r="588" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A588" s="1"/>
       <c r="B588" s="27"/>
       <c r="C588" s="17"/>
@@ -14682,7 +14650,7 @@
       <c r="T588" s="11"/>
       <c r="U588" s="11"/>
     </row>
-    <row r="589" spans="1:21" ht="18" customHeight="1">
+    <row r="589" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A589" s="1"/>
       <c r="B589" s="27"/>
       <c r="C589" s="17"/>
@@ -14705,7 +14673,7 @@
       <c r="T589" s="11"/>
       <c r="U589" s="11"/>
     </row>
-    <row r="590" spans="1:21" ht="18" customHeight="1">
+    <row r="590" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A590" s="1"/>
       <c r="B590" s="27"/>
       <c r="C590" s="17"/>
@@ -14728,7 +14696,7 @@
       <c r="T590" s="11"/>
       <c r="U590" s="11"/>
     </row>
-    <row r="591" spans="1:21" ht="18" customHeight="1">
+    <row r="591" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A591" s="1"/>
       <c r="B591" s="27"/>
       <c r="C591" s="17"/>
@@ -14751,7 +14719,7 @@
       <c r="T591" s="11"/>
       <c r="U591" s="11"/>
     </row>
-    <row r="592" spans="1:21" ht="18" customHeight="1">
+    <row r="592" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A592" s="1"/>
       <c r="B592" s="27"/>
       <c r="C592" s="17"/>
@@ -14774,7 +14742,7 @@
       <c r="T592" s="11"/>
       <c r="U592" s="11"/>
     </row>
-    <row r="593" spans="1:21" ht="18" customHeight="1">
+    <row r="593" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A593" s="1"/>
       <c r="B593" s="27"/>
       <c r="C593" s="17"/>
@@ -14797,7 +14765,7 @@
       <c r="T593" s="11"/>
       <c r="U593" s="11"/>
     </row>
-    <row r="594" spans="1:21" ht="18" customHeight="1">
+    <row r="594" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A594" s="1"/>
       <c r="B594" s="27"/>
       <c r="C594" s="17"/>
@@ -14820,7 +14788,7 @@
       <c r="T594" s="11"/>
       <c r="U594" s="11"/>
     </row>
-    <row r="595" spans="1:21" ht="18" customHeight="1">
+    <row r="595" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A595" s="1"/>
       <c r="B595" s="27"/>
       <c r="C595" s="17"/>
@@ -14843,7 +14811,7 @@
       <c r="T595" s="11"/>
       <c r="U595" s="11"/>
     </row>
-    <row r="596" spans="1:21" ht="18" customHeight="1">
+    <row r="596" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A596" s="1"/>
       <c r="B596" s="27"/>
       <c r="C596" s="17"/>
@@ -14866,7 +14834,7 @@
       <c r="T596" s="11"/>
       <c r="U596" s="11"/>
     </row>
-    <row r="597" spans="1:21" ht="18" customHeight="1">
+    <row r="597" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A597" s="1"/>
       <c r="B597" s="27"/>
       <c r="C597" s="17"/>
@@ -14889,7 +14857,7 @@
       <c r="T597" s="11"/>
       <c r="U597" s="11"/>
     </row>
-    <row r="598" spans="1:21" ht="18" customHeight="1">
+    <row r="598" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A598" s="1"/>
       <c r="B598" s="27"/>
       <c r="C598" s="17"/>
@@ -14912,7 +14880,7 @@
       <c r="T598" s="11"/>
       <c r="U598" s="11"/>
     </row>
-    <row r="599" spans="1:21" ht="18" customHeight="1">
+    <row r="599" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A599" s="1"/>
       <c r="B599" s="27"/>
       <c r="C599" s="17"/>
@@ -14935,7 +14903,7 @@
       <c r="T599" s="11"/>
       <c r="U599" s="11"/>
     </row>
-    <row r="600" spans="1:21" ht="18" customHeight="1">
+    <row r="600" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A600" s="1"/>
       <c r="B600" s="27"/>
       <c r="C600" s="17"/>
@@ -14958,7 +14926,7 @@
       <c r="T600" s="11"/>
       <c r="U600" s="11"/>
     </row>
-    <row r="601" spans="1:21" ht="18" customHeight="1">
+    <row r="601" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A601" s="1"/>
       <c r="B601" s="27"/>
       <c r="C601" s="17"/>
@@ -14981,7 +14949,7 @@
       <c r="T601" s="11"/>
       <c r="U601" s="11"/>
     </row>
-    <row r="602" spans="1:21" ht="18" customHeight="1">
+    <row r="602" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A602" s="1"/>
       <c r="B602" s="27"/>
       <c r="C602" s="17"/>
@@ -15004,7 +14972,7 @@
       <c r="T602" s="11"/>
       <c r="U602" s="11"/>
     </row>
-    <row r="603" spans="1:21" ht="18" customHeight="1">
+    <row r="603" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A603" s="1"/>
       <c r="B603" s="27"/>
       <c r="C603" s="17"/>
@@ -15027,7 +14995,7 @@
       <c r="T603" s="11"/>
       <c r="U603" s="11"/>
     </row>
-    <row r="604" spans="1:21" ht="18" customHeight="1">
+    <row r="604" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A604" s="1"/>
       <c r="B604" s="27"/>
       <c r="C604" s="17"/>
@@ -15050,7 +15018,7 @@
       <c r="T604" s="11"/>
       <c r="U604" s="11"/>
     </row>
-    <row r="605" spans="1:21" ht="18" customHeight="1">
+    <row r="605" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A605" s="1"/>
       <c r="B605" s="27"/>
       <c r="C605" s="17"/>
@@ -15073,7 +15041,7 @@
       <c r="T605" s="11"/>
       <c r="U605" s="11"/>
     </row>
-    <row r="606" spans="1:21" ht="18" customHeight="1">
+    <row r="606" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A606" s="1"/>
       <c r="B606" s="27"/>
       <c r="C606" s="17"/>
@@ -15096,7 +15064,7 @@
       <c r="T606" s="11"/>
       <c r="U606" s="11"/>
     </row>
-    <row r="607" spans="1:21" ht="18" customHeight="1">
+    <row r="607" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A607" s="1"/>
       <c r="B607" s="27"/>
       <c r="C607" s="17"/>
@@ -15119,7 +15087,7 @@
       <c r="T607" s="11"/>
       <c r="U607" s="11"/>
     </row>
-    <row r="608" spans="1:21" ht="18" customHeight="1">
+    <row r="608" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A608" s="1"/>
       <c r="B608" s="27"/>
       <c r="C608" s="17"/>
@@ -15142,7 +15110,7 @@
       <c r="T608" s="11"/>
       <c r="U608" s="11"/>
     </row>
-    <row r="609" spans="1:21" ht="18" customHeight="1">
+    <row r="609" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A609" s="1"/>
       <c r="B609" s="27"/>
       <c r="C609" s="17"/>
@@ -15165,7 +15133,7 @@
       <c r="T609" s="11"/>
       <c r="U609" s="11"/>
     </row>
-    <row r="610" spans="1:21" ht="18" customHeight="1">
+    <row r="610" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A610" s="1"/>
       <c r="B610" s="27"/>
       <c r="C610" s="17"/>
@@ -15188,7 +15156,7 @@
       <c r="T610" s="11"/>
       <c r="U610" s="11"/>
     </row>
-    <row r="611" spans="1:21" ht="18" customHeight="1">
+    <row r="611" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A611" s="1"/>
       <c r="B611" s="27"/>
       <c r="C611" s="17"/>
@@ -15211,7 +15179,7 @@
       <c r="T611" s="11"/>
       <c r="U611" s="11"/>
     </row>
-    <row r="612" spans="1:21" ht="18" customHeight="1">
+    <row r="612" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A612" s="1"/>
       <c r="B612" s="27"/>
       <c r="C612" s="17"/>
@@ -15234,7 +15202,7 @@
       <c r="T612" s="11"/>
       <c r="U612" s="11"/>
     </row>
-    <row r="613" spans="1:21" ht="18" customHeight="1">
+    <row r="613" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A613" s="1"/>
       <c r="B613" s="27"/>
       <c r="C613" s="17"/>
@@ -15257,7 +15225,7 @@
       <c r="T613" s="11"/>
       <c r="U613" s="11"/>
     </row>
-    <row r="614" spans="1:21" ht="18" customHeight="1">
+    <row r="614" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A614" s="1"/>
       <c r="B614" s="27"/>
       <c r="C614" s="17"/>
@@ -15280,7 +15248,7 @@
       <c r="T614" s="11"/>
       <c r="U614" s="11"/>
     </row>
-    <row r="615" spans="1:21" ht="18" customHeight="1">
+    <row r="615" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A615" s="1"/>
       <c r="B615" s="27"/>
       <c r="C615" s="17"/>
@@ -15303,7 +15271,7 @@
       <c r="T615" s="11"/>
       <c r="U615" s="11"/>
     </row>
-    <row r="616" spans="1:21" ht="18" customHeight="1">
+    <row r="616" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A616" s="1"/>
       <c r="B616" s="27"/>
       <c r="C616" s="17"/>
@@ -15326,7 +15294,7 @@
       <c r="T616" s="11"/>
       <c r="U616" s="11"/>
     </row>
-    <row r="617" spans="1:21" ht="18" customHeight="1">
+    <row r="617" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A617" s="1"/>
       <c r="B617" s="27"/>
       <c r="C617" s="17"/>
@@ -15349,7 +15317,7 @@
       <c r="T617" s="11"/>
       <c r="U617" s="11"/>
     </row>
-    <row r="618" spans="1:21" ht="18" customHeight="1">
+    <row r="618" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A618" s="1"/>
       <c r="B618" s="27"/>
       <c r="C618" s="17"/>
@@ -15372,7 +15340,7 @@
       <c r="T618" s="11"/>
       <c r="U618" s="11"/>
     </row>
-    <row r="619" spans="1:21" ht="18" customHeight="1">
+    <row r="619" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A619" s="1"/>
       <c r="B619" s="27"/>
       <c r="C619" s="17"/>
@@ -15395,7 +15363,7 @@
       <c r="T619" s="11"/>
       <c r="U619" s="11"/>
     </row>
-    <row r="620" spans="1:21" ht="18" customHeight="1">
+    <row r="620" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A620" s="1"/>
       <c r="B620" s="27"/>
       <c r="C620" s="17"/>
@@ -15418,7 +15386,7 @@
       <c r="T620" s="11"/>
       <c r="U620" s="11"/>
     </row>
-    <row r="621" spans="1:21" ht="18" customHeight="1">
+    <row r="621" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A621" s="1"/>
       <c r="B621" s="27"/>
       <c r="C621" s="17"/>
@@ -15441,7 +15409,7 @@
       <c r="T621" s="11"/>
       <c r="U621" s="11"/>
     </row>
-    <row r="622" spans="1:21" ht="18" customHeight="1">
+    <row r="622" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A622" s="1"/>
       <c r="B622" s="27"/>
       <c r="C622" s="17"/>
@@ -15464,7 +15432,7 @@
       <c r="T622" s="11"/>
       <c r="U622" s="11"/>
     </row>
-    <row r="623" spans="1:21" ht="18" customHeight="1">
+    <row r="623" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A623" s="1"/>
       <c r="B623" s="27"/>
       <c r="C623" s="17"/>
@@ -15487,7 +15455,7 @@
       <c r="T623" s="11"/>
       <c r="U623" s="11"/>
     </row>
-    <row r="624" spans="1:21" ht="18" customHeight="1">
+    <row r="624" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A624" s="1"/>
       <c r="B624" s="27"/>
       <c r="C624" s="17"/>
@@ -15510,7 +15478,7 @@
       <c r="T624" s="11"/>
       <c r="U624" s="11"/>
     </row>
-    <row r="625" spans="1:21" ht="18" customHeight="1">
+    <row r="625" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A625" s="1"/>
       <c r="B625" s="27"/>
       <c r="C625" s="17"/>
@@ -15533,7 +15501,7 @@
       <c r="T625" s="11"/>
       <c r="U625" s="11"/>
     </row>
-    <row r="626" spans="1:21" ht="18" customHeight="1">
+    <row r="626" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A626" s="1"/>
       <c r="B626" s="27"/>
       <c r="C626" s="17"/>
@@ -15556,7 +15524,7 @@
       <c r="T626" s="11"/>
       <c r="U626" s="11"/>
     </row>
-    <row r="627" spans="1:21" ht="18" customHeight="1">
+    <row r="627" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A627" s="1"/>
       <c r="B627" s="27"/>
       <c r="C627" s="17"/>
@@ -15579,7 +15547,7 @@
       <c r="T627" s="11"/>
       <c r="U627" s="11"/>
     </row>
-    <row r="628" spans="1:21" ht="18" customHeight="1">
+    <row r="628" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A628" s="1"/>
       <c r="B628" s="27"/>
       <c r="C628" s="17"/>
@@ -15602,7 +15570,7 @@
       <c r="T628" s="11"/>
       <c r="U628" s="11"/>
     </row>
-    <row r="629" spans="1:21" ht="18" customHeight="1">
+    <row r="629" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A629" s="1"/>
       <c r="B629" s="27"/>
       <c r="C629" s="17"/>
@@ -15625,7 +15593,7 @@
       <c r="T629" s="11"/>
       <c r="U629" s="11"/>
     </row>
-    <row r="630" spans="1:21" ht="18" customHeight="1">
+    <row r="630" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A630" s="1"/>
       <c r="B630" s="27"/>
       <c r="C630" s="17"/>
@@ -15648,7 +15616,7 @@
       <c r="T630" s="11"/>
       <c r="U630" s="11"/>
     </row>
-    <row r="631" spans="1:21" ht="18" customHeight="1">
+    <row r="631" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A631" s="1"/>
       <c r="B631" s="27"/>
       <c r="C631" s="17"/>
@@ -15671,7 +15639,7 @@
       <c r="T631" s="11"/>
       <c r="U631" s="11"/>
     </row>
-    <row r="632" spans="1:21" ht="18" customHeight="1">
+    <row r="632" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A632" s="1"/>
       <c r="B632" s="27"/>
       <c r="C632" s="17"/>
@@ -15694,7 +15662,7 @@
       <c r="T632" s="11"/>
       <c r="U632" s="11"/>
     </row>
-    <row r="633" spans="1:21" ht="18" customHeight="1">
+    <row r="633" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A633" s="1"/>
       <c r="B633" s="27"/>
       <c r="C633" s="17"/>
@@ -15717,7 +15685,7 @@
       <c r="T633" s="11"/>
       <c r="U633" s="11"/>
     </row>
-    <row r="634" spans="1:21" ht="18" customHeight="1">
+    <row r="634" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A634" s="1"/>
       <c r="B634" s="27"/>
       <c r="C634" s="17"/>
@@ -15740,7 +15708,7 @@
       <c r="T634" s="11"/>
       <c r="U634" s="11"/>
     </row>
-    <row r="635" spans="1:21" ht="18" customHeight="1">
+    <row r="635" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A635" s="1"/>
       <c r="B635" s="27"/>
       <c r="C635" s="17"/>
@@ -15763,7 +15731,7 @@
       <c r="T635" s="11"/>
       <c r="U635" s="11"/>
     </row>
-    <row r="636" spans="1:21" ht="18" customHeight="1">
+    <row r="636" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A636" s="1"/>
       <c r="B636" s="27"/>
       <c r="C636" s="17"/>
@@ -15786,7 +15754,7 @@
       <c r="T636" s="11"/>
       <c r="U636" s="11"/>
     </row>
-    <row r="637" spans="1:21" ht="18" customHeight="1">
+    <row r="637" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A637" s="1"/>
       <c r="B637" s="27"/>
       <c r="C637" s="17"/>
@@ -15809,7 +15777,7 @@
       <c r="T637" s="11"/>
       <c r="U637" s="11"/>
     </row>
-    <row r="638" spans="1:21" ht="18" customHeight="1">
+    <row r="638" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A638" s="1"/>
       <c r="B638" s="27"/>
       <c r="C638" s="17"/>
@@ -15832,7 +15800,7 @@
       <c r="T638" s="11"/>
       <c r="U638" s="11"/>
     </row>
-    <row r="639" spans="1:21" ht="18" customHeight="1">
+    <row r="639" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A639" s="1"/>
       <c r="B639" s="27"/>
       <c r="C639" s="17"/>
@@ -15855,7 +15823,7 @@
       <c r="T639" s="11"/>
       <c r="U639" s="11"/>
     </row>
-    <row r="640" spans="1:21" ht="18" customHeight="1">
+    <row r="640" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A640" s="1"/>
       <c r="B640" s="27"/>
       <c r="C640" s="17"/>
@@ -15878,7 +15846,7 @@
       <c r="T640" s="11"/>
       <c r="U640" s="11"/>
     </row>
-    <row r="641" spans="1:21" ht="18" customHeight="1">
+    <row r="641" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A641" s="1"/>
       <c r="B641" s="27"/>
       <c r="C641" s="17"/>
@@ -15901,7 +15869,7 @@
       <c r="T641" s="11"/>
       <c r="U641" s="11"/>
     </row>
-    <row r="642" spans="1:21" ht="18" customHeight="1">
+    <row r="642" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A642" s="1"/>
       <c r="B642" s="27"/>
       <c r="C642" s="17"/>
@@ -15924,7 +15892,7 @@
       <c r="T642" s="11"/>
       <c r="U642" s="11"/>
     </row>
-    <row r="643" spans="1:21" ht="18" customHeight="1">
+    <row r="643" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A643" s="1"/>
       <c r="B643" s="27"/>
       <c r="C643" s="17"/>
@@ -15947,7 +15915,7 @@
       <c r="T643" s="11"/>
       <c r="U643" s="11"/>
     </row>
-    <row r="644" spans="1:21" ht="18" customHeight="1">
+    <row r="644" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A644" s="1"/>
       <c r="B644" s="27"/>
       <c r="C644" s="17"/>
@@ -15970,7 +15938,7 @@
       <c r="T644" s="11"/>
       <c r="U644" s="11"/>
     </row>
-    <row r="645" spans="1:21" ht="18" customHeight="1">
+    <row r="645" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A645" s="1"/>
       <c r="B645" s="27"/>
       <c r="C645" s="17"/>
@@ -15993,7 +15961,7 @@
       <c r="T645" s="11"/>
       <c r="U645" s="11"/>
     </row>
-    <row r="646" spans="1:21" ht="18" customHeight="1">
+    <row r="646" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A646" s="1"/>
       <c r="B646" s="27"/>
       <c r="C646" s="17"/>
@@ -16016,7 +15984,7 @@
       <c r="T646" s="11"/>
       <c r="U646" s="11"/>
     </row>
-    <row r="647" spans="1:21" ht="18" customHeight="1">
+    <row r="647" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A647" s="1"/>
       <c r="B647" s="27"/>
       <c r="C647" s="17"/>
@@ -16039,7 +16007,7 @@
       <c r="T647" s="11"/>
       <c r="U647" s="11"/>
     </row>
-    <row r="648" spans="1:21" ht="18" customHeight="1">
+    <row r="648" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A648" s="1"/>
       <c r="B648" s="27"/>
       <c r="C648" s="17"/>
@@ -16062,7 +16030,7 @@
       <c r="T648" s="11"/>
       <c r="U648" s="11"/>
     </row>
-    <row r="649" spans="1:21" ht="18" customHeight="1">
+    <row r="649" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A649" s="1"/>
       <c r="B649" s="27"/>
       <c r="C649" s="17"/>
@@ -16085,7 +16053,7 @@
       <c r="T649" s="11"/>
       <c r="U649" s="11"/>
     </row>
-    <row r="650" spans="1:21" ht="18" customHeight="1">
+    <row r="650" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A650" s="1"/>
       <c r="B650" s="27"/>
       <c r="C650" s="17"/>
@@ -16108,7 +16076,7 @@
       <c r="T650" s="11"/>
       <c r="U650" s="11"/>
     </row>
-    <row r="651" spans="1:21" ht="18" customHeight="1">
+    <row r="651" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A651" s="1"/>
       <c r="B651" s="27"/>
       <c r="C651" s="17"/>
@@ -16131,7 +16099,7 @@
       <c r="T651" s="11"/>
       <c r="U651" s="11"/>
     </row>
-    <row r="652" spans="1:21" ht="18" customHeight="1">
+    <row r="652" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A652" s="1"/>
       <c r="B652" s="27"/>
       <c r="C652" s="17"/>
@@ -16154,7 +16122,7 @@
       <c r="T652" s="11"/>
       <c r="U652" s="11"/>
     </row>
-    <row r="653" spans="1:21" ht="18" customHeight="1">
+    <row r="653" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A653" s="1"/>
       <c r="B653" s="27"/>
       <c r="C653" s="17"/>
@@ -16177,7 +16145,7 @@
       <c r="T653" s="11"/>
       <c r="U653" s="11"/>
     </row>
-    <row r="654" spans="1:21" ht="18" customHeight="1">
+    <row r="654" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A654" s="1"/>
       <c r="B654" s="27"/>
       <c r="C654" s="17"/>
@@ -16200,7 +16168,7 @@
       <c r="T654" s="11"/>
       <c r="U654" s="11"/>
     </row>
-    <row r="655" spans="1:21" ht="18" customHeight="1">
+    <row r="655" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A655" s="1"/>
       <c r="B655" s="27"/>
       <c r="C655" s="17"/>
@@ -16223,7 +16191,7 @@
       <c r="T655" s="11"/>
       <c r="U655" s="11"/>
     </row>
-    <row r="656" spans="1:21" ht="18" customHeight="1">
+    <row r="656" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A656" s="1"/>
       <c r="B656" s="27"/>
       <c r="C656" s="17"/>
@@ -16246,7 +16214,7 @@
       <c r="T656" s="11"/>
       <c r="U656" s="11"/>
     </row>
-    <row r="657" spans="1:21" ht="18" customHeight="1">
+    <row r="657" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A657" s="1"/>
       <c r="B657" s="27"/>
       <c r="C657" s="17"/>
@@ -16269,7 +16237,7 @@
       <c r="T657" s="11"/>
       <c r="U657" s="11"/>
     </row>
-    <row r="658" spans="1:21" ht="18" customHeight="1">
+    <row r="658" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A658" s="1"/>
       <c r="B658" s="27"/>
       <c r="C658" s="17"/>
@@ -16292,7 +16260,7 @@
       <c r="T658" s="11"/>
       <c r="U658" s="11"/>
     </row>
-    <row r="659" spans="1:21" ht="18" customHeight="1">
+    <row r="659" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A659" s="1"/>
       <c r="B659" s="27"/>
       <c r="C659" s="17"/>
@@ -16315,7 +16283,7 @@
       <c r="T659" s="11"/>
       <c r="U659" s="11"/>
     </row>
-    <row r="660" spans="1:21" ht="18" customHeight="1">
+    <row r="660" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A660" s="1"/>
       <c r="B660" s="27"/>
       <c r="C660" s="17"/>
@@ -16338,7 +16306,7 @@
       <c r="T660" s="11"/>
       <c r="U660" s="11"/>
     </row>
-    <row r="661" spans="1:21" ht="18" customHeight="1">
+    <row r="661" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A661" s="1"/>
       <c r="B661" s="27"/>
       <c r="C661" s="17"/>
@@ -16361,7 +16329,7 @@
       <c r="T661" s="11"/>
       <c r="U661" s="11"/>
     </row>
-    <row r="662" spans="1:21" ht="18" customHeight="1">
+    <row r="662" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A662" s="1"/>
       <c r="B662" s="27"/>
       <c r="C662" s="17"/>
@@ -16384,7 +16352,7 @@
       <c r="T662" s="11"/>
       <c r="U662" s="11"/>
     </row>
-    <row r="663" spans="1:21" ht="18" customHeight="1">
+    <row r="663" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A663" s="1"/>
       <c r="B663" s="27"/>
       <c r="C663" s="17"/>
@@ -16407,7 +16375,7 @@
       <c r="T663" s="11"/>
       <c r="U663" s="11"/>
     </row>
-    <row r="664" spans="1:21" ht="18" customHeight="1">
+    <row r="664" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A664" s="1"/>
       <c r="B664" s="27"/>
       <c r="C664" s="17"/>
@@ -16430,7 +16398,7 @@
       <c r="T664" s="11"/>
       <c r="U664" s="11"/>
     </row>
-    <row r="665" spans="1:21" ht="18" customHeight="1">
+    <row r="665" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A665" s="1"/>
       <c r="B665" s="27"/>
       <c r="C665" s="17"/>
@@ -16453,7 +16421,7 @@
       <c r="T665" s="11"/>
       <c r="U665" s="11"/>
     </row>
-    <row r="666" spans="1:21" ht="18" customHeight="1">
+    <row r="666" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A666" s="1"/>
       <c r="B666" s="27"/>
       <c r="C666" s="17"/>
@@ -16476,7 +16444,7 @@
       <c r="T666" s="11"/>
       <c r="U666" s="11"/>
     </row>
-    <row r="667" spans="1:21" ht="18" customHeight="1">
+    <row r="667" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A667" s="1"/>
       <c r="B667" s="27"/>
       <c r="C667" s="17"/>
@@ -16499,7 +16467,7 @@
       <c r="T667" s="11"/>
       <c r="U667" s="11"/>
     </row>
-    <row r="668" spans="1:21" ht="18" customHeight="1">
+    <row r="668" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A668" s="1"/>
       <c r="B668" s="27"/>
       <c r="C668" s="17"/>
@@ -16522,7 +16490,7 @@
       <c r="T668" s="11"/>
       <c r="U668" s="11"/>
     </row>
-    <row r="669" spans="1:21" ht="18" customHeight="1">
+    <row r="669" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A669" s="1"/>
       <c r="B669" s="27"/>
       <c r="C669" s="17"/>
@@ -16545,7 +16513,7 @@
       <c r="T669" s="11"/>
       <c r="U669" s="11"/>
     </row>
-    <row r="670" spans="1:21" ht="18" customHeight="1">
+    <row r="670" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A670" s="1"/>
       <c r="B670" s="27"/>
       <c r="C670" s="17"/>
@@ -16568,7 +16536,7 @@
       <c r="T670" s="11"/>
       <c r="U670" s="11"/>
     </row>
-    <row r="671" spans="1:21" ht="18" customHeight="1">
+    <row r="671" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A671" s="1"/>
       <c r="B671" s="27"/>
       <c r="C671" s="17"/>
@@ -16591,7 +16559,7 @@
       <c r="T671" s="11"/>
       <c r="U671" s="11"/>
     </row>
-    <row r="672" spans="1:21" ht="18" customHeight="1">
+    <row r="672" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A672" s="1"/>
       <c r="B672" s="27"/>
       <c r="C672" s="17"/>
@@ -16614,7 +16582,7 @@
       <c r="T672" s="11"/>
       <c r="U672" s="11"/>
     </row>
-    <row r="673" spans="1:21" ht="18" customHeight="1">
+    <row r="673" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A673" s="1"/>
       <c r="B673" s="27"/>
       <c r="C673" s="17"/>
@@ -16637,7 +16605,7 @@
       <c r="T673" s="11"/>
       <c r="U673" s="11"/>
     </row>
-    <row r="674" spans="1:21" ht="18" customHeight="1">
+    <row r="674" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A674" s="1"/>
       <c r="B674" s="27"/>
       <c r="C674" s="17"/>
@@ -16660,7 +16628,7 @@
       <c r="T674" s="11"/>
       <c r="U674" s="11"/>
     </row>
-    <row r="675" spans="1:21" ht="18" customHeight="1">
+    <row r="675" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A675" s="1"/>
       <c r="B675" s="27"/>
       <c r="C675" s="17"/>
@@ -16683,7 +16651,7 @@
       <c r="T675" s="11"/>
       <c r="U675" s="11"/>
     </row>
-    <row r="676" spans="1:21" ht="18" customHeight="1">
+    <row r="676" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A676" s="1"/>
       <c r="B676" s="27"/>
       <c r="C676" s="17"/>
@@ -16706,7 +16674,7 @@
       <c r="T676" s="11"/>
       <c r="U676" s="11"/>
     </row>
-    <row r="677" spans="1:21" ht="18" customHeight="1">
+    <row r="677" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A677" s="1"/>
       <c r="B677" s="27"/>
       <c r="C677" s="17"/>
@@ -16729,7 +16697,7 @@
       <c r="T677" s="11"/>
       <c r="U677" s="11"/>
     </row>
-    <row r="678" spans="1:21" ht="18" customHeight="1">
+    <row r="678" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A678" s="1"/>
       <c r="B678" s="27"/>
       <c r="C678" s="17"/>
@@ -16752,7 +16720,7 @@
       <c r="T678" s="11"/>
       <c r="U678" s="11"/>
     </row>
-    <row r="679" spans="1:21" ht="18" customHeight="1">
+    <row r="679" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A679" s="1"/>
       <c r="B679" s="27"/>
       <c r="C679" s="17"/>
@@ -16775,7 +16743,7 @@
       <c r="T679" s="11"/>
       <c r="U679" s="11"/>
     </row>
-    <row r="680" spans="1:21" ht="18" customHeight="1">
+    <row r="680" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A680" s="1"/>
       <c r="B680" s="27"/>
       <c r="C680" s="17"/>
@@ -16798,7 +16766,7 @@
       <c r="T680" s="11"/>
       <c r="U680" s="11"/>
     </row>
-    <row r="681" spans="1:21" ht="18" customHeight="1">
+    <row r="681" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A681" s="1"/>
       <c r="B681" s="27"/>
       <c r="C681" s="17"/>
@@ -16821,7 +16789,7 @@
       <c r="T681" s="11"/>
       <c r="U681" s="11"/>
     </row>
-    <row r="682" spans="1:21" ht="18" customHeight="1">
+    <row r="682" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A682" s="1"/>
       <c r="B682" s="27"/>
       <c r="C682" s="17"/>
@@ -16844,7 +16812,7 @@
       <c r="T682" s="11"/>
       <c r="U682" s="11"/>
     </row>
-    <row r="683" spans="1:21" ht="18" customHeight="1">
+    <row r="683" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A683" s="1"/>
       <c r="B683" s="27"/>
       <c r="C683" s="17"/>
@@ -16867,7 +16835,7 @@
       <c r="T683" s="11"/>
       <c r="U683" s="11"/>
     </row>
-    <row r="684" spans="1:21" ht="18" customHeight="1">
+    <row r="684" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A684" s="1"/>
       <c r="B684" s="27"/>
       <c r="C684" s="17"/>
@@ -16890,7 +16858,7 @@
       <c r="T684" s="11"/>
       <c r="U684" s="11"/>
     </row>
-    <row r="685" spans="1:21" ht="18" customHeight="1">
+    <row r="685" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A685" s="1"/>
       <c r="B685" s="27"/>
       <c r="C685" s="17"/>
@@ -16913,7 +16881,7 @@
       <c r="T685" s="11"/>
       <c r="U685" s="11"/>
     </row>
-    <row r="686" spans="1:21" ht="18" customHeight="1">
+    <row r="686" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A686" s="1"/>
       <c r="B686" s="27"/>
       <c r="C686" s="17"/>
@@ -16936,7 +16904,7 @@
       <c r="T686" s="11"/>
       <c r="U686" s="11"/>
     </row>
-    <row r="687" spans="1:21" ht="18" customHeight="1">
+    <row r="687" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A687" s="1"/>
       <c r="B687" s="27"/>
       <c r="C687" s="17"/>
@@ -16959,7 +16927,7 @@
       <c r="T687" s="11"/>
       <c r="U687" s="11"/>
     </row>
-    <row r="688" spans="1:21" ht="18" customHeight="1">
+    <row r="688" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A688" s="1"/>
       <c r="B688" s="27"/>
       <c r="C688" s="17"/>
@@ -16982,7 +16950,7 @@
       <c r="T688" s="11"/>
       <c r="U688" s="11"/>
     </row>
-    <row r="689" spans="1:21" ht="18" customHeight="1">
+    <row r="689" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A689" s="1"/>
       <c r="B689" s="27"/>
       <c r="C689" s="17"/>
@@ -17005,7 +16973,7 @@
       <c r="T689" s="11"/>
       <c r="U689" s="11"/>
     </row>
-    <row r="690" spans="1:21" ht="18" customHeight="1">
+    <row r="690" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A690" s="1"/>
       <c r="B690" s="27"/>
       <c r="C690" s="17"/>
@@ -17028,7 +16996,7 @@
       <c r="T690" s="11"/>
       <c r="U690" s="11"/>
     </row>
-    <row r="691" spans="1:21" ht="18" customHeight="1">
+    <row r="691" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A691" s="1"/>
       <c r="B691" s="27"/>
       <c r="C691" s="17"/>
@@ -17051,7 +17019,7 @@
       <c r="T691" s="11"/>
       <c r="U691" s="11"/>
     </row>
-    <row r="692" spans="1:21" ht="18" customHeight="1">
+    <row r="692" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A692" s="1"/>
       <c r="B692" s="27"/>
       <c r="C692" s="17"/>
@@ -17074,7 +17042,7 @@
       <c r="T692" s="11"/>
       <c r="U692" s="11"/>
     </row>
-    <row r="693" spans="1:21" ht="18" customHeight="1">
+    <row r="693" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A693" s="1"/>
       <c r="B693" s="27"/>
       <c r="C693" s="17"/>
@@ -17097,7 +17065,7 @@
       <c r="T693" s="11"/>
       <c r="U693" s="11"/>
     </row>
-    <row r="694" spans="1:21" ht="18" customHeight="1">
+    <row r="694" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A694" s="1"/>
       <c r="B694" s="27"/>
       <c r="C694" s="17"/>
@@ -17120,7 +17088,7 @@
       <c r="T694" s="11"/>
       <c r="U694" s="11"/>
     </row>
-    <row r="695" spans="1:21" ht="18" customHeight="1">
+    <row r="695" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A695" s="1"/>
       <c r="B695" s="27"/>
       <c r="C695" s="17"/>
@@ -17143,7 +17111,7 @@
       <c r="T695" s="11"/>
       <c r="U695" s="11"/>
     </row>
-    <row r="696" spans="1:21" ht="18" customHeight="1">
+    <row r="696" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A696" s="1"/>
       <c r="B696" s="27"/>
       <c r="C696" s="17"/>
@@ -17166,7 +17134,7 @@
       <c r="T696" s="11"/>
       <c r="U696" s="11"/>
     </row>
-    <row r="697" spans="1:21" ht="18" customHeight="1">
+    <row r="697" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A697" s="1"/>
       <c r="B697" s="27"/>
       <c r="C697" s="17"/>
@@ -17189,7 +17157,7 @@
       <c r="T697" s="11"/>
       <c r="U697" s="11"/>
     </row>
-    <row r="698" spans="1:21" ht="18" customHeight="1">
+    <row r="698" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A698" s="1"/>
       <c r="B698" s="27"/>
       <c r="C698" s="17"/>
@@ -17212,7 +17180,7 @@
       <c r="T698" s="11"/>
       <c r="U698" s="11"/>
     </row>
-    <row r="699" spans="1:21" ht="18" customHeight="1">
+    <row r="699" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A699" s="1"/>
       <c r="B699" s="27"/>
       <c r="C699" s="17"/>
@@ -17235,7 +17203,7 @@
       <c r="T699" s="11"/>
       <c r="U699" s="11"/>
     </row>
-    <row r="700" spans="1:21" ht="18" customHeight="1">
+    <row r="700" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A700" s="1"/>
       <c r="B700" s="27"/>
       <c r="C700" s="17"/>
@@ -17258,7 +17226,7 @@
       <c r="T700" s="11"/>
       <c r="U700" s="11"/>
     </row>
-    <row r="701" spans="1:21" ht="18" customHeight="1">
+    <row r="701" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A701" s="1"/>
       <c r="B701" s="27"/>
       <c r="C701" s="17"/>
@@ -17281,7 +17249,7 @@
       <c r="T701" s="11"/>
       <c r="U701" s="11"/>
     </row>
-    <row r="702" spans="1:21" ht="18" customHeight="1">
+    <row r="702" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A702" s="1"/>
       <c r="B702" s="27"/>
       <c r="C702" s="17"/>
@@ -17304,7 +17272,7 @@
       <c r="T702" s="11"/>
       <c r="U702" s="11"/>
     </row>
-    <row r="703" spans="1:21" ht="18" customHeight="1">
+    <row r="703" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A703" s="1"/>
       <c r="B703" s="27"/>
       <c r="C703" s="17"/>
@@ -17327,7 +17295,7 @@
       <c r="T703" s="11"/>
       <c r="U703" s="11"/>
     </row>
-    <row r="704" spans="1:21" ht="18" customHeight="1">
+    <row r="704" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A704" s="1"/>
       <c r="B704" s="27"/>
       <c r="C704" s="17"/>
@@ -17350,7 +17318,7 @@
       <c r="T704" s="11"/>
       <c r="U704" s="11"/>
     </row>
-    <row r="705" spans="1:21" ht="18" customHeight="1">
+    <row r="705" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A705" s="1"/>
       <c r="B705" s="27"/>
       <c r="C705" s="17"/>
@@ -17373,7 +17341,7 @@
       <c r="T705" s="11"/>
       <c r="U705" s="11"/>
     </row>
-    <row r="706" spans="1:21" ht="18" customHeight="1">
+    <row r="706" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A706" s="1"/>
       <c r="B706" s="27"/>
       <c r="C706" s="17"/>
@@ -17396,7 +17364,7 @@
       <c r="T706" s="11"/>
       <c r="U706" s="11"/>
     </row>
-    <row r="707" spans="1:21" ht="18" customHeight="1">
+    <row r="707" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A707" s="1"/>
       <c r="B707" s="27"/>
       <c r="C707" s="17"/>
@@ -17419,7 +17387,7 @@
       <c r="T707" s="11"/>
       <c r="U707" s="11"/>
     </row>
-    <row r="708" spans="1:21" ht="18" customHeight="1">
+    <row r="708" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A708" s="1"/>
       <c r="B708" s="27"/>
       <c r="C708" s="17"/>
@@ -17442,7 +17410,7 @@
       <c r="T708" s="11"/>
       <c r="U708" s="11"/>
     </row>
-    <row r="709" spans="1:21" ht="18" customHeight="1">
+    <row r="709" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A709" s="1"/>
       <c r="B709" s="27"/>
       <c r="C709" s="17"/>
@@ -17465,7 +17433,7 @@
       <c r="T709" s="11"/>
       <c r="U709" s="11"/>
     </row>
-    <row r="710" spans="1:21" ht="18" customHeight="1">
+    <row r="710" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A710" s="1"/>
       <c r="B710" s="27"/>
       <c r="C710" s="17"/>
@@ -17488,7 +17456,7 @@
       <c r="T710" s="11"/>
       <c r="U710" s="11"/>
     </row>
-    <row r="711" spans="1:21" ht="18" customHeight="1">
+    <row r="711" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A711" s="1"/>
       <c r="B711" s="27"/>
       <c r="C711" s="17"/>
@@ -17511,7 +17479,7 @@
       <c r="T711" s="11"/>
       <c r="U711" s="11"/>
     </row>
-    <row r="712" spans="1:21" ht="18" customHeight="1">
+    <row r="712" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A712" s="1"/>
       <c r="B712" s="27"/>
       <c r="C712" s="17"/>
@@ -17534,7 +17502,7 @@
       <c r="T712" s="11"/>
       <c r="U712" s="11"/>
     </row>
-    <row r="713" spans="1:21" ht="18" customHeight="1">
+    <row r="713" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A713" s="1"/>
       <c r="B713" s="27"/>
       <c r="C713" s="17"/>
@@ -17557,7 +17525,7 @@
       <c r="T713" s="11"/>
       <c r="U713" s="11"/>
     </row>
-    <row r="714" spans="1:21" ht="18" customHeight="1">
+    <row r="714" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A714" s="1"/>
       <c r="B714" s="27"/>
       <c r="C714" s="17"/>
@@ -17580,7 +17548,7 @@
       <c r="T714" s="11"/>
       <c r="U714" s="11"/>
     </row>
-    <row r="715" spans="1:21" ht="18" customHeight="1">
+    <row r="715" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A715" s="1"/>
       <c r="B715" s="27"/>
       <c r="C715" s="17"/>
@@ -17603,7 +17571,7 @@
       <c r="T715" s="11"/>
       <c r="U715" s="11"/>
     </row>
-    <row r="716" spans="1:21" ht="18" customHeight="1">
+    <row r="716" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A716" s="1"/>
       <c r="B716" s="27"/>
       <c r="C716" s="17"/>
@@ -17626,7 +17594,7 @@
       <c r="T716" s="11"/>
       <c r="U716" s="11"/>
     </row>
-    <row r="717" spans="1:21" ht="18" customHeight="1">
+    <row r="717" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A717" s="1"/>
       <c r="B717" s="27"/>
       <c r="C717" s="17"/>
@@ -17649,7 +17617,7 @@
       <c r="T717" s="11"/>
       <c r="U717" s="11"/>
     </row>
-    <row r="718" spans="1:21" ht="18" customHeight="1">
+    <row r="718" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A718" s="1"/>
       <c r="B718" s="27"/>
       <c r="C718" s="17"/>
@@ -17672,7 +17640,7 @@
       <c r="T718" s="11"/>
       <c r="U718" s="11"/>
     </row>
-    <row r="719" spans="1:21" ht="18" customHeight="1">
+    <row r="719" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A719" s="1"/>
       <c r="B719" s="27"/>
       <c r="C719" s="17"/>
@@ -17695,7 +17663,7 @@
       <c r="T719" s="11"/>
       <c r="U719" s="11"/>
     </row>
-    <row r="720" spans="1:21" ht="18" customHeight="1">
+    <row r="720" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A720" s="1"/>
       <c r="B720" s="27"/>
       <c r="C720" s="17"/>
@@ -17718,7 +17686,7 @@
       <c r="T720" s="11"/>
       <c r="U720" s="11"/>
     </row>
-    <row r="721" spans="1:21" ht="18" customHeight="1">
+    <row r="721" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A721" s="1"/>
       <c r="B721" s="27"/>
       <c r="C721" s="17"/>
@@ -17741,7 +17709,7 @@
       <c r="T721" s="11"/>
       <c r="U721" s="11"/>
     </row>
-    <row r="722" spans="1:21" ht="18" customHeight="1">
+    <row r="722" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A722" s="1"/>
       <c r="B722" s="27"/>
       <c r="C722" s="17"/>
@@ -17764,7 +17732,7 @@
       <c r="T722" s="11"/>
       <c r="U722" s="11"/>
     </row>
-    <row r="723" spans="1:21" ht="18" customHeight="1">
+    <row r="723" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A723" s="1"/>
       <c r="B723" s="27"/>
       <c r="C723" s="17"/>
@@ -17787,7 +17755,7 @@
       <c r="T723" s="11"/>
       <c r="U723" s="11"/>
     </row>
-    <row r="724" spans="1:21" ht="18" customHeight="1">
+    <row r="724" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A724" s="1"/>
       <c r="B724" s="27"/>
       <c r="C724" s="17"/>
@@ -17810,7 +17778,7 @@
       <c r="T724" s="11"/>
       <c r="U724" s="11"/>
     </row>
-    <row r="725" spans="1:21" ht="18" customHeight="1">
+    <row r="725" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A725" s="1"/>
       <c r="B725" s="27"/>
       <c r="C725" s="17"/>
@@ -17833,7 +17801,7 @@
       <c r="T725" s="11"/>
       <c r="U725" s="11"/>
     </row>
-    <row r="726" spans="1:21" ht="18" customHeight="1">
+    <row r="726" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A726" s="1"/>
       <c r="B726" s="27"/>
       <c r="C726" s="17"/>
@@ -17856,7 +17824,7 @@
       <c r="T726" s="11"/>
       <c r="U726" s="11"/>
     </row>
-    <row r="727" spans="1:21" ht="18" customHeight="1">
+    <row r="727" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A727" s="1"/>
       <c r="B727" s="27"/>
       <c r="C727" s="17"/>
@@ -17879,7 +17847,7 @@
       <c r="T727" s="11"/>
       <c r="U727" s="11"/>
     </row>
-    <row r="728" spans="1:21" ht="18" customHeight="1">
+    <row r="728" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A728" s="1"/>
       <c r="B728" s="27"/>
       <c r="C728" s="17"/>
@@ -17902,7 +17870,7 @@
       <c r="T728" s="11"/>
       <c r="U728" s="11"/>
     </row>
-    <row r="729" spans="1:21" ht="18" customHeight="1">
+    <row r="729" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A729" s="1"/>
       <c r="B729" s="27"/>
       <c r="C729" s="17"/>
@@ -17925,7 +17893,7 @@
       <c r="T729" s="11"/>
       <c r="U729" s="11"/>
     </row>
-    <row r="730" spans="1:21" ht="18" customHeight="1">
+    <row r="730" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A730" s="1"/>
       <c r="B730" s="27"/>
       <c r="C730" s="17"/>
@@ -17948,7 +17916,7 @@
       <c r="T730" s="11"/>
       <c r="U730" s="11"/>
     </row>
-    <row r="731" spans="1:21" ht="18" customHeight="1">
+    <row r="731" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A731" s="1"/>
       <c r="B731" s="27"/>
       <c r="C731" s="17"/>
@@ -17971,7 +17939,7 @@
       <c r="T731" s="11"/>
       <c r="U731" s="11"/>
     </row>
-    <row r="732" spans="1:21" ht="18" customHeight="1">
+    <row r="732" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A732" s="1"/>
       <c r="B732" s="27"/>
       <c r="C732" s="17"/>
@@ -17994,7 +17962,7 @@
       <c r="T732" s="11"/>
       <c r="U732" s="11"/>
     </row>
-    <row r="733" spans="1:21" ht="18" customHeight="1">
+    <row r="733" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A733" s="1"/>
       <c r="B733" s="27"/>
       <c r="C733" s="17"/>
@@ -18017,7 +17985,7 @@
       <c r="T733" s="11"/>
       <c r="U733" s="11"/>
     </row>
-    <row r="734" spans="1:21" ht="18" customHeight="1">
+    <row r="734" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A734" s="1"/>
       <c r="B734" s="27"/>
       <c r="C734" s="17"/>
@@ -18040,7 +18008,7 @@
       <c r="T734" s="11"/>
       <c r="U734" s="11"/>
     </row>
-    <row r="735" spans="1:21" ht="18" customHeight="1">
+    <row r="735" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A735" s="1"/>
       <c r="B735" s="27"/>
       <c r="C735" s="17"/>
@@ -18063,7 +18031,7 @@
       <c r="T735" s="11"/>
       <c r="U735" s="11"/>
     </row>
-    <row r="736" spans="1:21" ht="18" customHeight="1">
+    <row r="736" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A736" s="1"/>
       <c r="B736" s="27"/>
       <c r="C736" s="17"/>
@@ -18086,7 +18054,7 @@
       <c r="T736" s="11"/>
       <c r="U736" s="11"/>
     </row>
-    <row r="737" spans="1:21" ht="18" customHeight="1">
+    <row r="737" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A737" s="1"/>
       <c r="B737" s="27"/>
       <c r="C737" s="17"/>
@@ -18109,7 +18077,7 @@
       <c r="T737" s="11"/>
       <c r="U737" s="11"/>
     </row>
-    <row r="738" spans="1:21" ht="18" customHeight="1">
+    <row r="738" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A738" s="1"/>
       <c r="B738" s="27"/>
       <c r="C738" s="17"/>
@@ -18132,7 +18100,7 @@
       <c r="T738" s="11"/>
       <c r="U738" s="11"/>
     </row>
-    <row r="739" spans="1:21" ht="18" customHeight="1">
+    <row r="739" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A739" s="1"/>
       <c r="B739" s="27"/>
       <c r="C739" s="17"/>
@@ -18155,7 +18123,7 @@
       <c r="T739" s="11"/>
       <c r="U739" s="11"/>
     </row>
-    <row r="740" spans="1:21" ht="18" customHeight="1">
+    <row r="740" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A740" s="1"/>
       <c r="B740" s="27"/>
       <c r="C740" s="17"/>
@@ -18178,7 +18146,7 @@
       <c r="T740" s="11"/>
       <c r="U740" s="11"/>
     </row>
-    <row r="741" spans="1:21" ht="18" customHeight="1">
+    <row r="741" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A741" s="1"/>
       <c r="B741" s="27"/>
       <c r="C741" s="17"/>
@@ -18201,7 +18169,7 @@
       <c r="T741" s="11"/>
       <c r="U741" s="11"/>
     </row>
-    <row r="742" spans="1:21" ht="18" customHeight="1">
+    <row r="742" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A742" s="1"/>
       <c r="B742" s="27"/>
       <c r="C742" s="17"/>
@@ -18224,7 +18192,7 @@
       <c r="T742" s="11"/>
       <c r="U742" s="11"/>
     </row>
-    <row r="743" spans="1:21" ht="18" customHeight="1">
+    <row r="743" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A743" s="1"/>
       <c r="B743" s="27"/>
       <c r="C743" s="17"/>
@@ -18247,7 +18215,7 @@
       <c r="T743" s="11"/>
       <c r="U743" s="11"/>
     </row>
-    <row r="744" spans="1:21" ht="18" customHeight="1">
+    <row r="744" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A744" s="1"/>
       <c r="B744" s="27"/>
       <c r="C744" s="17"/>
@@ -18270,7 +18238,7 @@
       <c r="T744" s="11"/>
       <c r="U744" s="11"/>
     </row>
-    <row r="745" spans="1:21" ht="18" customHeight="1">
+    <row r="745" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A745" s="1"/>
       <c r="B745" s="27"/>
       <c r="C745" s="17"/>
@@ -18293,7 +18261,7 @@
       <c r="T745" s="11"/>
       <c r="U745" s="11"/>
     </row>
-    <row r="746" spans="1:21" ht="18" customHeight="1">
+    <row r="746" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A746" s="1"/>
       <c r="B746" s="27"/>
       <c r="C746" s="17"/>
@@ -18316,7 +18284,7 @@
       <c r="T746" s="11"/>
       <c r="U746" s="11"/>
     </row>
-    <row r="747" spans="1:21" ht="18" customHeight="1">
+    <row r="747" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A747" s="1"/>
       <c r="B747" s="27"/>
       <c r="C747" s="17"/>
@@ -18339,7 +18307,7 @@
       <c r="T747" s="11"/>
       <c r="U747" s="11"/>
     </row>
-    <row r="748" spans="1:21" ht="18" customHeight="1">
+    <row r="748" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A748" s="1"/>
       <c r="B748" s="27"/>
       <c r="C748" s="17"/>
@@ -18362,7 +18330,7 @@
       <c r="T748" s="11"/>
       <c r="U748" s="11"/>
     </row>
-    <row r="749" spans="1:21" ht="18" customHeight="1">
+    <row r="749" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A749" s="1"/>
       <c r="B749" s="27"/>
       <c r="C749" s="17"/>
@@ -18385,7 +18353,7 @@
       <c r="T749" s="11"/>
       <c r="U749" s="11"/>
     </row>
-    <row r="750" spans="1:21" ht="18" customHeight="1">
+    <row r="750" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A750" s="1"/>
       <c r="B750" s="27"/>
       <c r="C750" s="17"/>
@@ -18408,7 +18376,7 @@
       <c r="T750" s="11"/>
       <c r="U750" s="11"/>
     </row>
-    <row r="751" spans="1:21" ht="18" customHeight="1">
+    <row r="751" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A751" s="1"/>
       <c r="B751" s="27"/>
       <c r="C751" s="17"/>
@@ -18431,7 +18399,7 @@
       <c r="T751" s="11"/>
       <c r="U751" s="11"/>
     </row>
-    <row r="752" spans="1:21" ht="18" customHeight="1">
+    <row r="752" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A752" s="1"/>
       <c r="B752" s="27"/>
       <c r="C752" s="17"/>
@@ -18454,7 +18422,7 @@
       <c r="T752" s="11"/>
       <c r="U752" s="11"/>
     </row>
-    <row r="753" spans="1:21" ht="18" customHeight="1">
+    <row r="753" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A753" s="1"/>
       <c r="B753" s="27"/>
       <c r="C753" s="17"/>
@@ -18477,7 +18445,7 @@
       <c r="T753" s="11"/>
       <c r="U753" s="11"/>
     </row>
-    <row r="754" spans="1:21" ht="18" customHeight="1">
+    <row r="754" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A754" s="1"/>
       <c r="B754" s="27"/>
       <c r="C754" s="17"/>
@@ -18500,7 +18468,7 @@
       <c r="T754" s="11"/>
       <c r="U754" s="11"/>
     </row>
-    <row r="755" spans="1:21" ht="18" customHeight="1">
+    <row r="755" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A755" s="1"/>
       <c r="B755" s="27"/>
       <c r="C755" s="17"/>
@@ -18523,7 +18491,7 @@
       <c r="T755" s="11"/>
       <c r="U755" s="11"/>
     </row>
-    <row r="756" spans="1:21" ht="18" customHeight="1">
+    <row r="756" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A756" s="1"/>
       <c r="B756" s="27"/>
       <c r="C756" s="17"/>
@@ -18546,7 +18514,7 @@
       <c r="T756" s="11"/>
       <c r="U756" s="11"/>
     </row>
-    <row r="757" spans="1:21" ht="18" customHeight="1">
+    <row r="757" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A757" s="1"/>
       <c r="B757" s="27"/>
       <c r="C757" s="17"/>
@@ -18569,7 +18537,7 @@
       <c r="T757" s="11"/>
       <c r="U757" s="11"/>
     </row>
-    <row r="758" spans="1:21" ht="18" customHeight="1">
+    <row r="758" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A758" s="1"/>
       <c r="B758" s="27"/>
       <c r="C758" s="17"/>
@@ -18592,7 +18560,7 @@
       <c r="T758" s="11"/>
       <c r="U758" s="11"/>
     </row>
-    <row r="759" spans="1:21" ht="18" customHeight="1">
+    <row r="759" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A759" s="1"/>
       <c r="B759" s="27"/>
       <c r="C759" s="17"/>
@@ -18615,7 +18583,7 @@
       <c r="T759" s="11"/>
       <c r="U759" s="11"/>
     </row>
-    <row r="760" spans="1:21" ht="18" customHeight="1">
+    <row r="760" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A760" s="1"/>
       <c r="B760" s="27"/>
       <c r="C760" s="17"/>
@@ -18638,7 +18606,7 @@
       <c r="T760" s="11"/>
       <c r="U760" s="11"/>
     </row>
-    <row r="761" spans="1:21" ht="18" customHeight="1">
+    <row r="761" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A761" s="1"/>
       <c r="B761" s="27"/>
       <c r="C761" s="17"/>
@@ -18661,7 +18629,7 @@
       <c r="T761" s="11"/>
       <c r="U761" s="11"/>
     </row>
-    <row r="762" spans="1:21" ht="18" customHeight="1">
+    <row r="762" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A762" s="1"/>
       <c r="B762" s="27"/>
       <c r="C762" s="17"/>
@@ -18684,7 +18652,7 @@
       <c r="T762" s="11"/>
       <c r="U762" s="11"/>
     </row>
-    <row r="763" spans="1:21" ht="18" customHeight="1">
+    <row r="763" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A763" s="1"/>
       <c r="B763" s="27"/>
       <c r="C763" s="17"/>
@@ -18707,7 +18675,7 @@
       <c r="T763" s="11"/>
       <c r="U763" s="11"/>
     </row>
-    <row r="764" spans="1:21" ht="18" customHeight="1">
+    <row r="764" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A764" s="1"/>
       <c r="B764" s="27"/>
       <c r="C764" s="17"/>
@@ -18730,7 +18698,7 @@
       <c r="T764" s="11"/>
       <c r="U764" s="11"/>
     </row>
-    <row r="765" spans="1:21" ht="18" customHeight="1">
+    <row r="765" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A765" s="1"/>
       <c r="B765" s="27"/>
       <c r="C765" s="17"/>
@@ -18753,7 +18721,7 @@
       <c r="T765" s="11"/>
       <c r="U765" s="11"/>
     </row>
-    <row r="766" spans="1:21" ht="18" customHeight="1">
+    <row r="766" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A766" s="1"/>
       <c r="B766" s="27"/>
       <c r="C766" s="17"/>
@@ -18776,7 +18744,7 @@
       <c r="T766" s="11"/>
       <c r="U766" s="11"/>
     </row>
-    <row r="767" spans="1:21" ht="18" customHeight="1">
+    <row r="767" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A767" s="1"/>
       <c r="B767" s="27"/>
       <c r="C767" s="17"/>
@@ -18799,7 +18767,7 @@
       <c r="T767" s="11"/>
       <c r="U767" s="11"/>
     </row>
-    <row r="768" spans="1:21" ht="18" customHeight="1">
+    <row r="768" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A768" s="1"/>
       <c r="B768" s="27"/>
       <c r="C768" s="17"/>
@@ -18822,7 +18790,7 @@
       <c r="T768" s="11"/>
       <c r="U768" s="11"/>
     </row>
-    <row r="769" spans="1:21" ht="18" customHeight="1">
+    <row r="769" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A769" s="1"/>
       <c r="B769" s="27"/>
       <c r="C769" s="17"/>
@@ -18845,7 +18813,7 @@
       <c r="T769" s="11"/>
       <c r="U769" s="11"/>
     </row>
-    <row r="770" spans="1:21" ht="18" customHeight="1">
+    <row r="770" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A770" s="1"/>
       <c r="B770" s="27"/>
       <c r="C770" s="17"/>
@@ -18868,7 +18836,7 @@
       <c r="T770" s="11"/>
       <c r="U770" s="11"/>
     </row>
-    <row r="771" spans="1:21" ht="18" customHeight="1">
+    <row r="771" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A771" s="1"/>
       <c r="B771" s="27"/>
       <c r="C771" s="17"/>
@@ -18891,7 +18859,7 @@
       <c r="T771" s="11"/>
       <c r="U771" s="11"/>
     </row>
-    <row r="772" spans="1:21" ht="18" customHeight="1">
+    <row r="772" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A772" s="1"/>
       <c r="B772" s="27"/>
       <c r="C772" s="17"/>
@@ -18914,7 +18882,7 @@
       <c r="T772" s="11"/>
       <c r="U772" s="11"/>
     </row>
-    <row r="773" spans="1:21" ht="18" customHeight="1">
+    <row r="773" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A773" s="1"/>
       <c r="B773" s="27"/>
       <c r="C773" s="17"/>
@@ -18937,7 +18905,7 @@
       <c r="T773" s="11"/>
       <c r="U773" s="11"/>
     </row>
-    <row r="774" spans="1:21" ht="18" customHeight="1">
+    <row r="774" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A774" s="1"/>
       <c r="B774" s="27"/>
       <c r="C774" s="17"/>
@@ -18960,7 +18928,7 @@
       <c r="T774" s="11"/>
       <c r="U774" s="11"/>
     </row>
-    <row r="775" spans="1:21" ht="18" customHeight="1">
+    <row r="775" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A775" s="1"/>
       <c r="B775" s="27"/>
       <c r="C775" s="17"/>
@@ -18983,7 +18951,7 @@
       <c r="T775" s="11"/>
       <c r="U775" s="11"/>
     </row>
-    <row r="776" spans="1:21" ht="18" customHeight="1">
+    <row r="776" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A776" s="1"/>
       <c r="B776" s="27"/>
       <c r="C776" s="17"/>
@@ -19006,7 +18974,7 @@
       <c r="T776" s="11"/>
       <c r="U776" s="11"/>
     </row>
-    <row r="777" spans="1:21" ht="18" customHeight="1">
+    <row r="777" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A777" s="1"/>
       <c r="B777" s="27"/>
       <c r="C777" s="17"/>
@@ -19029,7 +18997,7 @@
       <c r="T777" s="11"/>
       <c r="U777" s="11"/>
     </row>
-    <row r="778" spans="1:21" ht="18" customHeight="1">
+    <row r="778" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A778" s="1"/>
       <c r="B778" s="27"/>
       <c r="C778" s="17"/>
@@ -19052,7 +19020,7 @@
       <c r="T778" s="11"/>
       <c r="U778" s="11"/>
     </row>
-    <row r="779" spans="1:21" ht="18" customHeight="1">
+    <row r="779" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A779" s="1"/>
       <c r="B779" s="27"/>
       <c r="C779" s="17"/>
@@ -19075,7 +19043,7 @@
       <c r="T779" s="11"/>
       <c r="U779" s="11"/>
     </row>
-    <row r="780" spans="1:21" ht="18" customHeight="1">
+    <row r="780" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A780" s="1"/>
       <c r="B780" s="27"/>
       <c r="C780" s="17"/>
@@ -19098,7 +19066,7 @@
       <c r="T780" s="11"/>
       <c r="U780" s="11"/>
     </row>
-    <row r="781" spans="1:21" ht="18" customHeight="1">
+    <row r="781" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A781" s="1"/>
       <c r="B781" s="27"/>
       <c r="C781" s="17"/>
@@ -19121,7 +19089,7 @@
       <c r="T781" s="11"/>
       <c r="U781" s="11"/>
     </row>
-    <row r="782" spans="1:21" ht="18" customHeight="1">
+    <row r="782" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A782" s="1"/>
       <c r="B782" s="27"/>
       <c r="C782" s="17"/>
@@ -19144,7 +19112,7 @@
       <c r="T782" s="11"/>
       <c r="U782" s="11"/>
     </row>
-    <row r="783" spans="1:21" ht="18" customHeight="1">
+    <row r="783" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A783" s="1"/>
       <c r="B783" s="27"/>
       <c r="C783" s="17"/>
@@ -19167,7 +19135,7 @@
       <c r="T783" s="11"/>
       <c r="U783" s="11"/>
     </row>
-    <row r="784" spans="1:21" ht="18" customHeight="1">
+    <row r="784" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A784" s="1"/>
       <c r="B784" s="27"/>
       <c r="C784" s="17"/>
@@ -19190,7 +19158,7 @@
       <c r="T784" s="11"/>
       <c r="U784" s="11"/>
     </row>
-    <row r="785" spans="1:21" ht="18" customHeight="1">
+    <row r="785" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A785" s="1"/>
       <c r="B785" s="27"/>
       <c r="C785" s="17"/>
@@ -19213,7 +19181,7 @@
       <c r="T785" s="11"/>
       <c r="U785" s="11"/>
     </row>
-    <row r="786" spans="1:21" ht="18" customHeight="1">
+    <row r="786" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A786" s="1"/>
       <c r="B786" s="27"/>
       <c r="C786" s="17"/>
@@ -19236,7 +19204,7 @@
       <c r="T786" s="11"/>
       <c r="U786" s="11"/>
     </row>
-    <row r="787" spans="1:21" ht="18" customHeight="1">
+    <row r="787" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A787" s="1"/>
       <c r="B787" s="27"/>
       <c r="C787" s="17"/>
@@ -19259,7 +19227,7 @@
       <c r="T787" s="11"/>
       <c r="U787" s="11"/>
     </row>
-    <row r="788" spans="1:21" ht="18" customHeight="1">
+    <row r="788" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A788" s="1"/>
       <c r="B788" s="27"/>
       <c r="C788" s="17"/>
@@ -19282,7 +19250,7 @@
       <c r="T788" s="11"/>
       <c r="U788" s="11"/>
     </row>
-    <row r="789" spans="1:21" ht="18" customHeight="1">
+    <row r="789" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A789" s="1"/>
       <c r="B789" s="27"/>
       <c r="C789" s="17"/>
@@ -19305,7 +19273,7 @@
       <c r="T789" s="11"/>
       <c r="U789" s="11"/>
     </row>
-    <row r="790" spans="1:21" ht="18" customHeight="1">
+    <row r="790" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A790" s="1"/>
       <c r="B790" s="27"/>
       <c r="C790" s="17"/>
@@ -19328,7 +19296,7 @@
       <c r="T790" s="11"/>
       <c r="U790" s="11"/>
     </row>
-    <row r="791" spans="1:21" ht="18" customHeight="1">
+    <row r="791" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A791" s="1"/>
       <c r="B791" s="27"/>
       <c r="C791" s="17"/>
@@ -19351,7 +19319,7 @@
       <c r="T791" s="11"/>
       <c r="U791" s="11"/>
     </row>
-    <row r="792" spans="1:21" ht="18" customHeight="1">
+    <row r="792" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A792" s="1"/>
       <c r="B792" s="27"/>
       <c r="C792" s="17"/>
@@ -19374,7 +19342,7 @@
       <c r="T792" s="11"/>
       <c r="U792" s="11"/>
     </row>
-    <row r="793" spans="1:21" ht="18" customHeight="1">
+    <row r="793" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A793" s="1"/>
       <c r="B793" s="27"/>
       <c r="C793" s="17"/>
@@ -19397,7 +19365,7 @@
       <c r="T793" s="11"/>
       <c r="U793" s="11"/>
     </row>
-    <row r="794" spans="1:21" ht="18" customHeight="1">
+    <row r="794" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A794" s="1"/>
       <c r="B794" s="27"/>
       <c r="C794" s="17"/>
@@ -19420,7 +19388,7 @@
       <c r="T794" s="11"/>
       <c r="U794" s="11"/>
     </row>
-    <row r="795" spans="1:21" ht="18" customHeight="1">
+    <row r="795" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A795" s="1"/>
       <c r="B795" s="27"/>
       <c r="C795" s="17"/>
@@ -19443,7 +19411,7 @@
       <c r="T795" s="11"/>
       <c r="U795" s="11"/>
     </row>
-    <row r="796" spans="1:21" ht="18" customHeight="1">
+    <row r="796" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A796" s="1"/>
       <c r="B796" s="27"/>
       <c r="C796" s="17"/>
@@ -19466,7 +19434,7 @@
       <c r="T796" s="11"/>
       <c r="U796" s="11"/>
     </row>
-    <row r="797" spans="1:21" ht="18" customHeight="1">
+    <row r="797" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A797" s="1"/>
       <c r="B797" s="27"/>
       <c r="C797" s="17"/>
@@ -19489,7 +19457,7 @@
       <c r="T797" s="11"/>
       <c r="U797" s="11"/>
     </row>
-    <row r="798" spans="1:21" ht="18" customHeight="1">
+    <row r="798" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A798" s="1"/>
       <c r="B798" s="27"/>
       <c r="C798" s="17"/>
@@ -19512,7 +19480,7 @@
       <c r="T798" s="11"/>
       <c r="U798" s="11"/>
     </row>
-    <row r="799" spans="1:21" ht="18" customHeight="1">
+    <row r="799" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A799" s="1"/>
       <c r="B799" s="27"/>
       <c r="C799" s="17"/>
@@ -19535,7 +19503,7 @@
       <c r="T799" s="11"/>
       <c r="U799" s="11"/>
     </row>
-    <row r="800" spans="1:21" ht="18" customHeight="1">
+    <row r="800" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A800" s="1"/>
       <c r="B800" s="27"/>
       <c r="C800" s="17"/>
@@ -19558,7 +19526,7 @@
       <c r="T800" s="11"/>
       <c r="U800" s="11"/>
     </row>
-    <row r="801" spans="1:21" ht="18" customHeight="1">
+    <row r="801" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A801" s="1"/>
       <c r="B801" s="27"/>
       <c r="C801" s="17"/>
@@ -19581,7 +19549,7 @@
       <c r="T801" s="11"/>
       <c r="U801" s="11"/>
     </row>
-    <row r="802" spans="1:21" ht="18" customHeight="1">
+    <row r="802" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A802" s="1"/>
       <c r="B802" s="27"/>
       <c r="C802" s="17"/>
@@ -19604,7 +19572,7 @@
       <c r="T802" s="11"/>
       <c r="U802" s="11"/>
     </row>
-    <row r="803" spans="1:21" ht="18" customHeight="1">
+    <row r="803" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A803" s="1"/>
       <c r="B803" s="27"/>
       <c r="C803" s="17"/>
@@ -19627,7 +19595,7 @@
       <c r="T803" s="11"/>
       <c r="U803" s="11"/>
     </row>
-    <row r="804" spans="1:21" ht="18" customHeight="1">
+    <row r="804" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A804" s="1"/>
       <c r="B804" s="27"/>
       <c r="C804" s="17"/>
@@ -19650,7 +19618,7 @@
       <c r="T804" s="11"/>
       <c r="U804" s="11"/>
     </row>
-    <row r="805" spans="1:21" ht="18" customHeight="1">
+    <row r="805" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A805" s="1"/>
       <c r="B805" s="27"/>
       <c r="C805" s="17"/>
@@ -19673,7 +19641,7 @@
       <c r="T805" s="11"/>
       <c r="U805" s="11"/>
     </row>
-    <row r="806" spans="1:21" ht="18" customHeight="1">
+    <row r="806" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A806" s="1"/>
       <c r="B806" s="27"/>
       <c r="C806" s="17"/>
@@ -19696,7 +19664,7 @@
       <c r="T806" s="11"/>
       <c r="U806" s="11"/>
     </row>
-    <row r="807" spans="1:21" ht="18" customHeight="1">
+    <row r="807" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A807" s="1"/>
       <c r="B807" s="27"/>
       <c r="C807" s="17"/>
@@ -19719,7 +19687,7 @@
       <c r="T807" s="11"/>
       <c r="U807" s="11"/>
     </row>
-    <row r="808" spans="1:21" ht="18" customHeight="1">
+    <row r="808" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A808" s="1"/>
       <c r="B808" s="27"/>
       <c r="C808" s="17"/>
@@ -19742,7 +19710,7 @@
       <c r="T808" s="11"/>
       <c r="U808" s="11"/>
     </row>
-    <row r="809" spans="1:21" ht="18" customHeight="1">
+    <row r="809" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A809" s="1"/>
       <c r="B809" s="27"/>
       <c r="C809" s="17"/>
@@ -19765,7 +19733,7 @@
       <c r="T809" s="11"/>
       <c r="U809" s="11"/>
     </row>
-    <row r="810" spans="1:21" ht="18" customHeight="1">
+    <row r="810" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A810" s="1"/>
       <c r="B810" s="27"/>
       <c r="C810" s="17"/>
@@ -19788,7 +19756,7 @@
       <c r="T810" s="11"/>
       <c r="U810" s="11"/>
     </row>
-    <row r="811" spans="1:21" ht="18" customHeight="1">
+    <row r="811" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A811" s="1"/>
       <c r="B811" s="27"/>
       <c r="C811" s="17"/>
@@ -19811,7 +19779,7 @@
       <c r="T811" s="11"/>
       <c r="U811" s="11"/>
     </row>
-    <row r="812" spans="1:21" ht="18" customHeight="1">
+    <row r="812" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A812" s="1"/>
       <c r="B812" s="27"/>
       <c r="C812" s="17"/>
@@ -19834,7 +19802,7 @@
       <c r="T812" s="11"/>
       <c r="U812" s="11"/>
     </row>
-    <row r="813" spans="1:21" ht="18" customHeight="1">
+    <row r="813" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A813" s="1"/>
       <c r="B813" s="27"/>
       <c r="C813" s="17"/>
@@ -19857,7 +19825,7 @@
       <c r="T813" s="11"/>
       <c r="U813" s="11"/>
     </row>
-    <row r="814" spans="1:21" ht="18" customHeight="1">
+    <row r="814" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A814" s="1"/>
       <c r="B814" s="27"/>
       <c r="C814" s="17"/>
@@ -19880,7 +19848,7 @@
       <c r="T814" s="11"/>
       <c r="U814" s="11"/>
     </row>
-    <row r="815" spans="1:21" ht="18" customHeight="1">
+    <row r="815" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A815" s="1"/>
       <c r="B815" s="27"/>
       <c r="C815" s="17"/>
@@ -19903,7 +19871,7 @@
       <c r="T815" s="11"/>
       <c r="U815" s="11"/>
     </row>
-    <row r="816" spans="1:21" ht="18" customHeight="1">
+    <row r="816" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A816" s="1"/>
       <c r="B816" s="27"/>
       <c r="C816" s="17"/>
@@ -19926,7 +19894,7 @@
       <c r="T816" s="11"/>
       <c r="U816" s="11"/>
     </row>
-    <row r="817" spans="1:21" ht="18" customHeight="1">
+    <row r="817" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A817" s="1"/>
       <c r="B817" s="27"/>
       <c r="C817" s="17"/>
@@ -19949,7 +19917,7 @@
       <c r="T817" s="11"/>
       <c r="U817" s="11"/>
     </row>
-    <row r="818" spans="1:21" ht="18" customHeight="1">
+    <row r="818" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A818" s="1"/>
       <c r="B818" s="27"/>
       <c r="C818" s="17"/>
@@ -19972,7 +19940,7 @@
       <c r="T818" s="11"/>
       <c r="U818" s="11"/>
     </row>
-    <row r="819" spans="1:21" ht="18" customHeight="1">
+    <row r="819" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A819" s="1"/>
       <c r="B819" s="27"/>
       <c r="C819" s="17"/>
@@ -19995,7 +19963,7 @@
       <c r="T819" s="11"/>
       <c r="U819" s="11"/>
     </row>
-    <row r="820" spans="1:21" ht="18" customHeight="1">
+    <row r="820" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A820" s="1"/>
       <c r="B820" s="27"/>
       <c r="C820" s="17"/>
@@ -20018,7 +19986,7 @@
       <c r="T820" s="11"/>
       <c r="U820" s="11"/>
     </row>
-    <row r="821" spans="1:21" ht="18" customHeight="1">
+    <row r="821" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A821" s="1"/>
       <c r="B821" s="27"/>
       <c r="C821" s="17"/>
@@ -20041,7 +20009,7 @@
       <c r="T821" s="11"/>
       <c r="U821" s="11"/>
     </row>
-    <row r="822" spans="1:21" ht="18" customHeight="1">
+    <row r="822" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A822" s="1"/>
       <c r="B822" s="27"/>
       <c r="C822" s="17"/>
@@ -20064,7 +20032,7 @@
       <c r="T822" s="11"/>
       <c r="U822" s="11"/>
     </row>
-    <row r="823" spans="1:21" ht="18" customHeight="1">
+    <row r="823" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A823" s="1"/>
       <c r="B823" s="27"/>
       <c r="C823" s="17"/>
@@ -20087,7 +20055,7 @@
       <c r="T823" s="11"/>
       <c r="U823" s="11"/>
     </row>
-    <row r="824" spans="1:21" ht="18" customHeight="1">
+    <row r="824" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A824" s="1"/>
       <c r="B824" s="27"/>
       <c r="C824" s="17"/>
@@ -20110,7 +20078,7 @@
       <c r="T824" s="11"/>
       <c r="U824" s="11"/>
     </row>
-    <row r="825" spans="1:21" ht="18" customHeight="1">
+    <row r="825" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A825" s="1"/>
       <c r="B825" s="27"/>
       <c r="C825" s="17"/>
@@ -20133,7 +20101,7 @@
       <c r="T825" s="11"/>
       <c r="U825" s="11"/>
     </row>
-    <row r="826" spans="1:21" ht="18" customHeight="1">
+    <row r="826" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A826" s="1"/>
       <c r="B826" s="27"/>
       <c r="C826" s="17"/>
@@ -20156,7 +20124,7 @@
       <c r="T826" s="11"/>
       <c r="U826" s="11"/>
     </row>
-    <row r="827" spans="1:21" ht="18" customHeight="1">
+    <row r="827" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A827" s="1"/>
       <c r="B827" s="27"/>
       <c r="C827" s="17"/>
@@ -20179,7 +20147,7 @@
       <c r="T827" s="11"/>
       <c r="U827" s="11"/>
     </row>
-    <row r="828" spans="1:21" ht="18" customHeight="1">
+    <row r="828" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A828" s="1"/>
       <c r="B828" s="27"/>
       <c r="C828" s="17"/>
@@ -20202,7 +20170,7 @@
       <c r="T828" s="11"/>
       <c r="U828" s="11"/>
     </row>
-    <row r="829" spans="1:21" ht="18" customHeight="1">
+    <row r="829" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A829" s="1"/>
       <c r="B829" s="27"/>
       <c r="C829" s="17"/>
@@ -20225,7 +20193,7 @@
       <c r="T829" s="11"/>
       <c r="U829" s="11"/>
     </row>
-    <row r="830" spans="1:21" ht="18" customHeight="1">
+    <row r="830" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A830" s="1"/>
       <c r="B830" s="27"/>
       <c r="C830" s="17"/>
@@ -20248,7 +20216,7 @@
       <c r="T830" s="11"/>
       <c r="U830" s="11"/>
     </row>
-    <row r="831" spans="1:21" ht="18" customHeight="1">
+    <row r="831" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A831" s="1"/>
       <c r="B831" s="27"/>
       <c r="C831" s="17"/>
@@ -20271,7 +20239,7 @@
       <c r="T831" s="11"/>
       <c r="U831" s="11"/>
     </row>
-    <row r="832" spans="1:21" ht="18" customHeight="1">
+    <row r="832" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A832" s="1"/>
       <c r="B832" s="27"/>
       <c r="C832" s="17"/>
@@ -20294,7 +20262,7 @@
       <c r="T832" s="11"/>
       <c r="U832" s="11"/>
     </row>
-    <row r="833" spans="1:21" ht="18" customHeight="1">
+    <row r="833" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A833" s="1"/>
       <c r="B833" s="27"/>
       <c r="C833" s="17"/>
@@ -20317,7 +20285,7 @@
       <c r="T833" s="11"/>
       <c r="U833" s="11"/>
     </row>
-    <row r="834" spans="1:21" ht="18" customHeight="1">
+    <row r="834" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A834" s="1"/>
       <c r="B834" s="27"/>
       <c r="C834" s="17"/>
@@ -20340,7 +20308,7 @@
       <c r="T834" s="11"/>
       <c r="U834" s="11"/>
     </row>
-    <row r="835" spans="1:21" ht="18" customHeight="1">
+    <row r="835" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A835" s="1"/>
       <c r="B835" s="27"/>
       <c r="C835" s="17"/>
@@ -20363,7 +20331,7 @@
       <c r="T835" s="11"/>
       <c r="U835" s="11"/>
     </row>
-    <row r="836" spans="1:21" ht="18" customHeight="1">
+    <row r="836" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A836" s="1"/>
       <c r="B836" s="27"/>
       <c r="C836" s="17"/>
@@ -20386,7 +20354,7 @@
       <c r="T836" s="11"/>
       <c r="U836" s="11"/>
     </row>
-    <row r="837" spans="1:21" ht="18" customHeight="1">
+    <row r="837" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A837" s="1"/>
       <c r="B837" s="27"/>
       <c r="C837" s="17"/>
@@ -20409,7 +20377,7 @@
       <c r="T837" s="11"/>
       <c r="U837" s="11"/>
     </row>
-    <row r="838" spans="1:21" ht="18" customHeight="1">
+    <row r="838" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A838" s="1"/>
       <c r="B838" s="27"/>
       <c r="C838" s="17"/>
@@ -20432,7 +20400,7 @@
       <c r="T838" s="11"/>
       <c r="U838" s="11"/>
     </row>
-    <row r="839" spans="1:21" ht="18" customHeight="1">
+    <row r="839" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A839" s="1"/>
       <c r="B839" s="27"/>
       <c r="C839" s="17"/>
@@ -20455,7 +20423,7 @@
       <c r="T839" s="11"/>
       <c r="U839" s="11"/>
     </row>
-    <row r="840" spans="1:21" ht="18" customHeight="1">
+    <row r="840" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A840" s="1"/>
       <c r="B840" s="27"/>
       <c r="C840" s="17"/>
@@ -20478,7 +20446,7 @@
       <c r="T840" s="11"/>
       <c r="U840" s="11"/>
     </row>
-    <row r="841" spans="1:21" ht="18" customHeight="1">
+    <row r="841" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A841" s="1"/>
       <c r="B841" s="27"/>
       <c r="C841" s="17"/>
@@ -20501,7 +20469,7 @@
       <c r="T841" s="11"/>
       <c r="U841" s="11"/>
     </row>
-    <row r="842" spans="1:21" ht="18" customHeight="1">
+    <row r="842" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A842" s="1"/>
       <c r="B842" s="27"/>
       <c r="C842" s="17"/>
@@ -20524,7 +20492,7 @@
       <c r="T842" s="11"/>
       <c r="U842" s="11"/>
     </row>
-    <row r="843" spans="1:21" ht="18" customHeight="1">
+    <row r="843" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A843" s="1"/>
       <c r="B843" s="27"/>
       <c r="C843" s="17"/>
@@ -20547,7 +20515,7 @@
       <c r="T843" s="11"/>
       <c r="U843" s="11"/>
     </row>
-    <row r="844" spans="1:21" ht="18" customHeight="1">
+    <row r="844" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A844" s="1"/>
       <c r="B844" s="27"/>
       <c r="C844" s="17"/>
@@ -20570,7 +20538,7 @@
       <c r="T844" s="11"/>
       <c r="U844" s="11"/>
     </row>
-    <row r="845" spans="1:21" ht="18" customHeight="1">
+    <row r="845" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A845" s="1"/>
       <c r="B845" s="27"/>
       <c r="C845" s="17"/>
@@ -20593,7 +20561,7 @@
       <c r="T845" s="11"/>
       <c r="U845" s="11"/>
     </row>
-    <row r="846" spans="1:21" ht="18" customHeight="1">
+    <row r="846" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A846" s="1"/>
       <c r="B846" s="27"/>
       <c r="C846" s="17"/>
@@ -20616,7 +20584,7 @@
       <c r="T846" s="11"/>
       <c r="U846" s="11"/>
     </row>
-    <row r="847" spans="1:21" ht="18" customHeight="1">
+    <row r="847" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A847" s="1"/>
       <c r="B847" s="27"/>
       <c r="C847" s="17"/>
@@ -20639,7 +20607,7 @@
       <c r="T847" s="11"/>
       <c r="U847" s="11"/>
     </row>
-    <row r="848" spans="1:21" ht="18" customHeight="1">
+    <row r="848" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A848" s="1"/>
       <c r="B848" s="27"/>
       <c r="C848" s="17"/>
@@ -20662,7 +20630,7 @@
       <c r="T848" s="11"/>
       <c r="U848" s="11"/>
     </row>
-    <row r="849" spans="1:21" ht="18" customHeight="1">
+    <row r="849" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A849" s="1"/>
       <c r="B849" s="27"/>
       <c r="C849" s="17"/>
@@ -20685,7 +20653,7 @@
       <c r="T849" s="11"/>
       <c r="U849" s="11"/>
     </row>
-    <row r="850" spans="1:21" ht="18" customHeight="1">
+    <row r="850" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A850" s="1"/>
       <c r="B850" s="27"/>
       <c r="C850" s="17"/>
@@ -20708,7 +20676,7 @@
       <c r="T850" s="11"/>
       <c r="U850" s="11"/>
     </row>
-    <row r="851" spans="1:21" ht="18" customHeight="1">
+    <row r="851" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A851" s="1"/>
       <c r="B851" s="27"/>
       <c r="C851" s="17"/>
@@ -20731,7 +20699,7 @@
       <c r="T851" s="11"/>
       <c r="U851" s="11"/>
     </row>
-    <row r="852" spans="1:21" ht="18" customHeight="1">
+    <row r="852" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A852" s="1"/>
       <c r="B852" s="27"/>
       <c r="C852" s="17"/>
@@ -20754,7 +20722,7 @@
       <c r="T852" s="11"/>
       <c r="U852" s="11"/>
     </row>
-    <row r="853" spans="1:21" ht="18" customHeight="1">
+    <row r="853" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A853" s="1"/>
       <c r="B853" s="27"/>
       <c r="C853" s="17"/>
@@ -20777,7 +20745,7 @@
       <c r="T853" s="11"/>
       <c r="U853" s="11"/>
     </row>
-    <row r="854" spans="1:21" ht="18" customHeight="1">
+    <row r="854" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A854" s="1"/>
       <c r="B854" s="27"/>
       <c r="C854" s="17"/>
@@ -20800,7 +20768,7 @@
       <c r="T854" s="11"/>
       <c r="U854" s="11"/>
     </row>
-    <row r="855" spans="1:21" ht="18" customHeight="1">
+    <row r="855" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A855" s="1"/>
       <c r="B855" s="27"/>
       <c r="C855" s="17"/>
@@ -20823,7 +20791,7 @@
       <c r="T855" s="11"/>
       <c r="U855" s="11"/>
     </row>
-    <row r="856" spans="1:21" ht="18" customHeight="1">
+    <row r="856" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A856" s="1"/>
       <c r="B856" s="27"/>
       <c r="C856" s="17"/>
@@ -20846,7 +20814,7 @@
       <c r="T856" s="11"/>
       <c r="U856" s="11"/>
     </row>
-    <row r="857" spans="1:21" ht="18" customHeight="1">
+    <row r="857" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A857" s="1"/>
       <c r="B857" s="27"/>
       <c r="C857" s="17"/>
@@ -20869,7 +20837,7 @@
       <c r="T857" s="11"/>
       <c r="U857" s="11"/>
     </row>
-    <row r="858" spans="1:21" ht="18" customHeight="1">
+    <row r="858" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A858" s="1"/>
       <c r="B858" s="27"/>
       <c r="C858" s="17"/>
@@ -20892,7 +20860,7 @@
       <c r="T858" s="11"/>
       <c r="U858" s="11"/>
     </row>
-    <row r="859" spans="1:21" ht="18" customHeight="1">
+    <row r="859" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A859" s="1"/>
       <c r="B859" s="27"/>
       <c r="C859" s="17"/>
@@ -20915,7 +20883,7 @@
       <c r="T859" s="11"/>
       <c r="U859" s="11"/>
     </row>
-    <row r="860" spans="1:21" ht="18" customHeight="1">
+    <row r="860" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A860" s="1"/>
       <c r="B860" s="27"/>
       <c r="C860" s="17"/>
@@ -20938,7 +20906,7 @@
       <c r="T860" s="11"/>
       <c r="U860" s="11"/>
     </row>
-    <row r="861" spans="1:21" ht="18" customHeight="1">
+    <row r="861" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A861" s="1"/>
       <c r="B861" s="27"/>
       <c r="C861" s="17"/>
@@ -20961,7 +20929,7 @@
       <c r="T861" s="11"/>
       <c r="U861" s="11"/>
     </row>
-    <row r="862" spans="1:21" ht="18" customHeight="1">
+    <row r="862" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A862" s="1"/>
       <c r="B862" s="27"/>
       <c r="C862" s="17"/>
@@ -20984,7 +20952,7 @@
       <c r="T862" s="11"/>
       <c r="U862" s="11"/>
     </row>
-    <row r="863" spans="1:21" ht="18" customHeight="1">
+    <row r="863" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A863" s="1"/>
       <c r="B863" s="27"/>
       <c r="C863" s="17"/>
@@ -21007,7 +20975,7 @@
       <c r="T863" s="11"/>
       <c r="U863" s="11"/>
     </row>
-    <row r="864" spans="1:21" ht="18" customHeight="1">
+    <row r="864" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A864" s="1"/>
       <c r="B864" s="27"/>
       <c r="C864" s="17"/>
@@ -21030,7 +20998,7 @@
       <c r="T864" s="11"/>
       <c r="U864" s="11"/>
     </row>
-    <row r="865" spans="1:21" ht="18" customHeight="1">
+    <row r="865" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A865" s="1"/>
       <c r="B865" s="27"/>
       <c r="C865" s="17"/>
@@ -21053,7 +21021,7 @@
       <c r="T865" s="11"/>
       <c r="U865" s="11"/>
     </row>
-    <row r="866" spans="1:21" ht="18" customHeight="1">
+    <row r="866" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A866" s="1"/>
       <c r="B866" s="27"/>
       <c r="C866" s="17"/>
@@ -21076,7 +21044,7 @@
       <c r="T866" s="11"/>
       <c r="U866" s="11"/>
     </row>
-    <row r="867" spans="1:21" ht="18" customHeight="1">
+    <row r="867" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A867" s="1"/>
       <c r="B867" s="27"/>
       <c r="C867" s="17"/>
@@ -21099,7 +21067,7 @@
       <c r="T867" s="11"/>
       <c r="U867" s="11"/>
     </row>
-    <row r="868" spans="1:21" ht="18" customHeight="1">
+    <row r="868" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A868" s="1"/>
       <c r="B868" s="27"/>
       <c r="C868" s="17"/>
@@ -21122,7 +21090,7 @@
       <c r="T868" s="11"/>
       <c r="U868" s="11"/>
     </row>
-    <row r="869" spans="1:21" ht="18" customHeight="1">
+    <row r="869" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A869" s="1"/>
       <c r="B869" s="27"/>
       <c r="C869" s="17"/>
@@ -21145,7 +21113,7 @@
       <c r="T869" s="11"/>
       <c r="U869" s="11"/>
     </row>
-    <row r="870" spans="1:21" ht="18" customHeight="1">
+    <row r="870" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A870" s="1"/>
       <c r="B870" s="27"/>
       <c r="C870" s="17"/>
@@ -21168,7 +21136,7 @@
       <c r="T870" s="11"/>
       <c r="U870" s="11"/>
     </row>
-    <row r="871" spans="1:21" ht="18" customHeight="1">
+    <row r="871" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A871" s="1"/>
       <c r="B871" s="27"/>
       <c r="C871" s="17"/>
@@ -21191,7 +21159,7 @@
       <c r="T871" s="11"/>
       <c r="U871" s="11"/>
     </row>
-    <row r="872" spans="1:21" ht="18" customHeight="1">
+    <row r="872" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A872" s="1"/>
       <c r="B872" s="27"/>
       <c r="C872" s="17"/>
@@ -21214,7 +21182,7 @@
       <c r="T872" s="11"/>
       <c r="U872" s="11"/>
     </row>
-    <row r="873" spans="1:21" ht="18" customHeight="1">
+    <row r="873" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A873" s="1"/>
       <c r="B873" s="27"/>
       <c r="C873" s="17"/>
@@ -21237,7 +21205,7 @@
       <c r="T873" s="11"/>
       <c r="U873" s="11"/>
     </row>
-    <row r="874" spans="1:21" ht="18" customHeight="1">
+    <row r="874" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A874" s="1"/>
       <c r="B874" s="27"/>
       <c r="C874" s="17"/>
@@ -21260,7 +21228,7 @@
       <c r="T874" s="11"/>
       <c r="U874" s="11"/>
     </row>
-    <row r="875" spans="1:21" ht="18" customHeight="1">
+    <row r="875" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A875" s="1"/>
       <c r="B875" s="27"/>
       <c r="C875" s="17"/>
@@ -21283,7 +21251,7 @@
       <c r="T875" s="11"/>
       <c r="U875" s="11"/>
     </row>
-    <row r="876" spans="1:21" ht="18" customHeight="1">
+    <row r="876" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A876" s="1"/>
       <c r="B876" s="27"/>
       <c r="C876" s="17"/>
@@ -21306,7 +21274,7 @@
       <c r="T876" s="11"/>
       <c r="U876" s="11"/>
     </row>
-    <row r="877" spans="1:21" ht="18" customHeight="1">
+    <row r="877" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A877" s="1"/>
       <c r="B877" s="27"/>
       <c r="C877" s="17"/>
@@ -21329,7 +21297,7 @@
       <c r="T877" s="11"/>
       <c r="U877" s="11"/>
     </row>
-    <row r="878" spans="1:21" ht="18" customHeight="1">
+    <row r="878" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A878" s="1"/>
       <c r="B878" s="27"/>
       <c r="C878" s="17"/>
@@ -21352,7 +21320,7 @@
       <c r="T878" s="11"/>
       <c r="U878" s="11"/>
     </row>
-    <row r="879" spans="1:21" ht="18" customHeight="1">
+    <row r="879" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A879" s="1"/>
       <c r="B879" s="27"/>
       <c r="C879" s="17"/>
@@ -21375,7 +21343,7 @@
       <c r="T879" s="11"/>
       <c r="U879" s="11"/>
     </row>
-    <row r="880" spans="1:21" ht="18" customHeight="1">
+    <row r="880" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A880" s="1"/>
       <c r="B880" s="27"/>
       <c r="C880" s="17"/>
@@ -21398,7 +21366,7 @@
       <c r="T880" s="11"/>
       <c r="U880" s="11"/>
     </row>
-    <row r="881" spans="1:21" ht="18" customHeight="1">
+    <row r="881" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A881" s="1"/>
       <c r="B881" s="27"/>
       <c r="C881" s="17"/>
@@ -21421,7 +21389,7 @@
       <c r="T881" s="11"/>
       <c r="U881" s="11"/>
     </row>
-    <row r="882" spans="1:21" ht="18" customHeight="1">
+    <row r="882" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A882" s="1"/>
       <c r="B882" s="27"/>
       <c r="C882" s="17"/>
@@ -21444,7 +21412,7 @@
       <c r="T882" s="11"/>
       <c r="U882" s="11"/>
     </row>
-    <row r="883" spans="1:21" ht="18" customHeight="1">
+    <row r="883" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A883" s="1"/>
       <c r="B883" s="27"/>
       <c r="C883" s="17"/>
@@ -21467,7 +21435,7 @@
       <c r="T883" s="11"/>
       <c r="U883" s="11"/>
     </row>
-    <row r="884" spans="1:21" ht="18" customHeight="1">
+    <row r="884" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A884" s="1"/>
       <c r="B884" s="27"/>
       <c r="C884" s="17"/>
@@ -21490,7 +21458,7 @@
       <c r="T884" s="11"/>
       <c r="U884" s="11"/>
     </row>
-    <row r="885" spans="1:21" ht="18" customHeight="1">
+    <row r="885" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A885" s="1"/>
       <c r="B885" s="27"/>
       <c r="C885" s="17"/>
@@ -21513,7 +21481,7 @@
       <c r="T885" s="11"/>
       <c r="U885" s="11"/>
     </row>
-    <row r="886" spans="1:21" ht="18" customHeight="1">
+    <row r="886" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A886" s="1"/>
       <c r="B886" s="27"/>
       <c r="C886" s="17"/>
@@ -21536,7 +21504,7 @@
       <c r="T886" s="11"/>
       <c r="U886" s="11"/>
     </row>
-    <row r="887" spans="1:21" ht="18" customHeight="1">
+    <row r="887" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A887" s="1"/>
       <c r="B887" s="27"/>
       <c r="C887" s="17"/>
@@ -21559,7 +21527,7 @@
       <c r="T887" s="11"/>
       <c r="U887" s="11"/>
     </row>
-    <row r="888" spans="1:21" ht="18" customHeight="1">
+    <row r="888" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A888" s="1"/>
       <c r="B888" s="27"/>
       <c r="C888" s="17"/>
@@ -21582,7 +21550,7 @@
       <c r="T888" s="11"/>
       <c r="U888" s="11"/>
     </row>
-    <row r="889" spans="1:21" ht="18" customHeight="1">
+    <row r="889" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A889" s="1"/>
       <c r="B889" s="27"/>
       <c r="C889" s="17"/>
@@ -21605,7 +21573,7 @@
       <c r="T889" s="11"/>
       <c r="U889" s="11"/>
     </row>
-    <row r="890" spans="1:21" ht="18" customHeight="1">
+    <row r="890" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A890" s="1"/>
       <c r="B890" s="27"/>
       <c r="C890" s="17"/>
@@ -21628,7 +21596,7 @@
       <c r="T890" s="11"/>
       <c r="U890" s="11"/>
     </row>
-    <row r="891" spans="1:21" ht="18" customHeight="1">
+    <row r="891" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A891" s="1"/>
       <c r="B891" s="27"/>
       <c r="C891" s="17"/>
@@ -21651,7 +21619,7 @@
       <c r="T891" s="11"/>
       <c r="U891" s="11"/>
     </row>
-    <row r="892" spans="1:21" ht="18" customHeight="1">
+    <row r="892" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A892" s="1"/>
       <c r="B892" s="27"/>
       <c r="C892" s="17"/>
@@ -21674,7 +21642,7 @@
       <c r="T892" s="11"/>
       <c r="U892" s="11"/>
     </row>
-    <row r="893" spans="1:21" ht="18" customHeight="1">
+    <row r="893" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A893" s="1"/>
       <c r="B893" s="27"/>
       <c r="C893" s="17"/>
@@ -21697,7 +21665,7 @@
       <c r="T893" s="11"/>
       <c r="U893" s="11"/>
     </row>
-    <row r="894" spans="1:21" ht="18" customHeight="1">
+    <row r="894" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A894" s="1"/>
       <c r="B894" s="27"/>
       <c r="C894" s="17"/>
@@ -21720,7 +21688,7 @@
       <c r="T894" s="11"/>
       <c r="U894" s="11"/>
     </row>
-    <row r="895" spans="1:21" ht="18" customHeight="1">
+    <row r="895" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A895" s="1"/>
       <c r="B895" s="27"/>
       <c r="C895" s="17"/>
@@ -21743,7 +21711,7 @@
       <c r="T895" s="11"/>
       <c r="U895" s="11"/>
     </row>
-    <row r="896" spans="1:21" ht="18" customHeight="1">
+    <row r="896" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A896" s="1"/>
       <c r="B896" s="27"/>
       <c r="C896" s="17"/>
@@ -21766,7 +21734,7 @@
       <c r="T896" s="11"/>
       <c r="U896" s="11"/>
     </row>
-    <row r="897" spans="1:21" ht="18" customHeight="1">
+    <row r="897" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A897" s="1"/>
       <c r="B897" s="27"/>
       <c r="C897" s="17"/>
@@ -21789,7 +21757,7 @@
       <c r="T897" s="11"/>
       <c r="U897" s="11"/>
     </row>
-    <row r="898" spans="1:21" ht="18" customHeight="1">
+    <row r="898" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A898" s="1"/>
       <c r="B898" s="27"/>
       <c r="C898" s="17"/>
@@ -21812,7 +21780,7 @@
       <c r="T898" s="11"/>
       <c r="U898" s="11"/>
     </row>
-    <row r="899" spans="1:21" ht="18" customHeight="1">
+    <row r="899" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A899" s="1"/>
       <c r="B899" s="27"/>
       <c r="C899" s="17"/>
@@ -21835,7 +21803,7 @@
       <c r="T899" s="11"/>
       <c r="U899" s="11"/>
     </row>
-    <row r="900" spans="1:21" ht="18" customHeight="1">
+    <row r="900" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A900" s="1"/>
       <c r="B900" s="27"/>
       <c r="C900" s="17"/>
@@ -21858,7 +21826,7 @@
       <c r="T900" s="11"/>
       <c r="U900" s="11"/>
     </row>
-    <row r="901" spans="1:21" ht="18" customHeight="1">
+    <row r="901" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A901" s="1"/>
       <c r="B901" s="27"/>
       <c r="C901" s="17"/>
@@ -21881,7 +21849,7 @@
       <c r="T901" s="11"/>
       <c r="U901" s="11"/>
     </row>
-    <row r="902" spans="1:21" ht="18" customHeight="1">
+    <row r="902" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A902" s="1"/>
       <c r="B902" s="27"/>
       <c r="C902" s="17"/>
@@ -21904,7 +21872,7 @@
       <c r="T902" s="11"/>
       <c r="U902" s="11"/>
     </row>
-    <row r="903" spans="1:21" ht="18" customHeight="1">
+    <row r="903" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A903" s="1"/>
       <c r="B903" s="27"/>
       <c r="C903" s="17"/>
@@ -21927,7 +21895,7 @@
       <c r="T903" s="11"/>
       <c r="U903" s="11"/>
     </row>
-    <row r="904" spans="1:21" ht="18" customHeight="1">
+    <row r="904" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A904" s="1"/>
       <c r="B904" s="27"/>
       <c r="C904" s="17"/>
@@ -21950,7 +21918,7 @@
       <c r="T904" s="11"/>
       <c r="U904" s="11"/>
     </row>
-    <row r="905" spans="1:21" ht="18" customHeight="1">
+    <row r="905" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A905" s="1"/>
       <c r="B905" s="27"/>
       <c r="C905" s="17"/>
@@ -21973,7 +21941,7 @@
       <c r="T905" s="11"/>
       <c r="U905" s="11"/>
     </row>
-    <row r="906" spans="1:21" ht="18" customHeight="1">
+    <row r="906" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A906" s="1"/>
       <c r="B906" s="27"/>
       <c r="C906" s="17"/>
@@ -21996,7 +21964,7 @@
       <c r="T906" s="11"/>
       <c r="U906" s="11"/>
     </row>
-    <row r="907" spans="1:21" ht="18" customHeight="1">
+    <row r="907" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A907" s="1"/>
       <c r="B907" s="27"/>
       <c r="C907" s="17"/>
@@ -22019,7 +21987,7 @@
       <c r="T907" s="11"/>
       <c r="U907" s="11"/>
     </row>
-    <row r="908" spans="1:21" ht="18" customHeight="1">
+    <row r="908" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A908" s="1"/>
       <c r="B908" s="27"/>
       <c r="C908" s="17"/>
@@ -22042,7 +22010,7 @@
       <c r="T908" s="11"/>
       <c r="U908" s="11"/>
     </row>
-    <row r="909" spans="1:21" ht="18" customHeight="1">
+    <row r="909" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A909" s="1"/>
       <c r="B909" s="27"/>
       <c r="C909" s="17"/>
@@ -22065,7 +22033,7 @@
       <c r="T909" s="11"/>
       <c r="U909" s="11"/>
     </row>
-    <row r="910" spans="1:21" ht="18" customHeight="1">
+    <row r="910" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A910" s="1"/>
       <c r="B910" s="27"/>
       <c r="C910" s="17"/>
@@ -22088,7 +22056,7 @@
       <c r="T910" s="11"/>
       <c r="U910" s="11"/>
     </row>
-    <row r="911" spans="1:21" ht="18" customHeight="1">
+    <row r="911" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A911" s="1"/>
       <c r="B911" s="27"/>
       <c r="C911" s="17"/>
@@ -22111,7 +22079,7 @@
       <c r="T911" s="11"/>
       <c r="U911" s="11"/>
     </row>
-    <row r="912" spans="1:21" ht="18" customHeight="1">
+    <row r="912" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A912" s="1"/>
       <c r="B912" s="27"/>
       <c r="C912" s="17"/>
@@ -22134,7 +22102,7 @@
       <c r="T912" s="11"/>
       <c r="U912" s="11"/>
     </row>
-    <row r="913" spans="1:21" ht="18" customHeight="1">
+    <row r="913" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A913" s="1"/>
       <c r="B913" s="27"/>
       <c r="C913" s="17"/>
@@ -22157,7 +22125,7 @@
       <c r="T913" s="11"/>
       <c r="U913" s="11"/>
     </row>
-    <row r="914" spans="1:21" ht="18" customHeight="1">
+    <row r="914" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A914" s="1"/>
       <c r="B914" s="27"/>
       <c r="C914" s="17"/>
@@ -22180,7 +22148,7 @@
       <c r="T914" s="11"/>
       <c r="U914" s="11"/>
     </row>
-    <row r="915" spans="1:21" ht="18" customHeight="1">
+    <row r="915" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A915" s="1"/>
       <c r="B915" s="27"/>
       <c r="C915" s="17"/>
@@ -22203,7 +22171,7 @@
       <c r="T915" s="11"/>
       <c r="U915" s="11"/>
     </row>
-    <row r="916" spans="1:21" ht="18" customHeight="1">
+    <row r="916" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A916" s="1"/>
       <c r="B916" s="27"/>
       <c r="C916" s="17"/>
@@ -22226,7 +22194,7 @@
       <c r="T916" s="11"/>
       <c r="U916" s="11"/>
     </row>
-    <row r="917" spans="1:21" ht="18" customHeight="1">
+    <row r="917" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A917" s="1"/>
       <c r="B917" s="27"/>
       <c r="C917" s="17"/>
@@ -22249,7 +22217,7 @@
       <c r="T917" s="11"/>
       <c r="U917" s="11"/>
     </row>
-    <row r="918" spans="1:21" ht="18" customHeight="1">
+    <row r="918" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A918" s="1"/>
       <c r="B918" s="27"/>
       <c r="C918" s="17"/>
@@ -22272,7 +22240,7 @@
       <c r="T918" s="11"/>
       <c r="U918" s="11"/>
     </row>
-    <row r="919" spans="1:21" ht="18" customHeight="1">
+    <row r="919" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A919" s="1"/>
       <c r="B919" s="27"/>
       <c r="C919" s="17"/>
@@ -22295,7 +22263,7 @@
       <c r="T919" s="11"/>
       <c r="U919" s="11"/>
     </row>
-    <row r="920" spans="1:21" ht="18" customHeight="1">
+    <row r="920" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A920" s="1"/>
       <c r="B920" s="27"/>
       <c r="C920" s="17"/>
@@ -22318,7 +22286,7 @@
       <c r="T920" s="11"/>
       <c r="U920" s="11"/>
     </row>
-    <row r="921" spans="1:21" ht="18" customHeight="1">
+    <row r="921" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A921" s="1"/>
       <c r="B921" s="27"/>
       <c r="C921" s="17"/>
@@ -22341,7 +22309,7 @@
       <c r="T921" s="11"/>
       <c r="U921" s="11"/>
     </row>
-    <row r="922" spans="1:21" ht="18" customHeight="1">
+    <row r="922" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A922" s="1"/>
       <c r="B922" s="27"/>
       <c r="C922" s="17"/>
@@ -22364,7 +22332,7 @@
       <c r="T922" s="11"/>
       <c r="U922" s="11"/>
     </row>
-    <row r="923" spans="1:21" ht="18" customHeight="1">
+    <row r="923" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A923" s="1"/>
       <c r="B923" s="27"/>
       <c r="C923" s="17"/>
@@ -22387,7 +22355,7 @@
       <c r="T923" s="11"/>
       <c r="U923" s="11"/>
     </row>
-    <row r="924" spans="1:21" ht="18" customHeight="1">
+    <row r="924" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A924" s="1"/>
       <c r="B924" s="27"/>
       <c r="C924" s="17"/>
@@ -22410,7 +22378,7 @@
       <c r="T924" s="11"/>
       <c r="U924" s="11"/>
     </row>
-    <row r="925" spans="1:21" ht="18" customHeight="1">
+    <row r="925" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A925" s="1"/>
       <c r="B925" s="27"/>
       <c r="C925" s="17"/>
@@ -22433,7 +22401,7 @@
       <c r="T925" s="11"/>
       <c r="U925" s="11"/>
     </row>
-    <row r="926" spans="1:21" ht="18" customHeight="1">
+    <row r="926" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A926" s="1"/>
       <c r="B926" s="27"/>
       <c r="C926" s="17"/>
@@ -22456,7 +22424,7 @@
       <c r="T926" s="11"/>
       <c r="U926" s="11"/>
     </row>
-    <row r="927" spans="1:21" ht="18" customHeight="1">
+    <row r="927" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A927" s="1"/>
       <c r="B927" s="27"/>
       <c r="C927" s="17"/>
@@ -22479,7 +22447,7 @@
       <c r="T927" s="11"/>
       <c r="U927" s="11"/>
     </row>
-    <row r="928" spans="1:21" ht="18" customHeight="1">
+    <row r="928" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A928" s="1"/>
       <c r="B928" s="27"/>
       <c r="C928" s="17"/>
@@ -22502,7 +22470,7 @@
       <c r="T928" s="11"/>
       <c r="U928" s="11"/>
     </row>
-    <row r="929" spans="1:21" ht="18" customHeight="1">
+    <row r="929" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A929" s="1"/>
       <c r="B929" s="27"/>
       <c r="C929" s="17"/>
@@ -22525,7 +22493,7 @@
       <c r="T929" s="11"/>
       <c r="U929" s="11"/>
     </row>
-    <row r="930" spans="1:21" ht="18" customHeight="1">
+    <row r="930" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A930" s="1"/>
       <c r="B930" s="27"/>
       <c r="C930" s="17"/>
@@ -22548,7 +22516,7 @@
       <c r="T930" s="11"/>
       <c r="U930" s="11"/>
     </row>
-    <row r="931" spans="1:21" ht="18" customHeight="1">
+    <row r="931" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A931" s="1"/>
       <c r="B931" s="27"/>
       <c r="C931" s="17"/>
@@ -22571,7 +22539,7 @@
       <c r="T931" s="11"/>
       <c r="U931" s="11"/>
     </row>
-    <row r="932" spans="1:21" ht="18" customHeight="1">
+    <row r="932" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A932" s="1"/>
       <c r="B932" s="27"/>
       <c r="C932" s="17"/>
@@ -22594,7 +22562,7 @@
       <c r="T932" s="11"/>
       <c r="U932" s="11"/>
     </row>
-    <row r="933" spans="1:21" ht="18" customHeight="1">
+    <row r="933" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A933" s="1"/>
       <c r="B933" s="27"/>
       <c r="C933" s="17"/>
@@ -22617,7 +22585,7 @@
       <c r="T933" s="11"/>
       <c r="U933" s="11"/>
     </row>
-    <row r="934" spans="1:21" ht="18" customHeight="1">
+    <row r="934" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A934" s="1"/>
       <c r="B934" s="27"/>
       <c r="C934" s="17"/>
@@ -22640,7 +22608,7 @@
       <c r="T934" s="11"/>
       <c r="U934" s="11"/>
     </row>
-    <row r="935" spans="1:21" ht="18" customHeight="1">
+    <row r="935" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A935" s="1"/>
       <c r="B935" s="27"/>
       <c r="C935" s="17"/>
@@ -22663,7 +22631,7 @@
       <c r="T935" s="11"/>
       <c r="U935" s="11"/>
     </row>
-    <row r="936" spans="1:21" ht="18" customHeight="1">
+    <row r="936" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A936" s="1"/>
       <c r="B936" s="27"/>
       <c r="C936" s="17"/>
@@ -22686,7 +22654,7 @@
       <c r="T936" s="11"/>
       <c r="U936" s="11"/>
     </row>
-    <row r="937" spans="1:21" ht="18" customHeight="1">
+    <row r="937" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A937" s="1"/>
       <c r="B937" s="27"/>
       <c r="C937" s="17"/>
@@ -22709,7 +22677,7 @@
       <c r="T937" s="11"/>
       <c r="U937" s="11"/>
     </row>
-    <row r="938" spans="1:21" ht="18" customHeight="1">
+    <row r="938" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A938" s="1"/>
       <c r="B938" s="27"/>
       <c r="C938" s="17"/>
@@ -22732,7 +22700,7 @@
       <c r="T938" s="11"/>
       <c r="U938" s="11"/>
     </row>
-    <row r="939" spans="1:21" ht="18" customHeight="1">
+    <row r="939" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A939" s="1"/>
       <c r="B939" s="27"/>
       <c r="C939" s="17"/>
@@ -22755,7 +22723,7 @@
       <c r="T939" s="11"/>
       <c r="U939" s="11"/>
     </row>
-    <row r="940" spans="1:21" ht="18" customHeight="1">
+    <row r="940" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A940" s="1"/>
       <c r="B940" s="27"/>
       <c r="C940" s="17"/>
@@ -22778,7 +22746,7 @@
       <c r="T940" s="11"/>
       <c r="U940" s="11"/>
     </row>
-    <row r="941" spans="1:21" ht="18" customHeight="1">
+    <row r="941" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A941" s="1"/>
       <c r="B941" s="27"/>
       <c r="C941" s="17"/>
@@ -22801,7 +22769,7 @@
       <c r="T941" s="11"/>
       <c r="U941" s="11"/>
     </row>
-    <row r="942" spans="1:21" ht="18" customHeight="1">
+    <row r="942" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A942" s="1"/>
       <c r="B942" s="27"/>
       <c r="C942" s="17"/>
@@ -22824,7 +22792,7 @@
       <c r="T942" s="11"/>
       <c r="U942" s="11"/>
     </row>
-    <row r="943" spans="1:21" ht="18" customHeight="1">
+    <row r="943" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A943" s="1"/>
       <c r="B943" s="27"/>
       <c r="C943" s="17"/>
@@ -22847,7 +22815,7 @@
       <c r="T943" s="11"/>
       <c r="U943" s="11"/>
     </row>
-    <row r="944" spans="1:21" ht="18" customHeight="1">
+    <row r="944" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A944" s="1"/>
       <c r="B944" s="27"/>
       <c r="C944" s="17"/>
@@ -22870,7 +22838,7 @@
       <c r="T944" s="11"/>
       <c r="U944" s="11"/>
     </row>
-    <row r="945" spans="1:21" ht="18" customHeight="1">
+    <row r="945" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A945" s="1"/>
       <c r="B945" s="27"/>
       <c r="C945" s="17"/>
@@ -22893,7 +22861,7 @@
       <c r="T945" s="11"/>
       <c r="U945" s="11"/>
     </row>
-    <row r="946" spans="1:21" ht="18" customHeight="1">
+    <row r="946" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A946" s="1"/>
       <c r="B946" s="27"/>
       <c r="C946" s="17"/>
@@ -22916,7 +22884,7 @@
       <c r="T946" s="11"/>
       <c r="U946" s="11"/>
     </row>
-    <row r="947" spans="1:21" ht="18" customHeight="1">
+    <row r="947" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A947" s="1"/>
       <c r="B947" s="27"/>
       <c r="C947" s="17"/>
@@ -22959,6 +22927,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F5D778AC6A79A84EAA5B25C5A2BFF7B6" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4061397ea8fd8f272d8b26ba942e61d2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3cd0eaed-44fe-4f97-8632-c05a782ebbb7" xmlns:ns3="75164c79-2692-43d6-94a7-34b44bf80abd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b13378bff9c1c8ba474ff50185c4976f" ns2:_="" ns3:_="">
     <xsd:import namespace="3cd0eaed-44fe-4f97-8632-c05a782ebbb7"/>
@@ -23123,15 +23100,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -23139,13 +23107,37 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55915E3D-8D32-4904-AE11-02FF4B35B651}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{075245DD-0B21-42AF-837E-557C93B33EF5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{075245DD-0B21-42AF-837E-557C93B33EF5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55915E3D-8D32-4904-AE11-02FF4B35B651}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3cd0eaed-44fe-4f97-8632-c05a782ebbb7"/>
+    <ds:schemaRef ds:uri="75164c79-2692-43d6-94a7-34b44bf80abd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F9D8340-318B-43DD-BE9C-C876AB21B0D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F9D8340-318B-43DD-BE9C-C876AB21B0D8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>